--- a/VA_result_TEL.xlsx
+++ b/VA_result_TEL.xlsx
@@ -1088,10 +1088,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>376576.054201833</v>
+        <v>376576.054202336</v>
       </c>
       <c r="C2" t="n">
-        <v>37.6576054201833</v>
+        <v>37.6576054202336</v>
       </c>
     </row>
     <row r="3">
@@ -1102,7 +1102,7 @@
         <v>487847.416454892</v>
       </c>
       <c r="C3" t="n">
-        <v>48.7847416454892</v>
+        <v>48.7847416454891</v>
       </c>
     </row>
     <row r="4">
@@ -1110,10 +1110,10 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>137930.497384685</v>
+        <v>137930.497384738</v>
       </c>
       <c r="C4" t="n">
-        <v>13.7930497384685</v>
+        <v>13.7930497384738</v>
       </c>
     </row>
     <row r="5">
@@ -1121,10 +1121,10 @@
         <v>31</v>
       </c>
       <c r="B5" t="n">
-        <v>696734.250950812</v>
+        <v>696734.250950203</v>
       </c>
       <c r="C5" t="n">
-        <v>69.6734250950812</v>
+        <v>69.6734250950203</v>
       </c>
     </row>
     <row r="6">
@@ -1132,10 +1132,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>377371.84080423</v>
+        <v>377371.840804729</v>
       </c>
       <c r="C6" t="n">
-        <v>37.737184080423</v>
+        <v>37.7371840804729</v>
       </c>
     </row>
     <row r="7">
@@ -1143,10 +1143,10 @@
         <v>32</v>
       </c>
       <c r="B7" t="n">
-        <v>487751.637279192</v>
+        <v>487751.637279191</v>
       </c>
       <c r="C7" t="n">
-        <v>48.7751637279192</v>
+        <v>48.7751637279191</v>
       </c>
     </row>
     <row r="8">
@@ -1154,10 +1154,10 @@
         <v>33</v>
       </c>
       <c r="B8" t="n">
-        <v>138355.786055623</v>
+        <v>138355.786055678</v>
       </c>
       <c r="C8" t="n">
-        <v>13.8355786055623</v>
+        <v>13.8355786055678</v>
       </c>
     </row>
     <row r="9">
@@ -1165,10 +1165,10 @@
         <v>34</v>
       </c>
       <c r="B9" t="n">
-        <v>695392.344295051</v>
+        <v>695392.344294446</v>
       </c>
       <c r="C9" t="n">
-        <v>69.5392344295051</v>
+        <v>69.5392344294446</v>
       </c>
     </row>
     <row r="10">
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>378236.895891716</v>
+        <v>378236.89589221</v>
       </c>
       <c r="C10" t="n">
-        <v>37.8236895891716</v>
+        <v>37.823689589221</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
         <v>487670.505777647</v>
       </c>
       <c r="C11" t="n">
-        <v>48.7670505777647</v>
+        <v>48.7670505777646</v>
       </c>
     </row>
     <row r="12">
@@ -1198,10 +1198,10 @@
         <v>36</v>
       </c>
       <c r="B12" t="n">
-        <v>138732.842726539</v>
+        <v>138732.842726596</v>
       </c>
       <c r="C12" t="n">
-        <v>13.8732842726539</v>
+        <v>13.8732842726596</v>
       </c>
     </row>
     <row r="13">
@@ -1209,10 +1209,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="n">
-        <v>693967.997410502</v>
+        <v>693967.997409902</v>
       </c>
       <c r="C13" t="n">
-        <v>69.3967997410502</v>
+        <v>69.3967997409902</v>
       </c>
     </row>
     <row r="14">
@@ -1220,10 +1220,10 @@
         <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>379922.12721674</v>
+        <v>379922.127217224</v>
       </c>
       <c r="C14" t="n">
-        <v>37.992212721674</v>
+        <v>37.9922127217224</v>
       </c>
     </row>
     <row r="15">
@@ -1242,10 +1242,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="n">
-        <v>139289.895421997</v>
+        <v>139289.895422058</v>
       </c>
       <c r="C16" t="n">
-        <v>13.9289895421997</v>
+        <v>13.9289895422058</v>
       </c>
     </row>
     <row r="17">
@@ -1253,10 +1253,10 @@
         <v>40</v>
       </c>
       <c r="B17" t="n">
-        <v>691727.904718579</v>
+        <v>691727.904717987</v>
       </c>
       <c r="C17" t="n">
-        <v>69.1727904718579</v>
+        <v>69.1727904717987</v>
       </c>
     </row>
     <row r="18">
@@ -1264,10 +1264,10 @@
         <v>6</v>
       </c>
       <c r="B18" t="n">
-        <v>381287.933904026</v>
+        <v>381287.933904503</v>
       </c>
       <c r="C18" t="n">
-        <v>38.1287933904026</v>
+        <v>38.1287933904503</v>
       </c>
     </row>
     <row r="19">
@@ -1275,10 +1275,10 @@
         <v>41</v>
       </c>
       <c r="B19" t="n">
-        <v>485794.669870245</v>
+        <v>485794.669870252</v>
       </c>
       <c r="C19" t="n">
-        <v>48.5794669870245</v>
+        <v>48.5794669870252</v>
       </c>
     </row>
     <row r="20">
@@ -1286,10 +1286,10 @@
         <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>137945.575803972</v>
+        <v>137945.575804048</v>
       </c>
       <c r="C20" t="n">
-        <v>13.7945575803971</v>
+        <v>13.7945575804048</v>
       </c>
     </row>
     <row r="21">
@@ -1297,10 +1297,10 @@
         <v>43</v>
       </c>
       <c r="B21" t="n">
-        <v>686931.041552067</v>
+        <v>686931.0415515</v>
       </c>
       <c r="C21" t="n">
-        <v>68.6931041552067</v>
+        <v>68.69310415515</v>
       </c>
     </row>
     <row r="22">
@@ -1308,10 +1308,10 @@
         <v>7</v>
       </c>
       <c r="B22" t="n">
-        <v>397755.939876154</v>
+        <v>397755.939876537</v>
       </c>
       <c r="C22" t="n">
-        <v>39.7755939876154</v>
+        <v>39.7755939876537</v>
       </c>
     </row>
     <row r="23">
@@ -1319,10 +1319,10 @@
         <v>44</v>
       </c>
       <c r="B23" t="n">
-        <v>478996.718856279</v>
+        <v>478996.71885631</v>
       </c>
       <c r="C23" t="n">
-        <v>47.8996718856279</v>
+        <v>47.899671885631</v>
       </c>
     </row>
     <row r="24">
@@ -1330,10 +1330,10 @@
         <v>45</v>
       </c>
       <c r="B24" t="n">
-        <v>135863.216935976</v>
+        <v>135863.216936083</v>
       </c>
       <c r="C24" t="n">
-        <v>13.5863216935976</v>
+        <v>13.5863216936083</v>
       </c>
     </row>
     <row r="25">
@@ -1341,10 +1341,10 @@
         <v>46</v>
       </c>
       <c r="B25" t="n">
-        <v>677929.020808246</v>
+        <v>677929.020807724</v>
       </c>
       <c r="C25" t="n">
-        <v>67.7929020808246</v>
+        <v>67.7929020807724</v>
       </c>
     </row>
     <row r="26">
@@ -1352,10 +1352,10 @@
         <v>8</v>
       </c>
       <c r="B26" t="n">
-        <v>414821.778162214</v>
+        <v>414821.778162503</v>
       </c>
       <c r="C26" t="n">
-        <v>41.4821778162214</v>
+        <v>41.4821778162503</v>
       </c>
     </row>
     <row r="27">
@@ -1363,10 +1363,10 @@
         <v>47</v>
       </c>
       <c r="B27" t="n">
-        <v>472967.850274146</v>
+        <v>472967.8502742</v>
       </c>
       <c r="C27" t="n">
-        <v>47.2967850274146</v>
+        <v>47.29678502742</v>
       </c>
     </row>
     <row r="28">
@@ -1374,10 +1374,10 @@
         <v>48</v>
       </c>
       <c r="B28" t="n">
-        <v>134582.080417518</v>
+        <v>134582.080417652</v>
       </c>
       <c r="C28" t="n">
-        <v>13.4582080417518</v>
+        <v>13.4582080417652</v>
       </c>
     </row>
     <row r="29">
@@ -1385,10 +1385,10 @@
         <v>49</v>
       </c>
       <c r="B29" t="n">
-        <v>669865.555332135</v>
+        <v>669865.555331655</v>
       </c>
       <c r="C29" t="n">
-        <v>66.9865555332135</v>
+        <v>66.9865555331655</v>
       </c>
     </row>
     <row r="30">
@@ -1396,10 +1396,10 @@
         <v>9</v>
       </c>
       <c r="B30" t="n">
-        <v>429632.858872673</v>
+        <v>429632.858872865</v>
       </c>
       <c r="C30" t="n">
-        <v>42.9632858872673</v>
+        <v>42.9632858872865</v>
       </c>
     </row>
     <row r="31">
@@ -1407,10 +1407,10 @@
         <v>50</v>
       </c>
       <c r="B31" t="n">
-        <v>465865.67485906</v>
+        <v>465865.674859121</v>
       </c>
       <c r="C31" t="n">
-        <v>46.5865674859059</v>
+        <v>46.5865674859121</v>
       </c>
     </row>
     <row r="32">
@@ -1418,10 +1418,10 @@
         <v>51</v>
       </c>
       <c r="B32" t="n">
-        <v>145584.43739607</v>
+        <v>145584.437396233</v>
       </c>
       <c r="C32" t="n">
-        <v>14.558443739607</v>
+        <v>14.5584437396233</v>
       </c>
     </row>
     <row r="33">
@@ -1429,10 +1429,10 @@
         <v>52</v>
       </c>
       <c r="B33" t="n">
-        <v>645385.610408032</v>
+        <v>645385.610407632</v>
       </c>
       <c r="C33" t="n">
-        <v>64.5385610408032</v>
+        <v>64.5385610407632</v>
       </c>
     </row>
     <row r="34">
@@ -1440,10 +1440,10 @@
         <v>10</v>
       </c>
       <c r="B34" t="n">
-        <v>447264.148739431</v>
+        <v>447264.148739515</v>
       </c>
       <c r="C34" t="n">
-        <v>44.7264148739431</v>
+        <v>44.7264148739514</v>
       </c>
     </row>
     <row r="35">
@@ -1451,10 +1451,10 @@
         <v>53</v>
       </c>
       <c r="B35" t="n">
-        <v>461101.054972202</v>
+        <v>461101.054972258</v>
       </c>
       <c r="C35" t="n">
-        <v>46.1101054972202</v>
+        <v>46.1101054972258</v>
       </c>
     </row>
     <row r="36">
@@ -1462,10 +1462,10 @@
         <v>54</v>
       </c>
       <c r="B36" t="n">
-        <v>157397.862586852</v>
+        <v>157397.86258703</v>
       </c>
       <c r="C36" t="n">
-        <v>15.7397862586852</v>
+        <v>15.739786258703</v>
       </c>
     </row>
     <row r="37">
@@ -1473,10 +1473,10 @@
         <v>55</v>
       </c>
       <c r="B37" t="n">
-        <v>618830.728834767</v>
+        <v>618830.728834432</v>
       </c>
       <c r="C37" t="n">
-        <v>61.8830728834767</v>
+        <v>61.8830728834432</v>
       </c>
     </row>
     <row r="38">
@@ -1484,10 +1484,10 @@
         <v>11</v>
       </c>
       <c r="B38" t="n">
-        <v>443918.182565187</v>
+        <v>443918.182565253</v>
       </c>
       <c r="C38" t="n">
-        <v>44.3918182565187</v>
+        <v>44.3918182565253</v>
       </c>
     </row>
     <row r="39">
@@ -1495,10 +1495,10 @@
         <v>56</v>
       </c>
       <c r="B39" t="n">
-        <v>447075.477303017</v>
+        <v>447075.477303055</v>
       </c>
       <c r="C39" t="n">
-        <v>44.7075477303017</v>
+        <v>44.7075477303055</v>
       </c>
     </row>
     <row r="40">
@@ -1506,10 +1506,10 @@
         <v>57</v>
       </c>
       <c r="B40" t="n">
-        <v>243698.473039501</v>
+        <v>243698.473039615</v>
       </c>
       <c r="C40" t="n">
-        <v>24.3698473039501</v>
+        <v>24.3698473039615</v>
       </c>
     </row>
     <row r="41">
@@ -1517,10 +1517,10 @@
         <v>58</v>
       </c>
       <c r="B41" t="n">
-        <v>558928.423531906</v>
+        <v>558928.423531672</v>
       </c>
       <c r="C41" t="n">
-        <v>55.8928423531906</v>
+        <v>55.8928423531672</v>
       </c>
     </row>
     <row r="42">
@@ -1528,10 +1528,10 @@
         <v>12</v>
       </c>
       <c r="B42" t="n">
-        <v>434581.342443</v>
+        <v>434581.342443047</v>
       </c>
       <c r="C42" t="n">
-        <v>43.4581342443</v>
+        <v>43.4581342443047</v>
       </c>
     </row>
     <row r="43">
@@ -1539,10 +1539,10 @@
         <v>59</v>
       </c>
       <c r="B43" t="n">
-        <v>430656.155081458</v>
+        <v>430656.155081479</v>
       </c>
       <c r="C43" t="n">
-        <v>43.0656155081458</v>
+        <v>43.0656155081479</v>
       </c>
     </row>
     <row r="44">
@@ -1550,10 +1550,10 @@
         <v>60</v>
       </c>
       <c r="B44" t="n">
-        <v>330749.82758449</v>
+        <v>330749.82758454</v>
       </c>
       <c r="C44" t="n">
-        <v>33.074982758449</v>
+        <v>33.074982758454</v>
       </c>
     </row>
     <row r="45">
@@ -1561,10 +1561,10 @@
         <v>61</v>
       </c>
       <c r="B45" t="n">
-        <v>502503.564584814</v>
+        <v>502503.56458468</v>
       </c>
       <c r="C45" t="n">
-        <v>50.2503564584814</v>
+        <v>50.250356458468</v>
       </c>
     </row>
     <row r="46">
@@ -1572,10 +1572,10 @@
         <v>13</v>
       </c>
       <c r="B46" t="n">
-        <v>431155.364883267</v>
+        <v>431155.364883295</v>
       </c>
       <c r="C46" t="n">
-        <v>43.1155364883267</v>
+        <v>43.1155364883295</v>
       </c>
     </row>
     <row r="47">
@@ -1583,10 +1583,10 @@
         <v>62</v>
       </c>
       <c r="B47" t="n">
-        <v>423402.711361439</v>
+        <v>423402.711361443</v>
       </c>
       <c r="C47" t="n">
-        <v>42.3402711361439</v>
+        <v>42.3402711361443</v>
       </c>
     </row>
     <row r="48">
@@ -1594,10 +1594,10 @@
         <v>63</v>
       </c>
       <c r="B48" t="n">
-        <v>364891.964911993</v>
+        <v>364891.96491201</v>
       </c>
       <c r="C48" t="n">
-        <v>36.4891964911993</v>
+        <v>36.4891964912009</v>
       </c>
     </row>
     <row r="49">
@@ -1605,10 +1605,10 @@
         <v>64</v>
       </c>
       <c r="B49" t="n">
-        <v>474511.465887906</v>
+        <v>474511.465887826</v>
       </c>
       <c r="C49" t="n">
-        <v>47.4511465887906</v>
+        <v>47.4511465887826</v>
       </c>
     </row>
     <row r="50">
@@ -1616,10 +1616,10 @@
         <v>14</v>
       </c>
       <c r="B50" t="n">
-        <v>431291.541665491</v>
+        <v>431291.541665506</v>
       </c>
       <c r="C50" t="n">
-        <v>43.1291541665491</v>
+        <v>43.1291541665506</v>
       </c>
     </row>
     <row r="51">
@@ -1627,10 +1627,10 @@
         <v>65</v>
       </c>
       <c r="B51" t="n">
-        <v>417753.259487038</v>
+        <v>417753.25948703</v>
       </c>
       <c r="C51" t="n">
-        <v>41.7753259487038</v>
+        <v>41.775325948703</v>
       </c>
     </row>
     <row r="52">
@@ -1638,10 +1638,10 @@
         <v>66</v>
       </c>
       <c r="B52" t="n">
-        <v>400089.107017075</v>
+        <v>400089.10701706</v>
       </c>
       <c r="C52" t="n">
-        <v>40.0089107017075</v>
+        <v>40.008910701706</v>
       </c>
     </row>
     <row r="53">
@@ -1649,10 +1649,10 @@
         <v>67</v>
       </c>
       <c r="B53" t="n">
-        <v>448318.016231539</v>
+        <v>448318.016231512</v>
       </c>
       <c r="C53" t="n">
-        <v>44.8318016231539</v>
+        <v>44.8318016231512</v>
       </c>
     </row>
     <row r="54">
@@ -2144,10 +2144,10 @@
         <v>26</v>
       </c>
       <c r="B98" t="n">
-        <v>1023362.15713526</v>
+        <v>1023362.15678541</v>
       </c>
       <c r="C98" t="n">
-        <v>102.336215713526</v>
+        <v>102.336215678541</v>
       </c>
     </row>
     <row r="99">
@@ -2155,10 +2155,10 @@
         <v>101</v>
       </c>
       <c r="B99" t="n">
-        <v>1058550.36630123</v>
+        <v>1058550.36594136</v>
       </c>
       <c r="C99" t="n">
-        <v>105.855036630123</v>
+        <v>105.855036594136</v>
       </c>
     </row>
     <row r="100">
@@ -2166,10 +2166,10 @@
         <v>102</v>
       </c>
       <c r="B100" t="n">
-        <v>891216.388781259</v>
+        <v>891216.38840692</v>
       </c>
       <c r="C100" t="n">
-        <v>89.1216388781259</v>
+        <v>89.121638840692</v>
       </c>
     </row>
     <row r="101">
@@ -2177,10 +2177,10 @@
         <v>103</v>
       </c>
       <c r="B101" t="n">
-        <v>1177679.557635</v>
+        <v>1177679.5572459</v>
       </c>
       <c r="C101" t="n">
-        <v>117.7679557635</v>
+        <v>117.76795572459</v>
       </c>
     </row>
     <row r="102">
@@ -2188,10 +2188,10 @@
         <v>104</v>
       </c>
       <c r="B102" t="n">
-        <v>1037258.2827634</v>
+        <v>1037258.28234799</v>
       </c>
       <c r="C102" t="n">
-        <v>103.72582827634</v>
+        <v>103.725828234799</v>
       </c>
     </row>
     <row r="103">
@@ -2199,10 +2199,10 @@
         <v>105</v>
       </c>
       <c r="B103" t="n">
-        <v>1090106.49591684</v>
+        <v>1090106.49547691</v>
       </c>
       <c r="C103" t="n">
-        <v>109.010649591684</v>
+        <v>109.010649547691</v>
       </c>
     </row>
     <row r="104">
@@ -2210,10 +2210,10 @@
         <v>106</v>
       </c>
       <c r="B104" t="n">
-        <v>943426.96615325</v>
+        <v>943426.965697953</v>
       </c>
       <c r="C104" t="n">
-        <v>94.342696615325</v>
+        <v>94.3426965697953</v>
       </c>
     </row>
     <row r="105">
@@ -2221,10 +2221,10 @@
         <v>107</v>
       </c>
       <c r="B105" t="n">
-        <v>1209999.3972692</v>
+        <v>1209999.39679714</v>
       </c>
       <c r="C105" t="n">
-        <v>120.99993972692</v>
+        <v>120.999939679714</v>
       </c>
     </row>
     <row r="106">
@@ -2232,10 +2232,10 @@
         <v>108</v>
       </c>
       <c r="B106" t="n">
-        <v>1090300.4198608</v>
+        <v>1090300.41935722</v>
       </c>
       <c r="C106" t="n">
-        <v>109.03004198608</v>
+        <v>109.030041935722</v>
       </c>
     </row>
     <row r="107">
@@ -2243,10 +2243,10 @@
         <v>109</v>
       </c>
       <c r="B107" t="n">
-        <v>1120826.67307071</v>
+        <v>1120826.67254911</v>
       </c>
       <c r="C107" t="n">
-        <v>112.082667307071</v>
+        <v>112.082667254911</v>
       </c>
     </row>
     <row r="108">
@@ -2254,10 +2254,10 @@
         <v>110</v>
       </c>
       <c r="B108" t="n">
-        <v>995844.45703105</v>
+        <v>995844.456495172</v>
       </c>
       <c r="C108" t="n">
-        <v>99.5844457031049</v>
+        <v>99.5844456495172</v>
       </c>
     </row>
     <row r="109">
@@ -2265,10 +2265,10 @@
         <v>111</v>
       </c>
       <c r="B109" t="n">
-        <v>1243068.23534822</v>
+        <v>1243068.23479661</v>
       </c>
       <c r="C109" t="n">
-        <v>124.306823534822</v>
+        <v>124.306823479661</v>
       </c>
     </row>
     <row r="110">
@@ -2276,10 +2276,10 @@
         <v>112</v>
       </c>
       <c r="B110" t="n">
-        <v>1142515.12150166</v>
+        <v>1142515.12090725</v>
       </c>
       <c r="C110" t="n">
-        <v>114.251512150166</v>
+        <v>114.251512090725</v>
       </c>
     </row>
     <row r="111">
@@ -2287,10 +2287,10 @@
         <v>113</v>
       </c>
       <c r="B111" t="n">
-        <v>1150719.15164821</v>
+        <v>1150719.1510433</v>
       </c>
       <c r="C111" t="n">
-        <v>115.071915164821</v>
+        <v>115.07191510433</v>
       </c>
     </row>
     <row r="112">
@@ -2298,10 +2298,10 @@
         <v>114</v>
       </c>
       <c r="B112" t="n">
-        <v>1048445.49971852</v>
+        <v>1048445.49910241</v>
       </c>
       <c r="C112" t="n">
-        <v>104.844549971852</v>
+        <v>104.844549910241</v>
       </c>
     </row>
     <row r="113">
@@ -2309,10 +2309,10 @@
         <v>115</v>
       </c>
       <c r="B113" t="n">
-        <v>1276905.31056381</v>
+        <v>1276905.30993609</v>
       </c>
       <c r="C113" t="n">
-        <v>127.690531056381</v>
+        <v>127.690530993609</v>
       </c>
     </row>
     <row r="114">
@@ -2320,10 +2320,10 @@
         <v>116</v>
       </c>
       <c r="B114" t="n">
-        <v>1193899.61681952</v>
+        <v>1193899.61613164</v>
       </c>
       <c r="C114" t="n">
-        <v>119.389961681952</v>
+        <v>119.389961613164</v>
       </c>
     </row>
     <row r="115">
@@ -2331,10 +2331,10 @@
         <v>117</v>
       </c>
       <c r="B115" t="n">
-        <v>1229087.82598562</v>
+        <v>1229087.82528772</v>
       </c>
       <c r="C115" t="n">
-        <v>122.908782598562</v>
+        <v>122.908782528772</v>
       </c>
     </row>
     <row r="116">
@@ -2342,10 +2342,10 @@
         <v>118</v>
       </c>
       <c r="B116" t="n">
-        <v>1061753.84846564</v>
+        <v>1061753.84775328</v>
       </c>
       <c r="C116" t="n">
-        <v>106.175384846564</v>
+        <v>106.175384775328</v>
       </c>
     </row>
     <row r="117">
@@ -2353,10 +2353,10 @@
         <v>119</v>
       </c>
       <c r="B117" t="n">
-        <v>1348217.01731935</v>
+        <v>1348217.01659223</v>
       </c>
       <c r="C117" t="n">
-        <v>134.821701731935</v>
+        <v>134.821701659223</v>
       </c>
     </row>
     <row r="118">
@@ -2364,10 +2364,10 @@
         <v>120</v>
       </c>
       <c r="B118" t="n">
-        <v>1207795.74244781</v>
+        <v>1207795.74169438</v>
       </c>
       <c r="C118" t="n">
-        <v>120.779574244781</v>
+        <v>120.779574169438</v>
       </c>
     </row>
     <row r="119">
@@ -2375,10 +2375,10 @@
         <v>121</v>
       </c>
       <c r="B119" t="n">
-        <v>1260643.95560121</v>
+        <v>1260643.95482326</v>
       </c>
       <c r="C119" t="n">
-        <v>126.064395560121</v>
+        <v>126.064395482326</v>
       </c>
     </row>
     <row r="120">
@@ -2386,10 +2386,10 @@
         <v>122</v>
       </c>
       <c r="B120" t="n">
-        <v>1113964.42583785</v>
+        <v>1113964.42504453</v>
       </c>
       <c r="C120" t="n">
-        <v>111.396442583785</v>
+        <v>111.396442504453</v>
       </c>
     </row>
     <row r="121">
@@ -2397,10 +2397,10 @@
         <v>123</v>
       </c>
       <c r="B121" t="n">
-        <v>1380536.85695371</v>
+        <v>1380536.85614363</v>
       </c>
       <c r="C121" t="n">
-        <v>138.053685695371</v>
+        <v>138.053685614363</v>
       </c>
     </row>
     <row r="122">
@@ -2408,10 +2408,10 @@
         <v>124</v>
       </c>
       <c r="B122" t="n">
-        <v>1260837.87954513</v>
+        <v>1260837.87870353</v>
       </c>
       <c r="C122" t="n">
-        <v>126.083787954513</v>
+        <v>126.083787870353</v>
       </c>
     </row>
     <row r="123">
@@ -2419,10 +2419,10 @@
         <v>125</v>
       </c>
       <c r="B123" t="n">
-        <v>1291364.13275511</v>
+        <v>1291364.13189548</v>
       </c>
       <c r="C123" t="n">
-        <v>129.136413275511</v>
+        <v>129.136413189548</v>
       </c>
     </row>
     <row r="124">
@@ -2430,10 +2430,10 @@
         <v>126</v>
       </c>
       <c r="B124" t="n">
-        <v>1166381.91671573</v>
+        <v>1166381.91584184</v>
       </c>
       <c r="C124" t="n">
-        <v>116.638191671573</v>
+        <v>116.638191584184</v>
       </c>
     </row>
     <row r="125">
@@ -2441,10 +2441,10 @@
         <v>127</v>
       </c>
       <c r="B125" t="n">
-        <v>1413605.69503267</v>
+        <v>1413605.69414305</v>
       </c>
       <c r="C125" t="n">
-        <v>141.360569503267</v>
+        <v>141.360569414305</v>
       </c>
     </row>
     <row r="126">
@@ -2452,10 +2452,10 @@
         <v>128</v>
       </c>
       <c r="B126" t="n">
-        <v>1313052.58118608</v>
+        <v>1313052.58025365</v>
       </c>
       <c r="C126" t="n">
-        <v>131.305258118608</v>
+        <v>131.305258025365</v>
       </c>
     </row>
     <row r="127">
@@ -2463,10 +2463,10 @@
         <v>129</v>
       </c>
       <c r="B127" t="n">
-        <v>1321256.61133254</v>
+        <v>1321256.61038962</v>
       </c>
       <c r="C127" t="n">
-        <v>132.125661133254</v>
+        <v>132.125661038962</v>
       </c>
     </row>
     <row r="128">
@@ -2474,10 +2474,10 @@
         <v>130</v>
       </c>
       <c r="B128" t="n">
-        <v>1218982.95940297</v>
+        <v>1218982.95844884</v>
       </c>
       <c r="C128" t="n">
-        <v>121.898295940297</v>
+        <v>121.898295844884</v>
       </c>
     </row>
     <row r="129">
@@ -2485,10 +2485,10 @@
         <v>131</v>
       </c>
       <c r="B129" t="n">
-        <v>1447442.77024813</v>
+        <v>1447442.76928239</v>
       </c>
       <c r="C129" t="n">
-        <v>144.744277024813</v>
+        <v>144.744276928239</v>
       </c>
     </row>
     <row r="130">
@@ -2496,10 +2496,10 @@
         <v>132</v>
       </c>
       <c r="B130" t="n">
-        <v>1364437.07650392</v>
+        <v>1364437.07547803</v>
       </c>
       <c r="C130" t="n">
-        <v>136.443707650392</v>
+        <v>136.443707547803</v>
       </c>
     </row>
     <row r="131">
@@ -2507,10 +2507,10 @@
         <v>133</v>
       </c>
       <c r="B131" t="n">
-        <v>1399625.28567002</v>
+        <v>1399625.28463411</v>
       </c>
       <c r="C131" t="n">
-        <v>139.962528567002</v>
+        <v>139.962528463411</v>
       </c>
     </row>
     <row r="132">
@@ -2518,10 +2518,10 @@
         <v>134</v>
       </c>
       <c r="B132" t="n">
-        <v>1232291.30815012</v>
+        <v>1232291.30709974</v>
       </c>
       <c r="C132" t="n">
-        <v>123.229130815012</v>
+        <v>123.229130709974</v>
       </c>
     </row>
     <row r="133">
@@ -2529,10 +2529,10 @@
         <v>135</v>
       </c>
       <c r="B133" t="n">
-        <v>1518754.4770038</v>
+        <v>1518754.47593865</v>
       </c>
       <c r="C133" t="n">
-        <v>151.87544770038</v>
+        <v>151.875447593865</v>
       </c>
     </row>
     <row r="134">
@@ -2540,10 +2540,10 @@
         <v>136</v>
       </c>
       <c r="B134" t="n">
-        <v>1378333.20213207</v>
+        <v>1378333.20104062</v>
       </c>
       <c r="C134" t="n">
-        <v>137.833320213207</v>
+        <v>137.833320104062</v>
       </c>
     </row>
     <row r="135">
@@ -2551,10 +2551,10 @@
         <v>137</v>
       </c>
       <c r="B135" t="n">
-        <v>1431181.41528564</v>
+        <v>1431181.41416967</v>
       </c>
       <c r="C135" t="n">
-        <v>143.118141528564</v>
+        <v>143.118141416967</v>
       </c>
     </row>
     <row r="136">
@@ -2562,10 +2562,10 @@
         <v>138</v>
       </c>
       <c r="B136" t="n">
-        <v>1284501.88552217</v>
+        <v>1284501.88439084</v>
       </c>
       <c r="C136" t="n">
-        <v>128.450188552217</v>
+        <v>128.450188439084</v>
       </c>
     </row>
     <row r="137">
@@ -2573,10 +2573,10 @@
         <v>139</v>
       </c>
       <c r="B137" t="n">
-        <v>1551074.31663807</v>
+        <v>1551074.31548997</v>
       </c>
       <c r="C137" t="n">
-        <v>155.107431663807</v>
+        <v>155.107431548997</v>
       </c>
     </row>
   </sheetData>
@@ -2618,7 +2618,7 @@
         <v>101.165037376644</v>
       </c>
       <c r="C2" t="n">
-        <v>42.4772054748055</v>
+        <v>42.4772054748042</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -2629,16 +2629,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>58.34730383431</v>
+        <v>58.3473038343102</v>
       </c>
       <c r="C3" t="n">
-        <v>42.4717902108524</v>
+        <v>42.4717902108511</v>
       </c>
       <c r="D3" t="n">
-        <v>-42.324635716706</v>
+        <v>-42.3246357167058</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0127486351624073</v>
+        <v>-0.0127486351623407</v>
       </c>
       <c r="F3" t="s">
         <v>145</v>
@@ -2649,16 +2649,16 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>60.1010872013662</v>
+        <v>60.1010872013666</v>
       </c>
       <c r="C4" t="n">
-        <v>42.4652060451601</v>
+        <v>42.4652060451589</v>
       </c>
       <c r="D4" t="n">
-        <v>3.00576590828681</v>
+        <v>3.00576590828703</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.015502444468618</v>
+        <v>-0.0155024444685403</v>
       </c>
       <c r="F4" t="s">
         <v>146</v>
@@ -2669,16 +2669,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>94.6648545879052</v>
+        <v>94.6648545879056</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4545576914791</v>
+        <v>42.4545576914779</v>
       </c>
       <c r="D5" t="n">
-        <v>57.509387926269</v>
+        <v>57.5093879262688</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0250754786629614</v>
+        <v>-0.0250754786628282</v>
       </c>
       <c r="F5" t="s">
         <v>146</v>
@@ -2692,13 +2692,13 @@
         <v>129.252044484291</v>
       </c>
       <c r="C6" t="n">
-        <v>42.2989805282577</v>
+        <v>42.2989805282576</v>
       </c>
       <c r="D6" t="n">
-        <v>36.5364633442373</v>
+        <v>36.5364633442369</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.366455739221005</v>
+        <v>-0.366455739218585</v>
       </c>
       <c r="F6" t="s">
         <v>146</v>
@@ -2712,13 +2712,13 @@
         <v>257.466432309015</v>
       </c>
       <c r="C7" t="n">
-        <v>42.2636224119164</v>
+        <v>42.2636224119163</v>
       </c>
       <c r="D7" t="n">
-        <v>99.1971835620037</v>
+        <v>99.1971835620036</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0835909421451175</v>
+        <v>-0.0835909421448955</v>
       </c>
       <c r="F7" t="s">
         <v>146</v>
@@ -2752,13 +2752,13 @@
         <v>350.222365072351</v>
       </c>
       <c r="C9" t="n">
-        <v>42.1617145383959</v>
+        <v>42.1617145383963</v>
       </c>
       <c r="D9" t="n">
-        <v>-12.744964002618</v>
+        <v>-12.7449640026181</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.340890888781609</v>
+        <v>-0.34089088878051</v>
       </c>
       <c r="F9" t="s">
         <v>145</v>
@@ -2772,13 +2772,13 @@
         <v>318.316550344891</v>
       </c>
       <c r="C10" t="n">
-        <v>42.1148448783313</v>
+        <v>42.1148448783309</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.11015911872697</v>
+        <v>-9.11015911872699</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.111166399606233</v>
+        <v>-0.111166399608209</v>
       </c>
       <c r="F10" t="s">
         <v>145</v>
@@ -2792,13 +2792,13 @@
         <v>269.683670445038</v>
       </c>
       <c r="C11" t="n">
-        <v>42.3405139109903</v>
+        <v>42.3405139109899</v>
       </c>
       <c r="D11" t="n">
         <v>-15.2781499570663</v>
       </c>
       <c r="E11" t="n">
-        <v>0.535842013216392</v>
+        <v>0.535842013216437</v>
       </c>
       <c r="F11" t="s">
         <v>146</v>
@@ -2812,13 +2812,13 @@
         <v>236.574897953766</v>
       </c>
       <c r="C12" t="n">
-        <v>42.462272242344</v>
+        <v>42.4622722423436</v>
       </c>
       <c r="D12" t="n">
         <v>-12.2768918253876</v>
       </c>
       <c r="E12" t="n">
-        <v>0.287569328066528</v>
+        <v>0.287569328066506</v>
       </c>
       <c r="F12" t="s">
         <v>146</v>
@@ -2832,13 +2832,13 @@
         <v>304.316723508352</v>
       </c>
       <c r="C13" t="n">
-        <v>42.3490376761151</v>
+        <v>42.3490376761143</v>
       </c>
       <c r="D13" t="n">
         <v>28.6344097114754</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.26667100051232</v>
+        <v>-0.266671000513174</v>
       </c>
       <c r="F13" t="s">
         <v>146</v>
@@ -2852,13 +2852,13 @@
         <v>360.611983899455</v>
       </c>
       <c r="C14" t="n">
-        <v>42.4362981100286</v>
+        <v>42.4362981100277</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4989046090191</v>
+        <v>18.4989046090192</v>
       </c>
       <c r="E14" t="n">
-        <v>0.206050570926331</v>
+        <v>0.206050570926108</v>
       </c>
       <c r="F14" t="s">
         <v>145</v>
@@ -2869,7 +2869,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>430.289828585279</v>
+        <v>430.28982858528</v>
       </c>
       <c r="C15" t="n">
         <v>42.8058015083304</v>
@@ -2878,7 +2878,7 @@
         <v>19.3221101341025</v>
       </c>
       <c r="E15" t="n">
-        <v>0.870724862342565</v>
+        <v>0.87072486234463</v>
       </c>
       <c r="F15" t="s">
         <v>145</v>
@@ -2915,7 +2915,7 @@
         <v>58.133357275209</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3038173924065</v>
+        <v>2.30381739240648</v>
       </c>
       <c r="E17" t="n">
         <v>9.97112536493081</v>
@@ -2955,7 +2955,7 @@
         <v>71.3263883378685</v>
       </c>
       <c r="D19" t="n">
-        <v>9.71468116310366</v>
+        <v>9.71468116310361</v>
       </c>
       <c r="E19" t="n">
         <v>7.28519677361497</v>
@@ -2975,7 +2975,7 @@
         <v>96.0637570530051</v>
       </c>
       <c r="D20" t="n">
-        <v>6.37649795897119</v>
+        <v>6.37649795897122</v>
       </c>
       <c r="E20" t="n">
         <v>34.6819308976607</v>
@@ -3035,7 +3035,7 @@
         <v>93.6898032816772</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.6305437472242</v>
+        <v>-18.6305437472241</v>
       </c>
       <c r="E23" t="n">
         <v>-6.95695094593462</v>
@@ -3075,7 +3075,7 @@
         <v>86.7319028330548</v>
       </c>
       <c r="D25" t="n">
-        <v>7.34506652154054</v>
+        <v>7.34506652154057</v>
       </c>
       <c r="E25" t="n">
         <v>-5.05278577990997</v>
@@ -3092,13 +3092,13 @@
         <v>674.560615938682</v>
       </c>
       <c r="C26" t="n">
-        <v>103.770211746319</v>
+        <v>103.77021170949</v>
       </c>
       <c r="D26" t="n">
         <v>-12.1007480974727</v>
       </c>
       <c r="E26" t="n">
-        <v>19.6448000755388</v>
+        <v>19.6448000330754</v>
       </c>
       <c r="F26" t="s">
         <v>146</v>
@@ -3109,16 +3109,16 @@
         <v>104</v>
       </c>
       <c r="B27" t="n">
-        <v>674.246840582289</v>
+        <v>674.246841013046</v>
       </c>
       <c r="C27" t="n">
-        <v>107.019778552567</v>
+        <v>107.019778508</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0465155167643116</v>
+        <v>-0.0465154529069145</v>
       </c>
       <c r="E27" t="n">
-        <v>3.13150253002508</v>
+        <v>3.13150252367922</v>
       </c>
       <c r="F27" t="s">
         <v>146</v>
@@ -3129,16 +3129,16 @@
         <v>108</v>
       </c>
       <c r="B28" t="n">
-        <v>677.666929055423</v>
+        <v>677.666929483074</v>
       </c>
       <c r="C28" t="n">
-        <v>111.250994632769</v>
+        <v>111.250994579953</v>
       </c>
       <c r="D28" t="n">
-        <v>0.507245754415386</v>
+        <v>0.507245753630747</v>
       </c>
       <c r="E28" t="n">
-        <v>3.95367672913256</v>
+        <v>3.95367672307119</v>
       </c>
       <c r="F28" t="s">
         <v>145</v>
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="B29" t="n">
-        <v>681.679773571627</v>
+        <v>681.679773803798</v>
       </c>
       <c r="C29" t="n">
-        <v>115.464627085805</v>
+        <v>115.464627024726</v>
       </c>
       <c r="D29" t="n">
-        <v>0.592155872472211</v>
+        <v>0.592155843252473</v>
       </c>
       <c r="E29" t="n">
-        <v>3.78750092702054</v>
+        <v>3.78750092139213</v>
       </c>
       <c r="F29" t="s">
         <v>145</v>
@@ -3169,16 +3169,16 @@
         <v>116</v>
       </c>
       <c r="B30" t="n">
-        <v>689.844959301256</v>
+        <v>689.844958912601</v>
       </c>
       <c r="C30" t="n">
-        <v>120.823957714753</v>
+        <v>120.823957644122</v>
       </c>
       <c r="D30" t="n">
-        <v>1.19780372635208</v>
+        <v>1.19780363487105</v>
       </c>
       <c r="E30" t="n">
-        <v>4.64153461039221</v>
+        <v>4.64153460457446</v>
       </c>
       <c r="F30" t="s">
         <v>145</v>
@@ -3189,16 +3189,16 @@
         <v>120</v>
       </c>
       <c r="B31" t="n">
-        <v>692.039525368949</v>
+        <v>692.039524666275</v>
       </c>
       <c r="C31" t="n">
-        <v>124.073524521015</v>
+        <v>124.073524442645</v>
       </c>
       <c r="D31" t="n">
-        <v>0.318124534810837</v>
+        <v>0.318124489469884</v>
       </c>
       <c r="E31" t="n">
-        <v>2.6895053495378</v>
+        <v>2.68950534470533</v>
       </c>
       <c r="F31" t="s">
         <v>145</v>
@@ -3209,16 +3209,16 @@
         <v>124</v>
       </c>
       <c r="B32" t="n">
-        <v>697.800323740355</v>
+        <v>697.800322374177</v>
       </c>
       <c r="C32" t="n">
-        <v>128.304740601216</v>
+        <v>128.304740514597</v>
       </c>
       <c r="D32" t="n">
-        <v>0.832437766951988</v>
+        <v>0.832437671920605</v>
       </c>
       <c r="E32" t="n">
-        <v>3.41024896047399</v>
+        <v>3.41024895597961</v>
       </c>
       <c r="F32" t="s">
         <v>145</v>
@@ -3229,16 +3229,16 @@
         <v>128</v>
       </c>
       <c r="B33" t="n">
-        <v>703.997449381648</v>
+        <v>703.997447236016</v>
       </c>
       <c r="C33" t="n">
-        <v>132.518373054243</v>
+        <v>132.518372959363</v>
       </c>
       <c r="D33" t="n">
-        <v>0.888094406158335</v>
+        <v>0.888094296195541</v>
       </c>
       <c r="E33" t="n">
-        <v>3.28408165846625</v>
+        <v>3.2840816542439</v>
       </c>
       <c r="F33" t="s">
         <v>145</v>
@@ -3249,16 +3249,16 @@
         <v>132</v>
       </c>
       <c r="B34" t="n">
-        <v>714.200941540062</v>
+        <v>714.20093825879</v>
       </c>
       <c r="C34" t="n">
-        <v>137.877703683196</v>
+        <v>137.877703578763</v>
       </c>
       <c r="D34" t="n">
-        <v>1.44936493269621</v>
+        <v>1.44936477580049</v>
       </c>
       <c r="E34" t="n">
-        <v>4.04421704359408</v>
+        <v>4.04421703928128</v>
       </c>
       <c r="F34" t="s">
         <v>145</v>
@@ -3269,16 +3269,16 @@
         <v>136</v>
       </c>
       <c r="B35" t="n">
-        <v>718.297594774888</v>
+        <v>718.297590727308</v>
       </c>
       <c r="C35" t="n">
-        <v>141.127270489449</v>
+        <v>141.127270377277</v>
       </c>
       <c r="D35" t="n">
-        <v>0.573599528725444</v>
+        <v>0.573599424064875</v>
       </c>
       <c r="E35" t="n">
-        <v>2.35684720549085</v>
+        <v>2.35684720166347</v>
       </c>
       <c r="F35" t="s">
         <v>145</v>
@@ -3323,16 +3323,16 @@
         <v>58.3473038343098</v>
       </c>
       <c r="C2" t="n">
-        <v>155.742016221748</v>
+        <v>155.742015536094</v>
       </c>
       <c r="D2" t="n">
-        <v>-97.3947123874381</v>
+        <v>-97.3947117017838</v>
       </c>
       <c r="E2" t="n">
-        <v>42.4717902108524</v>
+        <v>42.4717902108511</v>
       </c>
       <c r="F2" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
     </row>
     <row r="3">
@@ -3343,16 +3343,16 @@
         <v>60.101087201366</v>
       </c>
       <c r="C3" t="n">
-        <v>76.4322657663486</v>
+        <v>76.4322652008593</v>
       </c>
       <c r="D3" t="n">
-        <v>-16.3311785649827</v>
+        <v>-16.3311779994933</v>
       </c>
       <c r="E3" t="n">
-        <v>42.4652060451601</v>
+        <v>42.4652060451589</v>
       </c>
       <c r="F3" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
     </row>
     <row r="4">
@@ -3363,16 +3363,16 @@
         <v>94.6648545879048</v>
       </c>
       <c r="C4" t="n">
-        <v>78.0549353838344</v>
+        <v>78.0549348248787</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6099192040704</v>
+        <v>16.6099197630261</v>
       </c>
       <c r="E4" t="n">
-        <v>42.4545576914791</v>
+        <v>42.4545576914779</v>
       </c>
       <c r="F4" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
     </row>
     <row r="5">
@@ -3383,16 +3383,16 @@
         <v>129.25204448429</v>
       </c>
       <c r="C5" t="n">
-        <v>109.858552008284</v>
+        <v>109.858551589212</v>
       </c>
       <c r="D5" t="n">
-        <v>19.3934924760064</v>
+        <v>19.3934928950776</v>
       </c>
       <c r="E5" t="n">
-        <v>42.2989805282577</v>
+        <v>42.2989805282576</v>
       </c>
       <c r="F5" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
     </row>
     <row r="6">
@@ -3403,16 +3403,16 @@
         <v>257.466432309015</v>
       </c>
       <c r="C6" t="n">
-        <v>142.475237495913</v>
+        <v>142.475237163069</v>
       </c>
       <c r="D6" t="n">
-        <v>114.991194813101</v>
+        <v>114.991195145946</v>
       </c>
       <c r="E6" t="n">
-        <v>42.2636224119164</v>
+        <v>42.2636224119163</v>
       </c>
       <c r="F6" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
     </row>
     <row r="7">
@@ -3423,16 +3423,16 @@
         <v>401.377824292983</v>
       </c>
       <c r="C7" t="n">
-        <v>262.357303042798</v>
+        <v>262.357303095958</v>
       </c>
       <c r="D7" t="n">
-        <v>139.020521250184</v>
+        <v>139.020521197024</v>
       </c>
       <c r="E7" t="n">
         <v>42.3059316046503</v>
       </c>
       <c r="F7" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
     </row>
     <row r="8">
@@ -3443,16 +3443,16 @@
         <v>350.222365072351</v>
       </c>
       <c r="C8" t="n">
-        <v>396.085538552166</v>
+        <v>396.08553909568</v>
       </c>
       <c r="D8" t="n">
-        <v>-45.863173479815</v>
+        <v>-45.8631740233296</v>
       </c>
       <c r="E8" t="n">
-        <v>42.1617145383959</v>
+        <v>42.1617145383963</v>
       </c>
       <c r="F8" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
     </row>
     <row r="9">
@@ -3463,16 +3463,16 @@
         <v>318.31655034489</v>
       </c>
       <c r="C9" t="n">
-        <v>348.619253768556</v>
+        <v>348.61925413418</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.3027034236657</v>
+        <v>-30.3027037892898</v>
       </c>
       <c r="E9" t="n">
-        <v>42.1148448783313</v>
+        <v>42.1148448783309</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
     </row>
     <row r="10">
@@ -3483,16 +3483,16 @@
         <v>269.683670445038</v>
       </c>
       <c r="C10" t="n">
-        <v>319.67934512692</v>
+        <v>319.679345334844</v>
       </c>
       <c r="D10" t="n">
-        <v>-49.995674681882</v>
+        <v>-49.9956748898066</v>
       </c>
       <c r="E10" t="n">
-        <v>42.3405139109903</v>
+        <v>42.3405139109899</v>
       </c>
       <c r="F10" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
     </row>
     <row r="11">
@@ -3503,16 +3503,16 @@
         <v>236.574897953765</v>
       </c>
       <c r="C11" t="n">
-        <v>274.020324510585</v>
+        <v>274.020324583041</v>
       </c>
       <c r="D11" t="n">
-        <v>-37.4454265568199</v>
+        <v>-37.4454266292758</v>
       </c>
       <c r="E11" t="n">
-        <v>42.462272242344</v>
+        <v>42.4622722423436</v>
       </c>
       <c r="F11" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
     </row>
     <row r="12">
@@ -3523,16 +3523,16 @@
         <v>304.316723508352</v>
       </c>
       <c r="C12" t="n">
-        <v>242.420821290097</v>
+        <v>242.420821306542</v>
       </c>
       <c r="D12" t="n">
-        <v>61.8959022182555</v>
+        <v>61.8959022018096</v>
       </c>
       <c r="E12" t="n">
-        <v>42.3490376761151</v>
+        <v>42.3490376761143</v>
       </c>
       <c r="F12" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
     </row>
     <row r="13">
@@ -3543,16 +3543,16 @@
         <v>360.611983899455</v>
       </c>
       <c r="C13" t="n">
-        <v>306.234584161626</v>
+        <v>306.234584349886</v>
       </c>
       <c r="D13" t="n">
-        <v>54.3773997378284</v>
+        <v>54.3773995495691</v>
       </c>
       <c r="E13" t="n">
-        <v>42.4362981100286</v>
+        <v>42.4362981100277</v>
       </c>
       <c r="F13" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
     </row>
     <row r="14">
@@ -3563,16 +3563,16 @@
         <v>430.289828585279</v>
       </c>
       <c r="C14" t="n">
-        <v>359.661155071036</v>
+        <v>359.66115537275</v>
       </c>
       <c r="D14" t="n">
-        <v>70.6286735142429</v>
+        <v>70.6286732125293</v>
       </c>
       <c r="E14" t="n">
         <v>42.8058015083304</v>
       </c>
       <c r="F14" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
     </row>
     <row r="15">
@@ -3583,16 +3583,16 @@
         <v>566.541738110914</v>
       </c>
       <c r="C15" t="n">
-        <v>454.762688727166</v>
+        <v>454.762687147777</v>
       </c>
       <c r="D15" t="n">
-        <v>111.779049383748</v>
+        <v>111.779050963137</v>
       </c>
       <c r="E15" t="n">
         <v>52.8623828139412</v>
       </c>
       <c r="F15" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
     </row>
     <row r="16">
@@ -3603,16 +3603,16 @@
         <v>579.593825208755</v>
       </c>
       <c r="C16" t="n">
-        <v>569.171219819474</v>
+        <v>569.171219457365</v>
       </c>
       <c r="D16" t="n">
-        <v>10.422605389281</v>
+        <v>10.4226057513901</v>
       </c>
       <c r="E16" t="n">
         <v>58.133357275209</v>
       </c>
       <c r="F16" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
     </row>
     <row r="17">
@@ -3623,16 +3623,16 @@
         <v>637.096554399705</v>
       </c>
       <c r="C17" t="n">
-        <v>591.976913422973</v>
+        <v>591.976912310196</v>
       </c>
       <c r="D17" t="n">
-        <v>45.1196409767326</v>
+        <v>45.1196420895098</v>
       </c>
       <c r="E17" t="n">
         <v>66.4829729383598</v>
       </c>
       <c r="F17" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
     </row>
     <row r="18">
@@ -3643,16 +3643,16 @@
         <v>698.988453360756</v>
       </c>
       <c r="C18" t="n">
-        <v>636.506526350527</v>
+        <v>636.506525973244</v>
       </c>
       <c r="D18" t="n">
-        <v>62.481927010229</v>
+        <v>62.4819273875117</v>
       </c>
       <c r="E18" t="n">
         <v>71.3263883378685</v>
       </c>
       <c r="F18" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
     </row>
     <row r="19">
@@ -3663,16 +3663,16 @@
         <v>743.559437822749</v>
       </c>
       <c r="C19" t="n">
-        <v>756.880005844979</v>
+        <v>756.880001251466</v>
       </c>
       <c r="D19" t="n">
-        <v>-13.32056802223</v>
+        <v>-13.3205634287168</v>
       </c>
       <c r="E19" t="n">
         <v>96.0637570530051</v>
       </c>
       <c r="F19" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
     </row>
     <row r="20">
@@ -3683,16 +3683,16 @@
         <v>742.49</v>
       </c>
       <c r="C20" t="n">
-        <v>739.167882607774</v>
+        <v>739.167882046324</v>
       </c>
       <c r="D20" t="n">
-        <v>3.32211739222626</v>
+        <v>3.32211795367564</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
     </row>
     <row r="21">
@@ -3703,16 +3703,16 @@
         <v>842.728</v>
       </c>
       <c r="C21" t="n">
-        <v>728.946122096568</v>
+        <v>728.946122136279</v>
       </c>
       <c r="D21" t="n">
-        <v>113.781877903432</v>
+        <v>113.781877863721</v>
       </c>
       <c r="E21" t="n">
         <v>100.695112890417</v>
       </c>
       <c r="F21" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
     </row>
     <row r="22">
@@ -3723,16 +3723,16 @@
         <v>685.723191289893</v>
       </c>
       <c r="C22" t="n">
-        <v>798.782167056885</v>
+        <v>798.7821690559</v>
       </c>
       <c r="D22" t="n">
-        <v>-113.058975766993</v>
+        <v>-113.058977766007</v>
       </c>
       <c r="E22" t="n">
         <v>93.6898032816772</v>
       </c>
       <c r="F22" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
     </row>
     <row r="23">
@@ -3743,16 +3743,16 @@
         <v>714.913853878923</v>
       </c>
       <c r="C23" t="n">
-        <v>665.258777125421</v>
+        <v>665.258777794945</v>
       </c>
       <c r="D23" t="n">
-        <v>49.6550767535016</v>
+        <v>49.6550760839779</v>
       </c>
       <c r="E23" t="n">
         <v>91.347496127699</v>
       </c>
       <c r="F23" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
     </row>
     <row r="24">
@@ -3763,16 +3763,16 @@
         <v>767.424752018039</v>
       </c>
       <c r="C24" t="n">
-        <v>684.974001603633</v>
+        <v>684.974002911779</v>
       </c>
       <c r="D24" t="n">
-        <v>82.4507504144055</v>
+        <v>82.45074910626</v>
       </c>
       <c r="E24" t="n">
         <v>86.7319028330548</v>
       </c>
       <c r="F24" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
     </row>
     <row r="25">
@@ -3783,16 +3783,16 @@
         <v>674.560615938681</v>
       </c>
       <c r="C25" t="n">
-        <v>800.086837681915</v>
+        <v>800.086834478748</v>
       </c>
       <c r="D25" t="n">
-        <v>-125.526221743234</v>
+        <v>-125.526218540067</v>
       </c>
       <c r="E25" t="n">
-        <v>103.770211746319</v>
+        <v>103.77021170949</v>
       </c>
       <c r="F25" t="n">
-        <v>155.292131893717</v>
+        <v>155.292146652219</v>
       </c>
     </row>
   </sheetData>
@@ -3846,34 +3846,34 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>9.43429602010574</v>
+        <v>9.43429602011821</v>
       </c>
       <c r="C2" t="n">
-        <v>-186.115116197947</v>
+        <v>-186.115112664519</v>
       </c>
       <c r="D2" t="n">
-        <v>35.2695779968113</v>
+        <v>35.2695780808856</v>
       </c>
       <c r="E2" t="n">
-        <v>155.742016221748</v>
+        <v>155.742015536094</v>
       </c>
       <c r="F2" t="n">
         <v>58.3473038343098</v>
       </c>
       <c r="G2" t="n">
-        <v>-97.3947123874381</v>
+        <v>-97.3947117017838</v>
       </c>
       <c r="H2" t="n">
-        <v>-28.6879914600948</v>
+        <v>-28.6879914765649</v>
       </c>
       <c r="I2" t="n">
-        <v>6.58158653671646</v>
+        <v>6.58158660432072</v>
       </c>
       <c r="J2" t="n">
-        <v>58.34730383431</v>
+        <v>58.3473038343102</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000000000000184741111297626</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="3">
@@ -3884,31 +3884,31 @@
         <v>12.1937909319798</v>
       </c>
       <c r="C3" t="n">
-        <v>-186.115116197947</v>
+        <v>-186.115112664519</v>
       </c>
       <c r="D3" t="n">
-        <v>43.8161003705038</v>
+        <v>43.8160998590024</v>
       </c>
       <c r="E3" t="n">
-        <v>155.742016221748</v>
+        <v>155.742015536094</v>
       </c>
       <c r="F3" t="n">
         <v>58.3473038343098</v>
       </c>
       <c r="G3" t="n">
-        <v>-97.3947123874381</v>
+        <v>-97.3947117017838</v>
       </c>
       <c r="H3" t="n">
-        <v>-26.9522661148007</v>
+        <v>-26.9522660561173</v>
       </c>
       <c r="I3" t="n">
-        <v>16.8638342557031</v>
+        <v>16.8638338028851</v>
       </c>
       <c r="J3" t="n">
-        <v>58.34730383431</v>
+        <v>58.3473038343102</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000000000000184741111297626</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="4">
@@ -3916,34 +3916,34 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>3.45889465139056</v>
+        <v>3.45889465139194</v>
       </c>
       <c r="C4" t="n">
-        <v>-186.115116197947</v>
+        <v>-186.115112664519</v>
       </c>
       <c r="D4" t="n">
-        <v>16.7629660549779</v>
+        <v>16.7629674285917</v>
       </c>
       <c r="E4" t="n">
-        <v>155.742016221748</v>
+        <v>155.742015536094</v>
       </c>
       <c r="F4" t="n">
         <v>58.3473038343098</v>
       </c>
       <c r="G4" t="n">
-        <v>-97.3947123874381</v>
+        <v>-97.3947117017838</v>
       </c>
       <c r="H4" t="n">
-        <v>-23.4808154242124</v>
+        <v>-23.480815215222</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.71784936923454</v>
+        <v>-6.7178477866303</v>
       </c>
       <c r="J4" t="n">
-        <v>58.34730383431</v>
+        <v>58.3473038343102</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000000000000184741111297626</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="5">
@@ -3951,34 +3951,34 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>17.3848086073763</v>
+        <v>17.3848086073612</v>
       </c>
       <c r="C5" t="n">
-        <v>-186.115116197947</v>
+        <v>-186.115112664519</v>
       </c>
       <c r="D5" t="n">
-        <v>59.893371799455</v>
+        <v>59.8933701676138</v>
       </c>
       <c r="E5" t="n">
-        <v>155.742016221748</v>
+        <v>155.742015536094</v>
       </c>
       <c r="F5" t="n">
         <v>58.3473038343098</v>
       </c>
       <c r="G5" t="n">
-        <v>-97.3947123874381</v>
+        <v>-97.3947117017838</v>
       </c>
       <c r="H5" t="n">
-        <v>-18.27363938833</v>
+        <v>-18.2736389538792</v>
       </c>
       <c r="I5" t="n">
-        <v>41.619732411125</v>
+        <v>41.6197312137347</v>
       </c>
       <c r="J5" t="n">
-        <v>58.34730383431</v>
+        <v>58.3473038343102</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000000000000184741111297626</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="6">
@@ -3986,34 +3986,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.45592239729289</v>
+        <v>9.45592239730524</v>
       </c>
       <c r="C6" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
       <c r="D6" t="n">
-        <v>15.5167870020628</v>
+        <v>15.5167862943437</v>
       </c>
       <c r="E6" t="n">
-        <v>76.4425411529435</v>
+        <v>76.4425373202073</v>
       </c>
       <c r="F6" t="n">
         <v>60.101087201366</v>
       </c>
       <c r="G6" t="n">
-        <v>-16.3414539515776</v>
+        <v>-16.3414501188413</v>
       </c>
       <c r="H6" t="n">
-        <v>-11.3307380071534</v>
+        <v>-11.3307372720887</v>
       </c>
       <c r="I6" t="n">
-        <v>4.18604899490934</v>
+        <v>4.18604902225504</v>
       </c>
       <c r="J6" t="n">
-        <v>60.1010872013662</v>
+        <v>60.1010872013666</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000000000000270006239588838</v>
+        <v>0.000000000000611066752753686</v>
       </c>
     </row>
     <row r="7">
@@ -4024,31 +4024,31 @@
         <v>12.1917626444412</v>
       </c>
       <c r="C7" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
       <c r="D7" t="n">
-        <v>23.9900477362969</v>
+        <v>23.9900464381075</v>
       </c>
       <c r="E7" t="n">
-        <v>76.4425411529435</v>
+        <v>76.4425373202073</v>
       </c>
       <c r="F7" t="n">
         <v>60.101087201366</v>
       </c>
       <c r="G7" t="n">
-        <v>-16.3414539515776</v>
+        <v>-16.3414501188413</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.65542764697917</v>
+        <v>-5.65542670242108</v>
       </c>
       <c r="I7" t="n">
-        <v>18.3346200893177</v>
+        <v>18.3346197356864</v>
       </c>
       <c r="J7" t="n">
-        <v>60.1010872013662</v>
+        <v>60.1010872013666</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000000000000270006239588838</v>
+        <v>0.000000000000611066752753686</v>
       </c>
     </row>
     <row r="8">
@@ -4056,34 +4056,34 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>3.46832106816347</v>
+        <v>3.46832106816489</v>
       </c>
       <c r="C8" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.02760983808295</v>
+        <v>-3.02760925362905</v>
       </c>
       <c r="E8" t="n">
-        <v>76.4425411529435</v>
+        <v>76.4425373202073</v>
       </c>
       <c r="F8" t="n">
         <v>60.101087201366</v>
       </c>
       <c r="G8" t="n">
-        <v>-16.3414539515776</v>
+        <v>-16.3414501188413</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.24770830780718</v>
+        <v>-1.24770724487637</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.27531814589013</v>
+        <v>-4.27531649850542</v>
       </c>
       <c r="J8" t="n">
-        <v>60.1010872013662</v>
+        <v>60.1010872013666</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000000000000270006239588838</v>
+        <v>0.000000000000611066752753686</v>
       </c>
     </row>
     <row r="9">
@@ -4091,34 +4091,34 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>17.3491999352625</v>
+        <v>17.3491999352476</v>
       </c>
       <c r="C9" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
       <c r="D9" t="n">
-        <v>39.9633162526668</v>
+        <v>39.9633138413851</v>
       </c>
       <c r="E9" t="n">
-        <v>76.4425411529435</v>
+        <v>76.4425373202073</v>
       </c>
       <c r="F9" t="n">
         <v>60.101087201366</v>
       </c>
       <c r="G9" t="n">
-        <v>-16.3414539515776</v>
+        <v>-16.3414501188413</v>
       </c>
       <c r="H9" t="n">
-        <v>1.89242001036252</v>
+        <v>1.89242110054546</v>
       </c>
       <c r="I9" t="n">
-        <v>41.8557362630293</v>
+        <v>41.8557349419305</v>
       </c>
       <c r="J9" t="n">
-        <v>60.1010872013662</v>
+        <v>60.1010872013666</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000000000000270006239588838</v>
+        <v>0.000000000000611066752753686</v>
       </c>
     </row>
     <row r="10">
@@ -4126,34 +4126,34 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>9.49805318041849</v>
+        <v>9.4980531804306</v>
       </c>
       <c r="C10" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
       <c r="D10" t="n">
-        <v>16.0611736149113</v>
+        <v>16.0611729038865</v>
       </c>
       <c r="E10" t="n">
-        <v>78.0651697065713</v>
+        <v>78.0651658992828</v>
       </c>
       <c r="F10" t="n">
         <v>94.6648545879048</v>
       </c>
       <c r="G10" t="n">
-        <v>16.5996848813335</v>
+        <v>16.599688688622</v>
       </c>
       <c r="H10" t="n">
-        <v>3.76495730752994</v>
+        <v>3.76495833384439</v>
       </c>
       <c r="I10" t="n">
-        <v>19.8261309224413</v>
+        <v>19.8261312377309</v>
       </c>
       <c r="J10" t="n">
-        <v>94.6648545879052</v>
+        <v>94.6648545879056</v>
       </c>
       <c r="K10" t="n">
-        <v>0.000000000000383693077310454</v>
+        <v>0.000000000000810018718766514</v>
       </c>
     </row>
     <row r="11">
@@ -4164,31 +4164,31 @@
         <v>12.1810595075462</v>
       </c>
       <c r="C11" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
       <c r="D11" t="n">
-        <v>24.3708006792289</v>
+        <v>24.3707993891368</v>
       </c>
       <c r="E11" t="n">
-        <v>78.0651697065713</v>
+        <v>78.0651658992828</v>
       </c>
       <c r="F11" t="n">
         <v>94.6648545879048</v>
       </c>
       <c r="G11" t="n">
-        <v>16.5996848813335</v>
+        <v>16.599688688622</v>
       </c>
       <c r="H11" t="n">
-        <v>4.66795779151832</v>
+        <v>4.66795876248848</v>
       </c>
       <c r="I11" t="n">
-        <v>29.0387584707472</v>
+        <v>29.0387581516253</v>
       </c>
       <c r="J11" t="n">
-        <v>94.6648545879052</v>
+        <v>94.6648545879056</v>
       </c>
       <c r="K11" t="n">
-        <v>0.000000000000383693077310454</v>
+        <v>0.000000000000810018718766514</v>
       </c>
     </row>
     <row r="12">
@@ -4196,34 +4196,34 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>3.48224738554993</v>
+        <v>3.48224738555144</v>
       </c>
       <c r="C12" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.57057620292619</v>
+        <v>-2.57057561569012</v>
       </c>
       <c r="E12" t="n">
-        <v>78.0651697065713</v>
+        <v>78.0651658992828</v>
       </c>
       <c r="F12" t="n">
         <v>94.6648545879048</v>
       </c>
       <c r="G12" t="n">
-        <v>16.5996848813335</v>
+        <v>16.599688688622</v>
       </c>
       <c r="H12" t="n">
-        <v>4.60142146232766</v>
+        <v>4.60142238647773</v>
       </c>
       <c r="I12" t="n">
-        <v>2.03084525940147</v>
+        <v>2.03084677078762</v>
       </c>
       <c r="J12" t="n">
-        <v>94.6648545879052</v>
+        <v>94.6648545879056</v>
       </c>
       <c r="K12" t="n">
-        <v>0.000000000000383693077310454</v>
+        <v>0.000000000000810018718766514</v>
       </c>
     </row>
     <row r="13">
@@ -4231,34 +4231,34 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>17.2931976179645</v>
+        <v>17.2931976179497</v>
       </c>
       <c r="C13" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
       <c r="D13" t="n">
-        <v>40.2037716153573</v>
+        <v>40.2037692219496</v>
       </c>
       <c r="E13" t="n">
-        <v>78.0651697065713</v>
+        <v>78.0651658992828</v>
       </c>
       <c r="F13" t="n">
         <v>94.6648545879048</v>
       </c>
       <c r="G13" t="n">
-        <v>16.5996848813335</v>
+        <v>16.599688688622</v>
       </c>
       <c r="H13" t="n">
-        <v>3.56534831995794</v>
+        <v>3.56534920581216</v>
       </c>
       <c r="I13" t="n">
-        <v>43.7691199353152</v>
+        <v>43.7691184277618</v>
       </c>
       <c r="J13" t="n">
-        <v>94.6648545879052</v>
+        <v>94.6648545879056</v>
       </c>
       <c r="K13" t="n">
-        <v>0.000000000000383693077310454</v>
+        <v>0.000000000000810018718766514</v>
       </c>
     </row>
     <row r="14">
@@ -4266,34 +4266,34 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>9.53219834760066</v>
+        <v>9.53219834761259</v>
       </c>
       <c r="C14" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
       <c r="D14" t="n">
-        <v>24.2380904883727</v>
+        <v>24.2380898887619</v>
       </c>
       <c r="E14" t="n">
-        <v>109.867985578236</v>
+        <v>109.86798227966</v>
       </c>
       <c r="F14" t="n">
         <v>129.25204448429</v>
       </c>
       <c r="G14" t="n">
-        <v>19.3840589060543</v>
+        <v>19.3840622046297</v>
       </c>
       <c r="H14" t="n">
-        <v>1.55973836440918</v>
+        <v>1.55973922049174</v>
       </c>
       <c r="I14" t="n">
-        <v>25.7978288527819</v>
+        <v>25.7978291092536</v>
       </c>
       <c r="J14" t="n">
         <v>129.252044484291</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000000000000795807864051312</v>
+        <v>0.000000000000966338120633736</v>
       </c>
     </row>
     <row r="15">
@@ -4301,34 +4301,34 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>12.1448667467561</v>
+        <v>12.1448667467563</v>
       </c>
       <c r="C15" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
       <c r="D15" t="n">
-        <v>32.3298716445326</v>
+        <v>32.3298704810355</v>
       </c>
       <c r="E15" t="n">
-        <v>109.867985578236</v>
+        <v>109.86798227966</v>
       </c>
       <c r="F15" t="n">
         <v>129.25204448429</v>
       </c>
       <c r="G15" t="n">
-        <v>19.3840589060543</v>
+        <v>19.3840622046297</v>
       </c>
       <c r="H15" t="n">
-        <v>2.07200492703151</v>
+        <v>2.07200575862994</v>
       </c>
       <c r="I15" t="n">
-        <v>34.4018765715641</v>
+        <v>34.4018762396655</v>
       </c>
       <c r="J15" t="n">
         <v>129.252044484291</v>
       </c>
       <c r="K15" t="n">
-        <v>0.000000000000795807864051312</v>
+        <v>0.000000000000966338120633736</v>
       </c>
     </row>
     <row r="16">
@@ -4336,34 +4336,34 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>3.44863939509929</v>
+        <v>3.44863939510121</v>
       </c>
       <c r="C16" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
       <c r="D16" t="n">
-        <v>5.39650013953603</v>
+        <v>5.39650085280999</v>
       </c>
       <c r="E16" t="n">
-        <v>109.867985578236</v>
+        <v>109.86798227966</v>
       </c>
       <c r="F16" t="n">
         <v>129.25204448429</v>
       </c>
       <c r="G16" t="n">
-        <v>19.3840589060543</v>
+        <v>19.3840622046297</v>
       </c>
       <c r="H16" t="n">
-        <v>5.10214800782493</v>
+        <v>5.10214882022676</v>
       </c>
       <c r="I16" t="n">
-        <v>10.498648147361</v>
+        <v>10.4986496730368</v>
       </c>
       <c r="J16" t="n">
         <v>129.252044484291</v>
       </c>
       <c r="K16" t="n">
-        <v>0.000000000000795807864051312</v>
+        <v>0.000000000000966338120633736</v>
       </c>
     </row>
     <row r="17">
@@ -4371,34 +4371,34 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>17.1732760388017</v>
+        <v>17.1732760387875</v>
       </c>
       <c r="C17" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
       <c r="D17" t="n">
-        <v>47.9035233057943</v>
+        <v>47.9035210570528</v>
       </c>
       <c r="E17" t="n">
-        <v>109.867985578236</v>
+        <v>109.86798227966</v>
       </c>
       <c r="F17" t="n">
         <v>129.25204448429</v>
       </c>
       <c r="G17" t="n">
-        <v>19.3840589060543</v>
+        <v>19.3840622046297</v>
       </c>
       <c r="H17" t="n">
-        <v>10.6501676067895</v>
+        <v>10.6501684052822</v>
       </c>
       <c r="I17" t="n">
-        <v>58.5536909125837</v>
+        <v>58.553689462335</v>
       </c>
       <c r="J17" t="n">
         <v>129.252044484291</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000000000000795807864051312</v>
+        <v>0.000000000000966338120633736</v>
       </c>
     </row>
     <row r="18">
@@ -4406,34 +4406,34 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>9.94389849690385</v>
+        <v>9.94389849691342</v>
       </c>
       <c r="C18" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
       <c r="D18" t="n">
-        <v>33.6945261969315</v>
+        <v>33.6945256215777</v>
       </c>
       <c r="E18" t="n">
-        <v>142.483859381863</v>
+        <v>142.483856543378</v>
       </c>
       <c r="F18" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="G18" t="n">
-        <v>114.982572927151</v>
+        <v>114.982575765636</v>
       </c>
       <c r="H18" t="n">
-        <v>18.7160637239251</v>
+        <v>18.7160645137963</v>
       </c>
       <c r="I18" t="n">
-        <v>52.4105899208566</v>
+        <v>52.410590135374</v>
       </c>
       <c r="J18" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="K18" t="n">
-        <v>0.000000000000625277607468888</v>
+        <v>0.00000000000085265128291212</v>
       </c>
     </row>
     <row r="19">
@@ -4441,34 +4441,34 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>11.974917971407</v>
+        <v>11.9749179714078</v>
       </c>
       <c r="C19" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
       <c r="D19" t="n">
-        <v>39.9848633544868</v>
+        <v>39.9848623407838</v>
       </c>
       <c r="E19" t="n">
-        <v>142.483859381863</v>
+        <v>142.483856543378</v>
       </c>
       <c r="F19" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="G19" t="n">
-        <v>114.982572927151</v>
+        <v>114.982575765636</v>
       </c>
       <c r="H19" t="n">
-        <v>25.9542539739245</v>
+        <v>25.9542547282471</v>
       </c>
       <c r="I19" t="n">
-        <v>65.9391173284113</v>
+        <v>65.9391170690309</v>
       </c>
       <c r="J19" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="K19" t="n">
-        <v>0.000000000000625277607468888</v>
+        <v>0.00000000000085265128291212</v>
       </c>
     </row>
     <row r="20">
@@ -4476,34 +4476,34 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>3.39658042339941</v>
+        <v>3.39658042340207</v>
       </c>
       <c r="C20" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4166122344503</v>
+        <v>13.4166130720764</v>
       </c>
       <c r="E20" t="n">
-        <v>142.483859381863</v>
+        <v>142.483856543378</v>
       </c>
       <c r="F20" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="G20" t="n">
-        <v>114.982572927151</v>
+        <v>114.982575765636</v>
       </c>
       <c r="H20" t="n">
-        <v>32.3647383567877</v>
+        <v>32.3647390486347</v>
       </c>
       <c r="I20" t="n">
-        <v>45.781350591238</v>
+        <v>45.7813521207111</v>
       </c>
       <c r="J20" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="K20" t="n">
-        <v>0.000000000000625277607468888</v>
+        <v>0.00000000000085265128291212</v>
       </c>
     </row>
     <row r="21">
@@ -4511,34 +4511,34 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>16.9482255202062</v>
+        <v>16.9482255201931</v>
       </c>
       <c r="C21" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
       <c r="D21" t="n">
-        <v>55.3878575959945</v>
+        <v>55.3878555089404</v>
       </c>
       <c r="E21" t="n">
-        <v>142.483859381863</v>
+        <v>142.483856543378</v>
       </c>
       <c r="F21" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="G21" t="n">
-        <v>114.982572927151</v>
+        <v>114.982575765636</v>
       </c>
       <c r="H21" t="n">
-        <v>37.9475168725148</v>
+        <v>37.947517474959</v>
       </c>
       <c r="I21" t="n">
-        <v>93.3353744685093</v>
+        <v>93.3353729838994</v>
       </c>
       <c r="J21" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="K21" t="n">
-        <v>0.000000000000625277607468888</v>
+        <v>0.00000000000085265128291212</v>
       </c>
     </row>
     <row r="22">
@@ -4546,34 +4546,34 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>10.3705444540554</v>
+        <v>10.3705444540626</v>
       </c>
       <c r="C22" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
       <c r="D22" t="n">
-        <v>64.9529199757094</v>
+        <v>64.9529197490644</v>
       </c>
       <c r="E22" t="n">
-        <v>262.36295483106</v>
+        <v>262.362953746613</v>
       </c>
       <c r="F22" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="G22" t="n">
-        <v>139.014869461923</v>
+        <v>139.014870546369</v>
       </c>
       <c r="H22" t="n">
-        <v>42.7025895211057</v>
+        <v>42.7025900072201</v>
       </c>
       <c r="I22" t="n">
-        <v>107.655509496815</v>
+        <v>107.655509756284</v>
       </c>
       <c r="J22" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000056843418860808</v>
       </c>
     </row>
     <row r="23">
@@ -4581,34 +4581,34 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>11.8241962568536</v>
+        <v>11.824196256855</v>
       </c>
       <c r="C23" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
       <c r="D23" t="n">
-        <v>69.4550727438537</v>
+        <v>69.4550722034726</v>
       </c>
       <c r="E23" t="n">
-        <v>262.36295483106</v>
+        <v>262.362953746613</v>
       </c>
       <c r="F23" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="G23" t="n">
-        <v>139.014869461923</v>
+        <v>139.014870546369</v>
       </c>
       <c r="H23" t="n">
-        <v>41.4250697182921</v>
+        <v>41.4250700718735</v>
       </c>
       <c r="I23" t="n">
-        <v>110.880142462146</v>
+        <v>110.880142275346</v>
       </c>
       <c r="J23" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="K23" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000056843418860808</v>
       </c>
     </row>
     <row r="24">
@@ -4616,34 +4616,34 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>3.36455201043794</v>
+        <v>3.36455201044131</v>
       </c>
       <c r="C24" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
       <c r="D24" t="n">
-        <v>43.2544305486596</v>
+        <v>43.2544318339924</v>
       </c>
       <c r="E24" t="n">
-        <v>262.36295483106</v>
+        <v>262.362953746613</v>
       </c>
       <c r="F24" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="G24" t="n">
-        <v>139.014869461923</v>
+        <v>139.014870546369</v>
       </c>
       <c r="H24" t="n">
-        <v>34.114957464074</v>
+        <v>34.1149576689192</v>
       </c>
       <c r="I24" t="n">
-        <v>77.3693880127336</v>
+        <v>77.3693895029116</v>
       </c>
       <c r="J24" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="K24" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000056843418860808</v>
       </c>
     </row>
     <row r="25">
@@ -4651,34 +4651,34 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>16.7466388833034</v>
+        <v>16.7466388832914</v>
       </c>
       <c r="C25" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
       <c r="D25" t="n">
-        <v>84.7005315628371</v>
+        <v>84.7005299600837</v>
       </c>
       <c r="E25" t="n">
-        <v>262.36295483106</v>
+        <v>262.362953746613</v>
       </c>
       <c r="F25" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="G25" t="n">
-        <v>139.014869461923</v>
+        <v>139.014870546369</v>
       </c>
       <c r="H25" t="n">
-        <v>20.7722527584513</v>
+        <v>20.7722527983573</v>
       </c>
       <c r="I25" t="n">
-        <v>105.472784321288</v>
+        <v>105.472782758441</v>
       </c>
       <c r="J25" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="K25" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000056843418860808</v>
       </c>
     </row>
     <row r="26">
@@ -4686,34 +4686,34 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>10.7408214718168</v>
+        <v>10.7408214718216</v>
       </c>
       <c r="C26" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
       <c r="D26" t="n">
-        <v>99.642608865944</v>
+        <v>99.6426090573907</v>
       </c>
       <c r="E26" t="n">
-        <v>396.087862498063</v>
+        <v>396.087863436782</v>
       </c>
       <c r="F26" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="G26" t="n">
-        <v>-45.8654974257124</v>
+        <v>-45.8654983644314</v>
       </c>
       <c r="H26" t="n">
-        <v>1.39695560142422</v>
+        <v>1.39695546018769</v>
       </c>
       <c r="I26" t="n">
-        <v>101.039564467368</v>
+        <v>101.039564517578</v>
       </c>
       <c r="J26" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="K26" t="n">
-        <v>0.00000000000028421709430404</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="27">
@@ -4721,34 +4721,34 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>11.6466418714765</v>
+        <v>11.646641871478</v>
       </c>
       <c r="C27" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
       <c r="D27" t="n">
-        <v>102.44805499267</v>
+        <v>102.448054988619</v>
       </c>
       <c r="E27" t="n">
-        <v>396.087862498063</v>
+        <v>396.087863436782</v>
       </c>
       <c r="F27" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="G27" t="n">
-        <v>-45.8654974257124</v>
+        <v>-45.8654983644314</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.4984952445275</v>
+        <v>-11.4984954955983</v>
       </c>
       <c r="I27" t="n">
-        <v>90.9495597481429</v>
+        <v>90.9495594930202</v>
       </c>
       <c r="J27" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="K27" t="n">
-        <v>0.00000000000028421709430404</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="28">
@@ -4756,34 +4756,34 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>3.63961093490175</v>
+        <v>3.63961093490583</v>
       </c>
       <c r="C28" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
       <c r="D28" t="n">
-        <v>77.6492163530987</v>
+        <v>77.6492180770822</v>
       </c>
       <c r="E28" t="n">
-        <v>396.087862498063</v>
+        <v>396.087863436782</v>
       </c>
       <c r="F28" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="G28" t="n">
-        <v>-45.8654974257124</v>
+        <v>-45.8654983644314</v>
       </c>
       <c r="H28" t="n">
-        <v>-17.9140997794039</v>
+        <v>-17.9141000690008</v>
       </c>
       <c r="I28" t="n">
-        <v>59.7351165736948</v>
+        <v>59.7351180080814</v>
       </c>
       <c r="J28" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00000000000028421709430404</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="29">
@@ -4791,34 +4791,34 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>16.1346402602008</v>
+        <v>16.1346402601908</v>
       </c>
       <c r="C29" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
       <c r="D29" t="n">
-        <v>116.34798228635</v>
+        <v>116.347981313691</v>
       </c>
       <c r="E29" t="n">
-        <v>396.087862498063</v>
+        <v>396.087863436782</v>
       </c>
       <c r="F29" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="G29" t="n">
-        <v>-45.8654974257124</v>
+        <v>-45.8654983644314</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.8498580032049</v>
+        <v>-17.8498582600197</v>
       </c>
       <c r="I29" t="n">
-        <v>98.4981242831451</v>
+        <v>98.4981230536709</v>
       </c>
       <c r="J29" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="K29" t="n">
-        <v>0.00000000000028421709430404</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="30">
@@ -4826,34 +4826,34 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>11.1816037184858</v>
+        <v>11.1816037184879</v>
       </c>
       <c r="C30" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
       <c r="D30" t="n">
-        <v>89.177782660079</v>
+        <v>89.1777825742411</v>
       </c>
       <c r="E30" t="n">
-        <v>348.622751385867</v>
+        <v>348.622751606101</v>
       </c>
       <c r="F30" t="n">
         <v>318.31655034489</v>
       </c>
       <c r="G30" t="n">
-        <v>-30.3062010409764</v>
+        <v>-30.3062012612101</v>
       </c>
       <c r="H30" t="n">
-        <v>-11.3057699159305</v>
+        <v>-11.305770068655</v>
       </c>
       <c r="I30" t="n">
-        <v>77.8720127441485</v>
+        <v>77.872012505586</v>
       </c>
       <c r="J30" t="n">
         <v>318.316550344891</v>
       </c>
       <c r="K30" t="n">
-        <v>0.000000000000511590769747272</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="31">
@@ -4861,34 +4861,34 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>11.527526374305</v>
+        <v>11.5275263743065</v>
       </c>
       <c r="C31" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
       <c r="D31" t="n">
-        <v>90.2491510850777</v>
+        <v>90.2491509245828</v>
       </c>
       <c r="E31" t="n">
-        <v>348.622751385867</v>
+        <v>348.622751606101</v>
       </c>
       <c r="F31" t="n">
         <v>318.31655034489</v>
       </c>
       <c r="G31" t="n">
-        <v>-30.3062010409764</v>
+        <v>-30.3062012612101</v>
       </c>
       <c r="H31" t="n">
-        <v>-7.19644681874616</v>
+        <v>-7.19644689076812</v>
       </c>
       <c r="I31" t="n">
-        <v>83.0527042663316</v>
+        <v>83.0527040338147</v>
       </c>
       <c r="J31" t="n">
         <v>318.316550344891</v>
       </c>
       <c r="K31" t="n">
-        <v>0.000000000000511590769747272</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="32">
@@ -4896,34 +4896,34 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>3.93494656467131</v>
+        <v>3.93494656467575</v>
       </c>
       <c r="C32" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
       <c r="D32" t="n">
-        <v>66.7339226503887</v>
+        <v>66.7339241284864</v>
       </c>
       <c r="E32" t="n">
-        <v>348.622751385867</v>
+        <v>348.622751606101</v>
       </c>
       <c r="F32" t="n">
         <v>318.31655034489</v>
       </c>
       <c r="G32" t="n">
-        <v>-30.3062010409764</v>
+        <v>-30.3062012612101</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.52188871165178</v>
+        <v>-5.52188872635897</v>
       </c>
       <c r="I32" t="n">
-        <v>61.2120339387369</v>
+        <v>61.2120354021274</v>
       </c>
       <c r="J32" t="n">
         <v>318.316550344891</v>
       </c>
       <c r="K32" t="n">
-        <v>0.000000000000511590769747272</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="33">
@@ -4931,34 +4931,34 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>15.4707682208692</v>
+        <v>15.4707682208608</v>
       </c>
       <c r="C33" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
       <c r="D33" t="n">
-        <v>102.461894990321</v>
+        <v>102.46189397879</v>
       </c>
       <c r="E33" t="n">
-        <v>348.622751385867</v>
+        <v>348.622751606101</v>
       </c>
       <c r="F33" t="n">
         <v>318.31655034489</v>
       </c>
       <c r="G33" t="n">
-        <v>-30.3062010409764</v>
+        <v>-30.3062012612101</v>
       </c>
       <c r="H33" t="n">
-        <v>-6.28209559464739</v>
+        <v>-6.28209557542758</v>
       </c>
       <c r="I33" t="n">
-        <v>96.179799395674</v>
+        <v>96.1797984033627</v>
       </c>
       <c r="J33" t="n">
         <v>318.316550344891</v>
       </c>
       <c r="K33" t="n">
-        <v>0.000000000000511590769747272</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="34">
@@ -4966,34 +4966,34 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>11.0979545641297</v>
+        <v>11.0979545641313</v>
       </c>
       <c r="C34" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
       <c r="D34" t="n">
-        <v>81.5091849882317</v>
+        <v>81.5091848085474</v>
       </c>
       <c r="E34" t="n">
-        <v>319.683577854721</v>
+        <v>319.683577578662</v>
       </c>
       <c r="F34" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="G34" t="n">
-        <v>-49.9999074096829</v>
+        <v>-49.9999071336239</v>
       </c>
       <c r="H34" t="n">
-        <v>-9.477067467733</v>
+        <v>-9.47706743797394</v>
       </c>
       <c r="I34" t="n">
-        <v>72.0321175204987</v>
+        <v>72.0321173705735</v>
       </c>
       <c r="J34" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="K34" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000170530256582424</v>
       </c>
     </row>
     <row r="35">
@@ -5001,34 +5001,34 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>11.1768869325754</v>
+        <v>11.1768869325764</v>
       </c>
       <c r="C35" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
       <c r="D35" t="n">
-        <v>81.7536490204092</v>
+        <v>81.7536488236882</v>
       </c>
       <c r="E35" t="n">
-        <v>319.683577854721</v>
+        <v>319.683577578662</v>
       </c>
       <c r="F35" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="G35" t="n">
-        <v>-49.9999074096829</v>
+        <v>-49.9999071336239</v>
       </c>
       <c r="H35" t="n">
-        <v>-11.9642199708423</v>
+        <v>-11.9642199211653</v>
       </c>
       <c r="I35" t="n">
-        <v>69.7894290495669</v>
+        <v>69.7894289025229</v>
       </c>
       <c r="J35" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="K35" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000170530256582424</v>
       </c>
     </row>
     <row r="36">
@@ -5036,34 +5036,34 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>6.09246182598753</v>
+        <v>6.09246182599038</v>
       </c>
       <c r="C36" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
       <c r="D36" t="n">
-        <v>66.0065089391448</v>
+        <v>66.0065098397185</v>
       </c>
       <c r="E36" t="n">
-        <v>319.683577854721</v>
+        <v>319.683577578662</v>
       </c>
       <c r="F36" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="G36" t="n">
-        <v>-49.9999074096829</v>
+        <v>-49.9999071336239</v>
       </c>
       <c r="H36" t="n">
-        <v>-13.7435531039753</v>
+        <v>-13.7435530250016</v>
       </c>
       <c r="I36" t="n">
-        <v>52.2629558351695</v>
+        <v>52.2629568147169</v>
       </c>
       <c r="J36" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="K36" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000170530256582424</v>
       </c>
     </row>
     <row r="37">
@@ -5071,34 +5071,34 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>13.9732105882977</v>
+        <v>13.9732105882918</v>
       </c>
       <c r="C37" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
       <c r="D37" t="n">
-        <v>90.4142349069349</v>
+        <v>90.4142341067075</v>
       </c>
       <c r="E37" t="n">
-        <v>319.683577854721</v>
+        <v>319.683577578662</v>
       </c>
       <c r="F37" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="G37" t="n">
-        <v>-49.9999074096829</v>
+        <v>-49.9999071336239</v>
       </c>
       <c r="H37" t="n">
-        <v>-14.815066867132</v>
+        <v>-14.8150667494829</v>
       </c>
       <c r="I37" t="n">
-        <v>75.5991680398029</v>
+        <v>75.5991673572246</v>
       </c>
       <c r="J37" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="K37" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000170530256582424</v>
       </c>
     </row>
     <row r="38">
@@ -5106,34 +5106,34 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>10.864533561075</v>
+        <v>10.8645335610762</v>
       </c>
       <c r="C38" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
       <c r="D38" t="n">
-        <v>69.2775039927475</v>
+        <v>69.2775037046601</v>
       </c>
       <c r="E38" t="n">
-        <v>274.025699038857</v>
+        <v>274.025698101413</v>
       </c>
       <c r="F38" t="n">
         <v>236.574897953765</v>
       </c>
       <c r="G38" t="n">
-        <v>-37.4508010850919</v>
+        <v>-37.4508001476473</v>
       </c>
       <c r="H38" t="n">
-        <v>-15.1787612603123</v>
+        <v>-15.1787610946092</v>
       </c>
       <c r="I38" t="n">
-        <v>54.0987427324352</v>
+        <v>54.0987426100509</v>
       </c>
       <c r="J38" t="n">
         <v>236.574897953766</v>
       </c>
       <c r="K38" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="39">
@@ -5141,34 +5141,34 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>10.7664038770365</v>
+        <v>10.766403877037</v>
       </c>
       <c r="C39" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
       <c r="D39" t="n">
-        <v>68.973583323588</v>
+        <v>68.9735830566764</v>
       </c>
       <c r="E39" t="n">
-        <v>274.025699038857</v>
+        <v>274.025698101413</v>
       </c>
       <c r="F39" t="n">
         <v>236.574897953765</v>
       </c>
       <c r="G39" t="n">
-        <v>-37.4508010850919</v>
+        <v>-37.4508001476473</v>
       </c>
       <c r="H39" t="n">
-        <v>-12.9978146219687</v>
+        <v>-12.9978144095808</v>
       </c>
       <c r="I39" t="n">
-        <v>55.9757687016194</v>
+        <v>55.9757686470956</v>
       </c>
       <c r="J39" t="n">
         <v>236.574897953766</v>
       </c>
       <c r="K39" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="40">
@@ -5176,34 +5176,34 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>8.26874568961225</v>
+        <v>8.26874568961349</v>
       </c>
       <c r="C40" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
       <c r="D40" t="n">
-        <v>61.2380040736302</v>
+        <v>61.2380043457498</v>
       </c>
       <c r="E40" t="n">
-        <v>274.025699038857</v>
+        <v>274.025698101413</v>
       </c>
       <c r="F40" t="n">
         <v>236.574897953765</v>
       </c>
       <c r="G40" t="n">
-        <v>-37.4508010850919</v>
+        <v>-37.4508001476473</v>
       </c>
       <c r="H40" t="n">
-        <v>-8.27222695210104</v>
+        <v>-8.27222669439751</v>
       </c>
       <c r="I40" t="n">
-        <v>52.9657771215292</v>
+        <v>52.9657776513523</v>
       </c>
       <c r="J40" t="n">
         <v>236.574897953766</v>
       </c>
       <c r="K40" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="41">
@@ -5211,34 +5211,34 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>12.5625891146203</v>
+        <v>12.562589114617</v>
       </c>
       <c r="C41" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
       <c r="D41" t="n">
-        <v>74.5366076488916</v>
+        <v>74.5366069943265</v>
       </c>
       <c r="E41" t="n">
-        <v>274.025699038857</v>
+        <v>274.025698101413</v>
       </c>
       <c r="F41" t="n">
         <v>236.574897953765</v>
       </c>
       <c r="G41" t="n">
-        <v>-37.4508010850919</v>
+        <v>-37.4508001476473</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.00199825070943</v>
+        <v>-1.00199794905949</v>
       </c>
       <c r="I41" t="n">
-        <v>73.5346093981822</v>
+        <v>73.534609045267</v>
       </c>
       <c r="J41" t="n">
         <v>236.574897953766</v>
       </c>
       <c r="K41" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="42">
@@ -5246,34 +5246,34 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>10.7788841220817</v>
+        <v>10.7788841220824</v>
       </c>
       <c r="C42" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
       <c r="D42" t="n">
-        <v>61.2002298798819</v>
+        <v>61.2002295009192</v>
       </c>
       <c r="E42" t="n">
-        <v>242.426970859653</v>
+        <v>242.426969509212</v>
       </c>
       <c r="F42" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="G42" t="n">
-        <v>61.8897526486993</v>
+        <v>61.8897539991403</v>
       </c>
       <c r="H42" t="n">
-        <v>8.81287148220617</v>
+        <v>8.81287182643331</v>
       </c>
       <c r="I42" t="n">
-        <v>70.0131013620881</v>
+        <v>70.0131013273525</v>
       </c>
       <c r="J42" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="K42" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="43">
@@ -5281,34 +5281,34 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>10.585067784036</v>
+        <v>10.5850677840361</v>
       </c>
       <c r="C43" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
       <c r="D43" t="n">
-        <v>60.5999549301557</v>
+        <v>60.5999545930194</v>
       </c>
       <c r="E43" t="n">
-        <v>242.426970859653</v>
+        <v>242.426969509212</v>
       </c>
       <c r="F43" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="G43" t="n">
-        <v>61.8897526486993</v>
+        <v>61.8897539991403</v>
       </c>
       <c r="H43" t="n">
-        <v>15.4026460473599</v>
+        <v>15.4026464059711</v>
       </c>
       <c r="I43" t="n">
-        <v>76.0026009775156</v>
+        <v>76.0026009989905</v>
       </c>
       <c r="J43" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="K43" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="44">
@@ -5316,34 +5316,34 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>9.12229912279982</v>
+        <v>9.12229912280024</v>
       </c>
       <c r="C44" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
       <c r="D44" t="n">
-        <v>56.0695660401466</v>
+        <v>56.0695660186969</v>
       </c>
       <c r="E44" t="n">
-        <v>242.426970859653</v>
+        <v>242.426969509212</v>
       </c>
       <c r="F44" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="G44" t="n">
-        <v>61.8897526486993</v>
+        <v>61.8897539991403</v>
       </c>
       <c r="H44" t="n">
-        <v>18.7673254447517</v>
+        <v>18.767325789554</v>
       </c>
       <c r="I44" t="n">
-        <v>74.8368914848983</v>
+        <v>74.8368918082509</v>
       </c>
       <c r="J44" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="K44" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="45">
@@ -5351,34 +5351,34 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>11.8627866471977</v>
+        <v>11.8627866471957</v>
       </c>
       <c r="C45" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
       <c r="D45" t="n">
-        <v>64.5572200094685</v>
+        <v>64.5572193965763</v>
       </c>
       <c r="E45" t="n">
-        <v>242.426970859653</v>
+        <v>242.426969509212</v>
       </c>
       <c r="F45" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="G45" t="n">
-        <v>61.8897526486993</v>
+        <v>61.8897539991403</v>
       </c>
       <c r="H45" t="n">
-        <v>18.9069096743816</v>
+        <v>18.9069099771819</v>
       </c>
       <c r="I45" t="n">
-        <v>83.4641296838501</v>
+        <v>83.4641293737582</v>
       </c>
       <c r="J45" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="K45" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="46">
@@ -5386,34 +5386,34 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>10.7822885416373</v>
+        <v>10.7822885416376</v>
       </c>
       <c r="C46" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
       <c r="D46" t="n">
-        <v>77.0962562422494</v>
+        <v>77.0962560916924</v>
       </c>
       <c r="E46" t="n">
-        <v>306.239157707811</v>
+        <v>306.239157255104</v>
       </c>
       <c r="F46" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="G46" t="n">
-        <v>54.3728261916438</v>
+        <v>54.372826644351</v>
       </c>
       <c r="H46" t="n">
-        <v>15.8213987362497</v>
+        <v>15.8213989688548</v>
       </c>
       <c r="I46" t="n">
-        <v>92.9176549784991</v>
+        <v>92.9176550605472</v>
       </c>
       <c r="J46" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="47">
@@ -5421,34 +5421,34 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>10.443831487176</v>
+        <v>10.4438314871757</v>
       </c>
       <c r="C47" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
       <c r="D47" t="n">
-        <v>76.0480097765498</v>
+        <v>76.0480096990348</v>
       </c>
       <c r="E47" t="n">
-        <v>306.239157707811</v>
+        <v>306.239157255104</v>
       </c>
       <c r="F47" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="G47" t="n">
-        <v>54.3728261916438</v>
+        <v>54.372826644351</v>
       </c>
       <c r="H47" t="n">
-        <v>13.6959174856614</v>
+        <v>13.6959176424172</v>
       </c>
       <c r="I47" t="n">
-        <v>89.7439272622113</v>
+        <v>89.743927341452</v>
       </c>
       <c r="J47" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="48">
@@ -5456,34 +5456,34 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>10.0022276754269</v>
+        <v>10.0022276754265</v>
       </c>
       <c r="C48" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
       <c r="D48" t="n">
-        <v>74.6803040992604</v>
+        <v>74.6803041170491</v>
       </c>
       <c r="E48" t="n">
-        <v>306.239157707811</v>
+        <v>306.239157255104</v>
       </c>
       <c r="F48" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="G48" t="n">
-        <v>54.3728261916438</v>
+        <v>54.372826644351</v>
       </c>
       <c r="H48" t="n">
-        <v>12.5304659226168</v>
+        <v>12.5304659978689</v>
       </c>
       <c r="I48" t="n">
-        <v>87.2107700218772</v>
+        <v>87.210770114918</v>
       </c>
       <c r="J48" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="49">
@@ -5491,34 +5491,34 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>11.2079504057885</v>
+        <v>11.2079504057878</v>
       </c>
       <c r="C49" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
       <c r="D49" t="n">
-        <v>78.4145875897513</v>
+        <v>78.4145873473275</v>
       </c>
       <c r="E49" t="n">
-        <v>306.239157707811</v>
+        <v>306.239157255104</v>
       </c>
       <c r="F49" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="G49" t="n">
-        <v>54.3728261916438</v>
+        <v>54.372826644351</v>
       </c>
       <c r="H49" t="n">
-        <v>12.3250440471158</v>
+        <v>12.3250440352101</v>
       </c>
       <c r="I49" t="n">
-        <v>90.7396316368671</v>
+        <v>90.7396313825376</v>
       </c>
       <c r="J49" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="50">
@@ -5529,31 +5529,31 @@
         <v>10.8200506299549</v>
       </c>
       <c r="C50" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
       <c r="D50" t="n">
-        <v>90.2834287157394</v>
+        <v>90.2834287546482</v>
       </c>
       <c r="E50" t="n">
-        <v>359.664431900577</v>
+        <v>359.664432158594</v>
       </c>
       <c r="F50" t="n">
         <v>430.289828585279</v>
       </c>
       <c r="G50" t="n">
-        <v>70.6253966847027</v>
+        <v>70.6253964266855</v>
       </c>
       <c r="H50" t="n">
-        <v>13.0796518591585</v>
+        <v>13.0796517544407</v>
       </c>
       <c r="I50" t="n">
-        <v>103.363080574898</v>
+        <v>103.363080509089</v>
       </c>
       <c r="J50" t="n">
-        <v>430.289828585279</v>
+        <v>430.28982858528</v>
       </c>
       <c r="K50" t="n">
-        <v>0.000000000000056843418860808</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="51">
@@ -5564,31 +5564,31 @@
         <v>10.5382561440265</v>
       </c>
       <c r="C51" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
       <c r="D51" t="n">
-        <v>89.4106737530807</v>
+        <v>89.4106738528045</v>
       </c>
       <c r="E51" t="n">
-        <v>359.664431900577</v>
+        <v>359.664432158594</v>
       </c>
       <c r="F51" t="n">
         <v>430.289828585279</v>
       </c>
       <c r="G51" t="n">
-        <v>70.6253966847027</v>
+        <v>70.6253964266855</v>
       </c>
       <c r="H51" t="n">
-        <v>15.2121739087824</v>
+        <v>15.2121737830252</v>
       </c>
       <c r="I51" t="n">
-        <v>104.622847661863</v>
+        <v>104.62284763583</v>
       </c>
       <c r="J51" t="n">
-        <v>430.289828585279</v>
+        <v>430.28982858528</v>
       </c>
       <c r="K51" t="n">
-        <v>0.000000000000056843418860808</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="52">
@@ -5599,31 +5599,31 @@
         <v>10.5759503785478</v>
       </c>
       <c r="C52" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
       <c r="D52" t="n">
-        <v>89.527417805519</v>
+        <v>89.5274178971079</v>
       </c>
       <c r="E52" t="n">
-        <v>359.664431900577</v>
+        <v>359.664432158594</v>
       </c>
       <c r="F52" t="n">
         <v>430.289828585279</v>
       </c>
       <c r="G52" t="n">
-        <v>70.6253966847027</v>
+        <v>70.6253964266855</v>
       </c>
       <c r="H52" t="n">
-        <v>18.7226101959877</v>
+        <v>18.7226101209637</v>
       </c>
       <c r="I52" t="n">
-        <v>108.250028001507</v>
+        <v>108.250028018072</v>
       </c>
       <c r="J52" t="n">
-        <v>430.289828585279</v>
+        <v>430.28982858528</v>
       </c>
       <c r="K52" t="n">
-        <v>0.000000000000056843418860808</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="53">
@@ -5634,31 +5634,31 @@
         <v>10.8715443558012</v>
       </c>
       <c r="C53" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
       <c r="D53" t="n">
-        <v>90.4429116262376</v>
+        <v>90.4429116540333</v>
       </c>
       <c r="E53" t="n">
-        <v>359.664431900577</v>
+        <v>359.664432158594</v>
       </c>
       <c r="F53" t="n">
         <v>430.289828585279</v>
       </c>
       <c r="G53" t="n">
-        <v>70.6253966847027</v>
+        <v>70.6253964266855</v>
       </c>
       <c r="H53" t="n">
-        <v>23.6109607207742</v>
+        <v>23.6109607682561</v>
       </c>
       <c r="I53" t="n">
-        <v>114.053872347012</v>
+        <v>114.053872422289</v>
       </c>
       <c r="J53" t="n">
-        <v>430.289828585279</v>
+        <v>430.28982858528</v>
       </c>
       <c r="K53" t="n">
-        <v>0.000000000000056843418860808</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="54">
@@ -5669,25 +5669,25 @@
         <v>12.9570570133416</v>
       </c>
       <c r="C54" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
       <c r="D54" t="n">
-        <v>112.890366158746</v>
+        <v>112.890365991425</v>
       </c>
       <c r="E54" t="n">
-        <v>454.764379328204</v>
+        <v>454.764378435737</v>
       </c>
       <c r="F54" t="n">
         <v>566.541738110914</v>
       </c>
       <c r="G54" t="n">
-        <v>111.77735878271</v>
+        <v>111.777359675177</v>
       </c>
       <c r="H54" t="n">
-        <v>29.877225483142</v>
+        <v>29.8772257249026</v>
       </c>
       <c r="I54" t="n">
-        <v>142.767591641887</v>
+        <v>142.767591716327</v>
       </c>
       <c r="J54" t="n">
         <v>566.541738110914</v>
@@ -5704,25 +5704,25 @@
         <v>12.7543914906828</v>
       </c>
       <c r="C55" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
       <c r="D55" t="n">
-        <v>112.262684108553</v>
+        <v>112.262683984971</v>
       </c>
       <c r="E55" t="n">
-        <v>454.764379328204</v>
+        <v>454.764378435737</v>
       </c>
       <c r="F55" t="n">
         <v>566.541738110914</v>
       </c>
       <c r="G55" t="n">
-        <v>111.77735878271</v>
+        <v>111.777359675177</v>
       </c>
       <c r="H55" t="n">
-        <v>31.6105770731033</v>
+        <v>31.6105773851178</v>
       </c>
       <c r="I55" t="n">
-        <v>143.873261181657</v>
+        <v>143.873261370088</v>
       </c>
       <c r="J55" t="n">
         <v>566.541738110914</v>
@@ -5739,25 +5739,25 @@
         <v>13.0397525391501</v>
       </c>
       <c r="C56" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
       <c r="D56" t="n">
-        <v>113.146485189256</v>
+        <v>113.146485004088</v>
       </c>
       <c r="E56" t="n">
-        <v>454.764379328204</v>
+        <v>454.764378435737</v>
       </c>
       <c r="F56" t="n">
         <v>566.541738110914</v>
       </c>
       <c r="G56" t="n">
-        <v>111.77735878271</v>
+        <v>111.777359675177</v>
       </c>
       <c r="H56" t="n">
-        <v>28.8110154906581</v>
+        <v>28.8110157489019</v>
       </c>
       <c r="I56" t="n">
-        <v>141.957500679914</v>
+        <v>141.95750075299</v>
       </c>
       <c r="J56" t="n">
         <v>566.541738110914</v>
@@ -5774,25 +5774,25 @@
         <v>14.1111817707667</v>
       </c>
       <c r="C57" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
       <c r="D57" t="n">
-        <v>116.46484387165</v>
+        <v>116.464843455253</v>
       </c>
       <c r="E57" t="n">
-        <v>454.764379328204</v>
+        <v>454.764378435737</v>
       </c>
       <c r="F57" t="n">
         <v>566.541738110914</v>
       </c>
       <c r="G57" t="n">
-        <v>111.77735878271</v>
+        <v>111.777359675177</v>
       </c>
       <c r="H57" t="n">
-        <v>21.4785407358064</v>
+        <v>21.4785408162547</v>
       </c>
       <c r="I57" t="n">
-        <v>137.943384607456</v>
+        <v>137.943384271508</v>
       </c>
       <c r="J57" t="n">
         <v>566.541738110914</v>
@@ -5809,31 +5809,31 @@
         <v>14.0378160523454</v>
       </c>
       <c r="C58" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
       <c r="D58" t="n">
-        <v>140.757918038574</v>
+        <v>140.757918506831</v>
       </c>
       <c r="E58" t="n">
-        <v>569.170477723727</v>
+        <v>569.170479168995</v>
       </c>
       <c r="F58" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="G58" t="n">
-        <v>10.4233474850274</v>
+        <v>10.4233460397594</v>
       </c>
       <c r="H58" t="n">
-        <v>9.61315280854823</v>
+        <v>9.61315258717642</v>
       </c>
       <c r="I58" t="n">
-        <v>150.371070847122</v>
+        <v>150.371071094008</v>
       </c>
       <c r="J58" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="K58" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5844,31 +5844,31 @@
         <v>12.2062827701092</v>
       </c>
       <c r="C59" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
       <c r="D59" t="n">
-        <v>135.085416122575</v>
+        <v>135.085416986103</v>
       </c>
       <c r="E59" t="n">
-        <v>569.170477723727</v>
+        <v>569.170479168995</v>
       </c>
       <c r="F59" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="G59" t="n">
-        <v>10.4233474850274</v>
+        <v>10.4233460397594</v>
       </c>
       <c r="H59" t="n">
-        <v>2.06407126272842</v>
+        <v>2.06407086465046</v>
       </c>
       <c r="I59" t="n">
-        <v>137.149487385303</v>
+        <v>137.149487850753</v>
       </c>
       <c r="J59" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="K59" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5879,31 +5879,31 @@
         <v>14.7690861061654</v>
       </c>
       <c r="C60" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
       <c r="D60" t="n">
-        <v>143.022758553151</v>
+        <v>143.022758863591</v>
       </c>
       <c r="E60" t="n">
-        <v>569.170477723727</v>
+        <v>569.170479168995</v>
       </c>
       <c r="F60" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="G60" t="n">
-        <v>10.4233474850274</v>
+        <v>10.4233460397594</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.16870390165303</v>
+        <v>-1.16870435132313</v>
       </c>
       <c r="I60" t="n">
-        <v>141.854054651498</v>
+        <v>141.854054512268</v>
       </c>
       <c r="J60" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="K60" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5914,31 +5914,31 @@
         <v>17.1201723465891</v>
       </c>
       <c r="C61" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
       <c r="D61" t="n">
-        <v>150.304385009428</v>
+        <v>150.30438481247</v>
       </c>
       <c r="E61" t="n">
-        <v>569.170477723727</v>
+        <v>569.170479168995</v>
       </c>
       <c r="F61" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="G61" t="n">
-        <v>10.4233474850274</v>
+        <v>10.4233460397594</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0851726845961081</v>
+        <v>-0.085173060744369</v>
       </c>
       <c r="I61" t="n">
-        <v>150.219212324832</v>
+        <v>150.219211751726</v>
       </c>
       <c r="J61" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="K61" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5949,31 +5949,31 @@
         <v>16.5595286531131</v>
       </c>
       <c r="C62" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
       <c r="D62" t="n">
-        <v>147.804472077513</v>
+        <v>147.804472255645</v>
       </c>
       <c r="E62" t="n">
-        <v>591.97624707772</v>
+        <v>591.976247737402</v>
       </c>
       <c r="F62" t="n">
         <v>637.096554399705</v>
       </c>
       <c r="G62" t="n">
-        <v>45.1203073219859</v>
+        <v>45.1203066623033</v>
       </c>
       <c r="H62" t="n">
-        <v>5.31466491389918</v>
+        <v>5.31466473638676</v>
       </c>
       <c r="I62" t="n">
-        <v>153.119136991412</v>
+        <v>153.119136992031</v>
       </c>
       <c r="J62" t="n">
         <v>637.096554399706</v>
       </c>
       <c r="K62" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="63">
@@ -5984,31 +5984,31 @@
         <v>16.1236209274397</v>
       </c>
       <c r="C63" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
       <c r="D63" t="n">
-        <v>146.454407935593</v>
+        <v>146.454408207799</v>
       </c>
       <c r="E63" t="n">
-        <v>591.97624707772</v>
+        <v>591.976247737402</v>
       </c>
       <c r="F63" t="n">
         <v>637.096554399705</v>
       </c>
       <c r="G63" t="n">
-        <v>45.1203073219859</v>
+        <v>45.1203066623033</v>
       </c>
       <c r="H63" t="n">
-        <v>9.86076471993623</v>
+        <v>9.86076462691483</v>
       </c>
       <c r="I63" t="n">
-        <v>156.315172655529</v>
+        <v>156.315172834714</v>
       </c>
       <c r="J63" t="n">
         <v>637.096554399706</v>
       </c>
       <c r="K63" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="64">
@@ -6019,31 +6019,31 @@
         <v>16.3192772141769</v>
       </c>
       <c r="C64" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
       <c r="D64" t="n">
-        <v>147.060381450876</v>
+        <v>147.060381680857</v>
       </c>
       <c r="E64" t="n">
-        <v>591.97624707772</v>
+        <v>591.976247737402</v>
       </c>
       <c r="F64" t="n">
         <v>637.096554399705</v>
       </c>
       <c r="G64" t="n">
-        <v>45.1203073219859</v>
+        <v>45.1203066623033</v>
       </c>
       <c r="H64" t="n">
-        <v>13.553126733515</v>
+        <v>13.5531266108399</v>
       </c>
       <c r="I64" t="n">
-        <v>160.613508184391</v>
+        <v>160.613508291697</v>
       </c>
       <c r="J64" t="n">
         <v>637.096554399706</v>
       </c>
       <c r="K64" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="65">
@@ -6054,31 +6054,31 @@
         <v>17.48054614363</v>
       </c>
       <c r="C65" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
       <c r="D65" t="n">
-        <v>150.656985613738</v>
+        <v>150.656985593102</v>
       </c>
       <c r="E65" t="n">
-        <v>591.97624707772</v>
+        <v>591.976247737402</v>
       </c>
       <c r="F65" t="n">
         <v>637.096554399705</v>
       </c>
       <c r="G65" t="n">
-        <v>45.1203073219859</v>
+        <v>45.1203066623033</v>
       </c>
       <c r="H65" t="n">
-        <v>16.3917509546356</v>
+        <v>16.3917506881618</v>
       </c>
       <c r="I65" t="n">
-        <v>167.048736568374</v>
+        <v>167.048736281263</v>
       </c>
       <c r="J65" t="n">
         <v>637.096554399706</v>
       </c>
       <c r="K65" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="66">
@@ -6089,31 +6089,31 @@
         <v>17.3052064617991</v>
       </c>
       <c r="C66" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
       <c r="D66" t="n">
-        <v>157.495980209647</v>
+        <v>157.495980756367</v>
       </c>
       <c r="E66" t="n">
-        <v>636.505127621141</v>
+        <v>636.505129353614</v>
       </c>
       <c r="F66" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="G66" t="n">
-        <v>62.4833257396152</v>
+        <v>62.4833240071421</v>
       </c>
       <c r="H66" t="n">
-        <v>18.376637383298</v>
+        <v>18.3766368588808</v>
       </c>
       <c r="I66" t="n">
-        <v>175.872617592945</v>
+        <v>175.872617615248</v>
       </c>
       <c r="J66" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="K66" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="67">
@@ -6124,31 +6124,31 @@
         <v>17.4491223381665</v>
       </c>
       <c r="C67" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
       <c r="D67" t="n">
-        <v>157.941706799687</v>
+        <v>157.941707315349</v>
       </c>
       <c r="E67" t="n">
-        <v>636.505127621141</v>
+        <v>636.505129353614</v>
       </c>
       <c r="F67" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="G67" t="n">
-        <v>62.4833257396152</v>
+        <v>62.4833240071421</v>
       </c>
       <c r="H67" t="n">
-        <v>18.0682695754053</v>
+        <v>18.0682689843302</v>
       </c>
       <c r="I67" t="n">
-        <v>176.009976375092</v>
+        <v>176.009976299679</v>
       </c>
       <c r="J67" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="K67" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="68">
@@ -6159,31 +6159,31 @@
         <v>17.259954781733</v>
       </c>
       <c r="C68" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
       <c r="D68" t="n">
-        <v>157.35582974426</v>
+        <v>157.355830300746</v>
       </c>
       <c r="E68" t="n">
-        <v>636.505127621141</v>
+        <v>636.505129353614</v>
       </c>
       <c r="F68" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="G68" t="n">
-        <v>62.4833257396152</v>
+        <v>62.4833240071421</v>
       </c>
       <c r="H68" t="n">
-        <v>15.4666475309576</v>
+        <v>15.4666470645103</v>
       </c>
       <c r="I68" t="n">
-        <v>172.822477275217</v>
+        <v>172.822477365257</v>
       </c>
       <c r="J68" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="K68" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="69">
@@ -6194,31 +6194,31 @@
         <v>19.3121047561699</v>
       </c>
       <c r="C69" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
       <c r="D69" t="n">
-        <v>163.711610867547</v>
+        <v>163.711610981152</v>
       </c>
       <c r="E69" t="n">
-        <v>636.505127621141</v>
+        <v>636.505129353614</v>
       </c>
       <c r="F69" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4833257396152</v>
+        <v>62.4833240071421</v>
       </c>
       <c r="H69" t="n">
-        <v>10.5717712499548</v>
+        <v>10.5717710994209</v>
       </c>
       <c r="I69" t="n">
-        <v>174.283382117502</v>
+        <v>174.283382080572</v>
       </c>
       <c r="J69" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="K69" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="70">
@@ -6229,31 +6229,31 @@
         <v>23.1154258857424</v>
       </c>
       <c r="C70" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
       <c r="D70" t="n">
-        <v>186.430370876925</v>
+        <v>186.430370575297</v>
       </c>
       <c r="E70" t="n">
-        <v>756.877521803797</v>
+        <v>756.877519819912</v>
       </c>
       <c r="F70" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="G70" t="n">
-        <v>-13.3180839810478</v>
+        <v>-13.3180819971633</v>
       </c>
       <c r="H70" t="n">
-        <v>3.38364073239704</v>
+        <v>3.38364108906204</v>
       </c>
       <c r="I70" t="n">
-        <v>189.814011609322</v>
+        <v>189.814011664359</v>
       </c>
       <c r="J70" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="K70" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="71">
@@ -6264,31 +6264,31 @@
         <v>23.8949714243776</v>
       </c>
       <c r="C71" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
       <c r="D71" t="n">
-        <v>188.844726981946</v>
+        <v>188.844726512081</v>
       </c>
       <c r="E71" t="n">
-        <v>756.877521803797</v>
+        <v>756.877519819912</v>
       </c>
       <c r="F71" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="G71" t="n">
-        <v>-13.3180839810478</v>
+        <v>-13.3180819971633</v>
       </c>
       <c r="H71" t="n">
-        <v>-2.17687616568963</v>
+        <v>-2.17687555042263</v>
       </c>
       <c r="I71" t="n">
-        <v>186.667850816256</v>
+        <v>186.667850961659</v>
       </c>
       <c r="J71" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="K71" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="72">
@@ -6299,31 +6299,31 @@
         <v>23.0079858138554</v>
       </c>
       <c r="C72" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
       <c r="D72" t="n">
-        <v>186.097614699603</v>
+        <v>186.097614421162</v>
       </c>
       <c r="E72" t="n">
-        <v>756.877521803797</v>
+        <v>756.877519819912</v>
       </c>
       <c r="F72" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="G72" t="n">
-        <v>-13.3180839810478</v>
+        <v>-13.3180819971633</v>
       </c>
       <c r="H72" t="n">
-        <v>-6.1097794443052</v>
+        <v>-6.10977881903313</v>
       </c>
       <c r="I72" t="n">
-        <v>179.987835255298</v>
+        <v>179.987835602129</v>
       </c>
       <c r="J72" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="K72" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="73">
@@ -6334,31 +6334,31 @@
         <v>26.0453739290296</v>
       </c>
       <c r="C73" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
       <c r="D73" t="n">
-        <v>195.504809245323</v>
+        <v>195.504808311372</v>
       </c>
       <c r="E73" t="n">
-        <v>756.877521803797</v>
+        <v>756.877519819912</v>
       </c>
       <c r="F73" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="G73" t="n">
-        <v>-13.3180839810478</v>
+        <v>-13.3180819971633</v>
       </c>
       <c r="H73" t="n">
-        <v>-8.41506910344967</v>
+        <v>-8.41506871676944</v>
       </c>
       <c r="I73" t="n">
-        <v>187.089740141874</v>
+        <v>187.089739594603</v>
       </c>
       <c r="J73" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="K73" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="74">
@@ -6369,31 +6369,31 @@
         <v>24.404052044643</v>
       </c>
       <c r="C74" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
       <c r="D74" t="n">
-        <v>182.945805061929</v>
+        <v>182.945805617153</v>
       </c>
       <c r="E74" t="n">
-        <v>739.166140233687</v>
+        <v>739.166141940129</v>
       </c>
       <c r="F74" t="n">
         <v>742.49</v>
       </c>
       <c r="G74" t="n">
-        <v>3.32385976631326</v>
+        <v>3.32385805987087</v>
       </c>
       <c r="H74" t="n">
-        <v>-9.09274514312303</v>
+        <v>-9.09274524363157</v>
       </c>
       <c r="I74" t="n">
-        <v>173.853059918806</v>
+        <v>173.853060373522</v>
       </c>
       <c r="J74" t="n">
         <v>742.49</v>
       </c>
       <c r="K74" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="75">
@@ -6404,31 +6404,31 @@
         <v>24.6011462830655</v>
       </c>
       <c r="C75" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
       <c r="D75" t="n">
-        <v>183.55623210463</v>
+        <v>183.556232617319</v>
       </c>
       <c r="E75" t="n">
-        <v>739.166140233687</v>
+        <v>739.166141940129</v>
       </c>
       <c r="F75" t="n">
         <v>742.49</v>
       </c>
       <c r="G75" t="n">
-        <v>3.32385976631326</v>
+        <v>3.32385805987087</v>
       </c>
       <c r="H75" t="n">
-        <v>-5.3943315251118</v>
+        <v>-5.39433195093671</v>
       </c>
       <c r="I75" t="n">
-        <v>178.161900579518</v>
+        <v>178.161900666382</v>
       </c>
       <c r="J75" t="n">
         <v>742.49</v>
       </c>
       <c r="K75" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="76">
@@ -6439,31 +6439,31 @@
         <v>24.7243859880522</v>
       </c>
       <c r="C76" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
       <c r="D76" t="n">
-        <v>183.93792184483</v>
+        <v>183.937922330922</v>
       </c>
       <c r="E76" t="n">
-        <v>739.166140233687</v>
+        <v>739.166141940129</v>
       </c>
       <c r="F76" t="n">
         <v>742.49</v>
       </c>
       <c r="G76" t="n">
-        <v>3.32385976631326</v>
+        <v>3.32385805987087</v>
       </c>
       <c r="H76" t="n">
-        <v>2.68017175058401</v>
+        <v>2.68017116131516</v>
       </c>
       <c r="I76" t="n">
-        <v>186.618093595414</v>
+        <v>186.618093492237</v>
       </c>
       <c r="J76" t="n">
         <v>742.49</v>
       </c>
       <c r="K76" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="77">
@@ -6474,31 +6474,31 @@
         <v>26.2704156842394</v>
       </c>
       <c r="C77" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
       <c r="D77" t="n">
-        <v>188.726181222298</v>
+        <v>188.726181374736</v>
       </c>
       <c r="E77" t="n">
-        <v>739.166140233687</v>
+        <v>739.166141940129</v>
       </c>
       <c r="F77" t="n">
         <v>742.49</v>
       </c>
       <c r="G77" t="n">
-        <v>3.32385976631326</v>
+        <v>3.32385805987087</v>
       </c>
       <c r="H77" t="n">
-        <v>15.1307646839644</v>
+        <v>15.130764093124</v>
       </c>
       <c r="I77" t="n">
-        <v>203.856945906263</v>
+        <v>203.85694546786</v>
       </c>
       <c r="J77" t="n">
         <v>742.49</v>
       </c>
       <c r="K77" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="78">
@@ -6509,31 +6509,31 @@
         <v>25.0797591916903</v>
       </c>
       <c r="C78" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
       <c r="D78" t="n">
-        <v>181.944982229997</v>
+        <v>181.944982791842</v>
       </c>
       <c r="E78" t="n">
-        <v>728.944686641121</v>
+        <v>728.944688807337</v>
       </c>
       <c r="F78" t="n">
         <v>842.728</v>
       </c>
       <c r="G78" t="n">
-        <v>113.783313358879</v>
+        <v>113.783311192663</v>
       </c>
       <c r="H78" t="n">
-        <v>31.9574472750294</v>
+        <v>31.9574468444899</v>
       </c>
       <c r="I78" t="n">
-        <v>213.902429505026</v>
+        <v>213.902429636331</v>
       </c>
       <c r="J78" t="n">
         <v>842.728</v>
       </c>
       <c r="K78" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="79">
@@ -6544,31 +6544,31 @@
         <v>24.5716220485478</v>
       </c>
       <c r="C79" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
       <c r="D79" t="n">
-        <v>180.37121398564</v>
+        <v>180.371214657148</v>
       </c>
       <c r="E79" t="n">
-        <v>728.944686641121</v>
+        <v>728.944688807337</v>
       </c>
       <c r="F79" t="n">
         <v>842.728</v>
       </c>
       <c r="G79" t="n">
-        <v>113.783313358879</v>
+        <v>113.783311192663</v>
       </c>
       <c r="H79" t="n">
-        <v>37.2834727373315</v>
+        <v>37.2834723265066</v>
       </c>
       <c r="I79" t="n">
-        <v>217.654686722971</v>
+        <v>217.654686983654</v>
       </c>
       <c r="J79" t="n">
         <v>842.728</v>
       </c>
       <c r="K79" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="80">
@@ -6579,31 +6579,31 @@
         <v>24.9068420844815</v>
       </c>
       <c r="C80" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
       <c r="D80" t="n">
-        <v>181.409434974883</v>
+        <v>181.409435574046</v>
       </c>
       <c r="E80" t="n">
-        <v>728.944686641121</v>
+        <v>728.944688807337</v>
       </c>
       <c r="F80" t="n">
         <v>842.728</v>
       </c>
       <c r="G80" t="n">
-        <v>113.783313358879</v>
+        <v>113.783311192663</v>
       </c>
       <c r="H80" t="n">
-        <v>31.1088410708709</v>
+        <v>31.108840539174</v>
       </c>
       <c r="I80" t="n">
-        <v>212.518276045754</v>
+        <v>212.51827611322</v>
       </c>
       <c r="J80" t="n">
         <v>842.728</v>
       </c>
       <c r="K80" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="81">
@@ -6614,31 +6614,31 @@
         <v>26.1368895656974</v>
       </c>
       <c r="C81" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
       <c r="D81" t="n">
-        <v>185.219055450601</v>
+        <v>185.219055784303</v>
       </c>
       <c r="E81" t="n">
-        <v>728.944686641121</v>
+        <v>728.944688807337</v>
       </c>
       <c r="F81" t="n">
         <v>842.728</v>
       </c>
       <c r="G81" t="n">
-        <v>113.783313358879</v>
+        <v>113.783311192663</v>
       </c>
       <c r="H81" t="n">
-        <v>13.4335522756475</v>
+        <v>13.4335514824922</v>
       </c>
       <c r="I81" t="n">
-        <v>198.652607726249</v>
+        <v>198.652607266795</v>
       </c>
       <c r="J81" t="n">
         <v>842.728</v>
       </c>
       <c r="K81" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="82">
@@ -6649,31 +6649,31 @@
         <v>22.1163428289219</v>
       </c>
       <c r="C82" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
       <c r="D82" t="n">
-        <v>195.649425365746</v>
+        <v>195.649426940417</v>
       </c>
       <c r="E82" t="n">
-        <v>798.778461389387</v>
+        <v>798.778466560567</v>
       </c>
       <c r="F82" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="G82" t="n">
-        <v>-113.055270099494</v>
+        <v>-113.055275270674</v>
       </c>
       <c r="H82" t="n">
-        <v>-15.7423936483387</v>
+        <v>-15.7423948435388</v>
       </c>
       <c r="I82" t="n">
-        <v>179.907031717407</v>
+        <v>179.907032096878</v>
       </c>
       <c r="J82" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="K82" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="83">
@@ -6684,31 +6684,31 @@
         <v>24.225607013601</v>
       </c>
       <c r="C83" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
       <c r="D83" t="n">
-        <v>202.182096786454</v>
+        <v>202.182097905917</v>
       </c>
       <c r="E83" t="n">
-        <v>798.778461389387</v>
+        <v>798.778466560567</v>
       </c>
       <c r="F83" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="G83" t="n">
-        <v>-113.055270099494</v>
+        <v>-113.055275270674</v>
       </c>
       <c r="H83" t="n">
-        <v>-32.4213415685471</v>
+        <v>-32.4213429636031</v>
       </c>
       <c r="I83" t="n">
-        <v>169.760755217907</v>
+        <v>169.760754942314</v>
       </c>
       <c r="J83" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="K83" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="84">
@@ -6719,31 +6719,31 @@
         <v>23.3046400646644</v>
       </c>
       <c r="C84" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
       <c r="D84" t="n">
-        <v>199.329739784218</v>
+        <v>199.329741102438</v>
       </c>
       <c r="E84" t="n">
-        <v>798.778461389387</v>
+        <v>798.778466560567</v>
       </c>
       <c r="F84" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="G84" t="n">
-        <v>-113.055270099494</v>
+        <v>-113.055275270674</v>
       </c>
       <c r="H84" t="n">
-        <v>-36.6032914849777</v>
+        <v>-36.6032928777007</v>
       </c>
       <c r="I84" t="n">
-        <v>162.72644829924</v>
+        <v>162.726448224737</v>
       </c>
       <c r="J84" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="K84" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="85">
@@ -6754,31 +6754,31 @@
         <v>24.0432133744899</v>
       </c>
       <c r="C85" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
       <c r="D85" t="n">
-        <v>201.617199452969</v>
+        <v>201.617200611795</v>
       </c>
       <c r="E85" t="n">
-        <v>798.778461389387</v>
+        <v>798.778466560567</v>
       </c>
       <c r="F85" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="G85" t="n">
-        <v>-113.055270099494</v>
+        <v>-113.055275270674</v>
       </c>
       <c r="H85" t="n">
-        <v>-28.2882433976304</v>
+        <v>-28.2882445858316</v>
       </c>
       <c r="I85" t="n">
-        <v>173.328956055339</v>
+        <v>173.328956025963</v>
       </c>
       <c r="J85" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="K85" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="86">
@@ -6789,31 +6789,31 @@
         <v>22.9199205166214</v>
       </c>
       <c r="C86" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
       <c r="D86" t="n">
-        <v>166.571756800558</v>
+        <v>166.571757382443</v>
       </c>
       <c r="E86" t="n">
-        <v>665.258203214969</v>
+        <v>665.2582056142</v>
       </c>
       <c r="F86" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="G86" t="n">
-        <v>49.6556506639536</v>
+        <v>49.6556482647231</v>
       </c>
       <c r="H86" t="n">
-        <v>-7.47619730650529</v>
+        <v>-7.47619808799581</v>
       </c>
       <c r="I86" t="n">
-        <v>159.095559494053</v>
+        <v>159.095559294447</v>
       </c>
       <c r="J86" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="K86" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="87">
@@ -6824,31 +6824,31 @@
         <v>22.1903787476254</v>
       </c>
       <c r="C87" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
       <c r="D87" t="n">
-        <v>164.312269013703</v>
+        <v>164.312269753033</v>
       </c>
       <c r="E87" t="n">
-        <v>665.258203214969</v>
+        <v>665.2582056142</v>
       </c>
       <c r="F87" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="G87" t="n">
-        <v>49.6556506639536</v>
+        <v>49.6556482647231</v>
       </c>
       <c r="H87" t="n">
-        <v>8.80466511894228</v>
+        <v>8.80466457280917</v>
       </c>
       <c r="I87" t="n">
-        <v>173.116934132645</v>
+        <v>173.116934325842</v>
       </c>
       <c r="J87" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="K87" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="88">
@@ -6859,31 +6859,31 @@
         <v>22.5186739517877</v>
       </c>
       <c r="C88" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
       <c r="D88" t="n">
-        <v>165.329042878904</v>
+        <v>165.329043547384</v>
       </c>
       <c r="E88" t="n">
-        <v>665.258203214969</v>
+        <v>665.2582056142</v>
       </c>
       <c r="F88" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="G88" t="n">
-        <v>49.6556506639536</v>
+        <v>49.6556482647231</v>
       </c>
       <c r="H88" t="n">
-        <v>20.5543438787123</v>
+        <v>20.5543433965834</v>
       </c>
       <c r="I88" t="n">
-        <v>185.883386757617</v>
+        <v>185.883386943967</v>
       </c>
       <c r="J88" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="K88" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="89">
@@ -6894,31 +6894,31 @@
         <v>23.7185229116645</v>
       </c>
       <c r="C89" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
       <c r="D89" t="n">
-        <v>169.045134521804</v>
+        <v>169.045134931339</v>
       </c>
       <c r="E89" t="n">
-        <v>665.258203214969</v>
+        <v>665.2582056142</v>
       </c>
       <c r="F89" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="G89" t="n">
-        <v>49.6556506639536</v>
+        <v>49.6556482647231</v>
       </c>
       <c r="H89" t="n">
-        <v>27.7728389728048</v>
+        <v>27.7728383833268</v>
       </c>
       <c r="I89" t="n">
-        <v>196.817973494608</v>
+        <v>196.817973314666</v>
       </c>
       <c r="J89" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="K89" t="n">
-        <v>0.000000000000454747350886464</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="90">
@@ -6929,25 +6929,25 @@
         <v>21.5190468048165</v>
       </c>
       <c r="C90" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
       <c r="D90" t="n">
-        <v>170.735436446048</v>
+        <v>170.735437338026</v>
       </c>
       <c r="E90" t="n">
-        <v>684.972584159691</v>
+        <v>684.972587586088</v>
       </c>
       <c r="F90" t="n">
         <v>767.424752018039</v>
       </c>
       <c r="G90" t="n">
-        <v>82.452167858348</v>
+        <v>82.4521644319509</v>
       </c>
       <c r="H90" t="n">
-        <v>30.4601504012197</v>
+        <v>30.4601495330394</v>
       </c>
       <c r="I90" t="n">
-        <v>201.195586847268</v>
+        <v>201.195586871065</v>
       </c>
       <c r="J90" t="n">
         <v>767.424752018039</v>
@@ -6964,25 +6964,25 @@
         <v>21.1510850813716</v>
       </c>
       <c r="C91" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
       <c r="D91" t="n">
-        <v>169.595810100462</v>
+        <v>169.59581107185</v>
       </c>
       <c r="E91" t="n">
-        <v>684.972584159691</v>
+        <v>684.972587586088</v>
       </c>
       <c r="F91" t="n">
         <v>767.424752018039</v>
       </c>
       <c r="G91" t="n">
-        <v>82.452167858348</v>
+        <v>82.4521644319509</v>
       </c>
       <c r="H91" t="n">
-        <v>27.5962315979327</v>
+        <v>27.5962306229039</v>
       </c>
       <c r="I91" t="n">
-        <v>197.192041698394</v>
+        <v>197.192041694754</v>
       </c>
       <c r="J91" t="n">
         <v>767.424752018039</v>
@@ -6999,25 +6999,25 @@
         <v>21.5583450125892</v>
       </c>
       <c r="C92" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
       <c r="D92" t="n">
-        <v>170.857148216753</v>
+        <v>170.857149100249</v>
       </c>
       <c r="E92" t="n">
-        <v>684.972584159691</v>
+        <v>684.972587586088</v>
       </c>
       <c r="F92" t="n">
         <v>767.424752018039</v>
       </c>
       <c r="G92" t="n">
-        <v>82.452167858348</v>
+        <v>82.4521644319509</v>
       </c>
       <c r="H92" t="n">
-        <v>19.1810825629437</v>
+        <v>19.1810816529201</v>
       </c>
       <c r="I92" t="n">
-        <v>190.038230779697</v>
+        <v>190.038230753169</v>
       </c>
       <c r="J92" t="n">
         <v>767.424752018039</v>
@@ -7034,25 +7034,25 @@
         <v>22.5034259342775</v>
       </c>
       <c r="C93" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
       <c r="D93" t="n">
-        <v>173.784189396428</v>
+        <v>173.784190075963</v>
       </c>
       <c r="E93" t="n">
-        <v>684.972584159691</v>
+        <v>684.972587586088</v>
       </c>
       <c r="F93" t="n">
         <v>767.424752018039</v>
       </c>
       <c r="G93" t="n">
-        <v>82.452167858348</v>
+        <v>82.4521644319509</v>
       </c>
       <c r="H93" t="n">
-        <v>5.21470329625282</v>
+        <v>5.21470262308825</v>
       </c>
       <c r="I93" t="n">
-        <v>178.998892692681</v>
+        <v>178.998892699051</v>
       </c>
       <c r="J93" t="n">
         <v>767.424752018039</v>
@@ -7066,28 +7066,28 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>25.5840539283816</v>
+        <v>25.5840539196353</v>
       </c>
       <c r="C94" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
       <c r="D94" t="n">
-        <v>198.910649438671</v>
+        <v>198.910649424295</v>
       </c>
       <c r="E94" t="n">
-        <v>800.083873991616</v>
+        <v>800.083873618929</v>
       </c>
       <c r="F94" t="n">
         <v>674.560615938681</v>
       </c>
       <c r="G94" t="n">
-        <v>-125.523258052936</v>
+        <v>-125.523257680248</v>
       </c>
       <c r="H94" t="n">
-        <v>-14.30290620214</v>
+        <v>-14.3029064665918</v>
       </c>
       <c r="I94" t="n">
-        <v>184.607743236531</v>
+        <v>184.607742957704</v>
       </c>
       <c r="J94" t="n">
         <v>674.560615938682</v>
@@ -7101,28 +7101,28 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>26.4637591575308</v>
+        <v>26.463759148534</v>
       </c>
       <c r="C95" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
       <c r="D95" t="n">
-        <v>201.635213412616</v>
+        <v>201.635213207613</v>
       </c>
       <c r="E95" t="n">
-        <v>800.083873991616</v>
+        <v>800.083873618929</v>
       </c>
       <c r="F95" t="n">
         <v>674.560615938681</v>
       </c>
       <c r="G95" t="n">
-        <v>-125.523258052936</v>
+        <v>-125.523257680248</v>
       </c>
       <c r="H95" t="n">
-        <v>-28.9411133259346</v>
+        <v>-28.9411132838518</v>
       </c>
       <c r="I95" t="n">
-        <v>172.694100086681</v>
+        <v>172.694099923761</v>
       </c>
       <c r="J95" t="n">
         <v>674.560615938682</v>
@@ -7136,28 +7136,28 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>22.2804097195315</v>
+        <v>22.280409710173</v>
       </c>
       <c r="C96" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
       <c r="D96" t="n">
-        <v>188.678824395557</v>
+        <v>188.678825092258</v>
       </c>
       <c r="E96" t="n">
-        <v>800.083873991616</v>
+        <v>800.083873618929</v>
       </c>
       <c r="F96" t="n">
         <v>674.560615938681</v>
       </c>
       <c r="G96" t="n">
-        <v>-125.523258052936</v>
+        <v>-125.523257680248</v>
       </c>
       <c r="H96" t="n">
-        <v>-38.699918075131</v>
+        <v>-38.6999178286919</v>
       </c>
       <c r="I96" t="n">
-        <v>149.978906320426</v>
+        <v>149.978907263566</v>
       </c>
       <c r="J96" t="n">
         <v>674.560615938682</v>
@@ -7171,28 +7171,28 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>29.4419889408751</v>
+        <v>29.4419889311474</v>
       </c>
       <c r="C97" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
       <c r="D97" t="n">
-        <v>210.859186744773</v>
+        <v>210.859185894763</v>
       </c>
       <c r="E97" t="n">
-        <v>800.083873991616</v>
+        <v>800.083873618929</v>
       </c>
       <c r="F97" t="n">
         <v>674.560615938681</v>
       </c>
       <c r="G97" t="n">
-        <v>-125.523258052936</v>
+        <v>-125.523257680248</v>
       </c>
       <c r="H97" t="n">
-        <v>-43.5793204497292</v>
+        <v>-43.5793201011119</v>
       </c>
       <c r="I97" t="n">
-        <v>167.279866295044</v>
+        <v>167.279865793651</v>
       </c>
       <c r="J97" t="n">
         <v>674.560615938682</v>
@@ -7231,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>6.58158653671646</v>
+        <v>6.58158660432072</v>
       </c>
       <c r="C2" t="n">
-        <v>9.43429602010574</v>
+        <v>9.43429602011821</v>
       </c>
       <c r="D2" t="n">
-        <v>-186.115116197947</v>
+        <v>-186.115112664519</v>
       </c>
     </row>
     <row r="3">
@@ -7245,13 +7245,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8638342557031</v>
+        <v>16.8638338028851</v>
       </c>
       <c r="C3" t="n">
         <v>12.1937909319798</v>
       </c>
       <c r="D3" t="n">
-        <v>-186.115116197947</v>
+        <v>-186.115112664519</v>
       </c>
     </row>
     <row r="4">
@@ -7259,13 +7259,13 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>-6.71784936923454</v>
+        <v>-6.7178477866303</v>
       </c>
       <c r="C4" t="n">
-        <v>3.45889465139056</v>
+        <v>3.45889465139194</v>
       </c>
       <c r="D4" t="n">
-        <v>-186.115116197947</v>
+        <v>-186.115112664519</v>
       </c>
     </row>
     <row r="5">
@@ -7273,13 +7273,13 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>41.619732411125</v>
+        <v>41.6197312137347</v>
       </c>
       <c r="C5" t="n">
-        <v>17.3848086073763</v>
+        <v>17.3848086073612</v>
       </c>
       <c r="D5" t="n">
-        <v>-186.115116197947</v>
+        <v>-186.115112664519</v>
       </c>
     </row>
     <row r="6">
@@ -7287,13 +7287,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.18604899490934</v>
+        <v>4.18604902225504</v>
       </c>
       <c r="C6" t="n">
-        <v>9.45592239729289</v>
+        <v>9.45592239730524</v>
       </c>
       <c r="D6" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
     </row>
     <row r="7">
@@ -7301,13 +7301,13 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>18.3346200893177</v>
+        <v>18.3346197356864</v>
       </c>
       <c r="C7" t="n">
         <v>12.1917626444412</v>
       </c>
       <c r="D7" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
     </row>
     <row r="8">
@@ -7315,13 +7315,13 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.27531814589013</v>
+        <v>-4.27531649850542</v>
       </c>
       <c r="C8" t="n">
-        <v>3.46832106816347</v>
+        <v>3.46832106816489</v>
       </c>
       <c r="D8" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
     </row>
     <row r="9">
@@ -7329,13 +7329,13 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>41.8557362630293</v>
+        <v>41.8557349419305</v>
       </c>
       <c r="C9" t="n">
-        <v>17.3491999352625</v>
+        <v>17.3491999352476</v>
       </c>
       <c r="D9" t="n">
-        <v>-271.071824493194</v>
+        <v>-271.071823077797</v>
       </c>
     </row>
     <row r="10">
@@ -7343,13 +7343,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>19.8261309224413</v>
+        <v>19.8261312377309</v>
       </c>
       <c r="C10" t="n">
-        <v>9.49805318041849</v>
+        <v>9.4980531804306</v>
       </c>
       <c r="D10" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
     </row>
     <row r="11">
@@ -7357,13 +7357,13 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>29.0387584707472</v>
+        <v>29.0387581516253</v>
       </c>
       <c r="C11" t="n">
         <v>12.1810595075462</v>
       </c>
       <c r="D11" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
     </row>
     <row r="12">
@@ -7371,13 +7371,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>2.03084525940147</v>
+        <v>2.03084677078762</v>
       </c>
       <c r="C12" t="n">
-        <v>3.48224738554993</v>
+        <v>3.48224738555144</v>
       </c>
       <c r="D12" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
     </row>
     <row r="13">
@@ -7385,13 +7385,13 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>43.7691199353152</v>
+        <v>43.7691184277618</v>
       </c>
       <c r="C13" t="n">
-        <v>17.2931976179645</v>
+        <v>17.2931976179497</v>
       </c>
       <c r="D13" t="n">
-        <v>-269.297649090204</v>
+        <v>-269.297647676228</v>
       </c>
     </row>
     <row r="14">
@@ -7399,13 +7399,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>25.7978288527819</v>
+        <v>25.7978291092536</v>
       </c>
       <c r="C14" t="n">
-        <v>9.53219834760066</v>
+        <v>9.53219834761259</v>
       </c>
       <c r="D14" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
     </row>
     <row r="15">
@@ -7413,13 +7413,13 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>34.4018765715641</v>
+        <v>34.4018762396655</v>
       </c>
       <c r="C15" t="n">
-        <v>12.1448667467561</v>
+        <v>12.1448667467563</v>
       </c>
       <c r="D15" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
     </row>
     <row r="16">
@@ -7427,13 +7427,13 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>10.498648147361</v>
+        <v>10.4986496730368</v>
       </c>
       <c r="C16" t="n">
-        <v>3.44863939509929</v>
+        <v>3.44863939510121</v>
       </c>
       <c r="D16" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
     </row>
     <row r="17">
@@ -7441,13 +7441,13 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>58.5536909125837</v>
+        <v>58.553689462335</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1732760388017</v>
+        <v>17.1732760387875</v>
       </c>
       <c r="D17" t="n">
-        <v>-234.700902337555</v>
+        <v>-234.700900925877</v>
       </c>
     </row>
     <row r="18">
@@ -7455,13 +7455,13 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>52.4105899208566</v>
+        <v>52.410590135374</v>
       </c>
       <c r="C18" t="n">
-        <v>9.94389849690385</v>
+        <v>9.94389849691342</v>
       </c>
       <c r="D18" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
     </row>
     <row r="19">
@@ -7469,13 +7469,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>65.9391173284113</v>
+        <v>65.9391170690309</v>
       </c>
       <c r="C19" t="n">
-        <v>11.974917971407</v>
+        <v>11.9749179714078</v>
       </c>
       <c r="D19" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
     </row>
     <row r="20">
@@ -7483,13 +7483,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>45.781350591238</v>
+        <v>45.7813521207111</v>
       </c>
       <c r="C20" t="n">
-        <v>3.39658042339941</v>
+        <v>3.39658042340207</v>
       </c>
       <c r="D20" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
     </row>
     <row r="21">
@@ -7497,13 +7497,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>93.3353744685093</v>
+        <v>93.3353729838994</v>
       </c>
       <c r="C21" t="n">
-        <v>16.9482255202062</v>
+        <v>16.9482255201931</v>
       </c>
       <c r="D21" t="n">
-        <v>-199.631869296403</v>
+        <v>-199.631867918304</v>
       </c>
     </row>
     <row r="22">
@@ -7511,13 +7511,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>107.655509496815</v>
+        <v>107.655509756284</v>
       </c>
       <c r="C22" t="n">
-        <v>10.3705444540554</v>
+        <v>10.3705444540626</v>
       </c>
       <c r="D22" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
     </row>
     <row r="23">
@@ -7525,13 +7525,13 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>110.880142462146</v>
+        <v>110.880142275346</v>
       </c>
       <c r="C23" t="n">
-        <v>11.8241962568536</v>
+        <v>11.824196256855</v>
       </c>
       <c r="D23" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
     </row>
     <row r="24">
@@ -7539,13 +7539,13 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>77.3693880127336</v>
+        <v>77.3693895029116</v>
       </c>
       <c r="C24" t="n">
-        <v>3.36455201043794</v>
+        <v>3.36455201044131</v>
       </c>
       <c r="D24" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
     </row>
     <row r="25">
@@ -7553,13 +7553,13 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>105.472784321288</v>
+        <v>105.472782758441</v>
       </c>
       <c r="C25" t="n">
-        <v>16.7466388833034</v>
+        <v>16.7466388832914</v>
       </c>
       <c r="D25" t="n">
-        <v>-71.3079726876238</v>
+        <v>-71.307971317156</v>
       </c>
     </row>
     <row r="26">
@@ -7567,13 +7567,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>101.039564467368</v>
+        <v>101.039564517578</v>
       </c>
       <c r="C26" t="n">
-        <v>10.7408214718168</v>
+        <v>10.7408214718216</v>
       </c>
       <c r="D26" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
     </row>
     <row r="27">
@@ -7581,13 +7581,13 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>90.9495597481429</v>
+        <v>90.9495594930202</v>
       </c>
       <c r="C27" t="n">
-        <v>11.6466418714765</v>
+        <v>11.646641871478</v>
       </c>
       <c r="D27" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
     </row>
     <row r="28">
@@ -7595,13 +7595,13 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>59.7351165736948</v>
+        <v>59.7351180080814</v>
       </c>
       <c r="C28" t="n">
-        <v>3.63961093490175</v>
+        <v>3.63961093490583</v>
       </c>
       <c r="D28" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
     </row>
     <row r="29">
@@ -7609,13 +7609,13 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>98.4981242831451</v>
+        <v>98.4981230536709</v>
       </c>
       <c r="C29" t="n">
-        <v>16.1346402602008</v>
+        <v>16.1346402601908</v>
       </c>
       <c r="D29" t="n">
-        <v>72.4723821051694</v>
+        <v>72.4723834847681</v>
       </c>
     </row>
     <row r="30">
@@ -7623,13 +7623,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>77.8720127441485</v>
+        <v>77.872012505586</v>
       </c>
       <c r="C30" t="n">
-        <v>11.1816037184858</v>
+        <v>11.1816037184879</v>
       </c>
       <c r="D30" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
     </row>
     <row r="31">
@@ -7637,13 +7637,13 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>83.0527042663316</v>
+        <v>83.0527040338147</v>
       </c>
       <c r="C31" t="n">
-        <v>11.527526374305</v>
+        <v>11.5275263743065</v>
       </c>
       <c r="D31" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
     </row>
     <row r="32">
@@ -7651,13 +7651,13 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>61.2120339387369</v>
+        <v>61.2120354021274</v>
       </c>
       <c r="C32" t="n">
-        <v>3.93494656467131</v>
+        <v>3.93494656467575</v>
       </c>
       <c r="D32" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
     </row>
     <row r="33">
@@ -7665,13 +7665,13 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>96.179799395674</v>
+        <v>96.1797984033627</v>
       </c>
       <c r="C33" t="n">
-        <v>15.4707682208692</v>
+        <v>15.4707682208608</v>
       </c>
       <c r="D33" t="n">
-        <v>21.7635822996747</v>
+        <v>21.7635836481479</v>
       </c>
     </row>
     <row r="34">
@@ -7679,13 +7679,13 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>72.0321175204987</v>
+        <v>72.0321173705735</v>
       </c>
       <c r="C34" t="n">
-        <v>11.0979545641297</v>
+        <v>11.0979545641313</v>
       </c>
       <c r="D34" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
     </row>
     <row r="35">
@@ -7693,13 +7693,13 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>69.7894290495669</v>
+        <v>69.7894289025229</v>
       </c>
       <c r="C35" t="n">
-        <v>11.1768869325754</v>
+        <v>11.1768869325764</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
     </row>
     <row r="36">
@@ -7707,13 +7707,13 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>52.2629558351695</v>
+        <v>52.2629568147169</v>
       </c>
       <c r="C36" t="n">
-        <v>6.09246182598753</v>
+        <v>6.09246182599038</v>
       </c>
       <c r="D36" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
     </row>
     <row r="37">
@@ -7721,13 +7721,13 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>75.5991680398029</v>
+        <v>75.5991673572246</v>
       </c>
       <c r="C37" t="n">
-        <v>13.9732105882977</v>
+        <v>13.9732105882918</v>
       </c>
       <c r="D37" t="n">
-        <v>-9.99707086337543</v>
+        <v>-9.99706952501475</v>
       </c>
     </row>
     <row r="38">
@@ -7735,13 +7735,13 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>54.0987427324352</v>
+        <v>54.0987426100509</v>
       </c>
       <c r="C38" t="n">
-        <v>10.864533561075</v>
+        <v>10.8645335610762</v>
       </c>
       <c r="D38" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
     </row>
     <row r="39">
@@ -7749,13 +7749,13 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>55.9757687016194</v>
+        <v>55.9757686470956</v>
       </c>
       <c r="C39" t="n">
-        <v>10.7664038770365</v>
+        <v>10.766403877037</v>
       </c>
       <c r="D39" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
     </row>
     <row r="40">
@@ -7763,13 +7763,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>52.9657771215292</v>
+        <v>52.9657776513523</v>
       </c>
       <c r="C40" t="n">
-        <v>8.26874568961225</v>
+        <v>8.26874568961349</v>
       </c>
       <c r="D40" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
     </row>
     <row r="41">
@@ -7777,13 +7777,13 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>73.5346093981822</v>
+        <v>73.534609045267</v>
       </c>
       <c r="C41" t="n">
-        <v>12.5625891146203</v>
+        <v>12.562589114617</v>
       </c>
       <c r="D41" t="n">
-        <v>-59.3288777401798</v>
+        <v>-59.3288763531168</v>
       </c>
     </row>
     <row r="42">
@@ -7791,13 +7791,13 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>70.0131013620881</v>
+        <v>70.0131013273525</v>
       </c>
       <c r="C42" t="n">
-        <v>10.7788841220817</v>
+        <v>10.7788841220824</v>
       </c>
       <c r="D42" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
     </row>
     <row r="43">
@@ -7805,13 +7805,13 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>76.0026009775156</v>
+        <v>76.0026009989905</v>
       </c>
       <c r="C43" t="n">
-        <v>10.585067784036</v>
+        <v>10.5850677840361</v>
       </c>
       <c r="D43" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
     </row>
     <row r="44">
@@ -7819,13 +7819,13 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>74.8368914848983</v>
+        <v>74.8368918082509</v>
       </c>
       <c r="C44" t="n">
-        <v>9.12229912279982</v>
+        <v>9.12229912280024</v>
       </c>
       <c r="D44" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
     </row>
     <row r="45">
@@ -7833,13 +7833,13 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>83.4641296838501</v>
+        <v>83.4641293737582</v>
       </c>
       <c r="C45" t="n">
-        <v>11.8627866471977</v>
+        <v>11.8627866471957</v>
       </c>
       <c r="D45" t="n">
-        <v>-92.8147519606926</v>
+        <v>-92.8147505473524</v>
       </c>
     </row>
     <row r="46">
@@ -7847,13 +7847,13 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>92.9176549784991</v>
+        <v>92.9176550605472</v>
       </c>
       <c r="C46" t="n">
-        <v>10.7822885416373</v>
+        <v>10.7822885416376</v>
       </c>
       <c r="D46" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
     </row>
     <row r="47">
@@ -7861,13 +7861,13 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>89.7439272622113</v>
+        <v>89.743927341452</v>
       </c>
       <c r="C47" t="n">
-        <v>10.443831487176</v>
+        <v>10.4438314871757</v>
       </c>
       <c r="D47" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
     </row>
     <row r="48">
@@ -7875,13 +7875,13 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>87.2107700218772</v>
+        <v>87.210770114918</v>
       </c>
       <c r="C48" t="n">
-        <v>10.0022276754269</v>
+        <v>10.0022276754265</v>
       </c>
       <c r="D48" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
     </row>
     <row r="49">
@@ -7889,13 +7889,13 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>90.7396316368671</v>
+        <v>90.7396313825376</v>
       </c>
       <c r="C49" t="n">
-        <v>11.2079504057885</v>
+        <v>11.2079504057878</v>
       </c>
       <c r="D49" t="n">
-        <v>-24.7222239099404</v>
+        <v>-24.7222225210366</v>
       </c>
     </row>
     <row r="50">
@@ -7903,13 +7903,13 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>103.363080574898</v>
+        <v>103.363080509089</v>
       </c>
       <c r="C50" t="n">
         <v>10.8200506299549</v>
       </c>
       <c r="D50" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
     </row>
     <row r="51">
@@ -7917,13 +7917,13 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>104.622847661863</v>
+        <v>104.62284763583</v>
       </c>
       <c r="C51" t="n">
         <v>10.5382561440265</v>
       </c>
       <c r="D51" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
     </row>
     <row r="52">
@@ -7931,13 +7931,13 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>108.250028001507</v>
+        <v>108.250028018072</v>
       </c>
       <c r="C52" t="n">
         <v>10.5759503785478</v>
       </c>
       <c r="D52" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
     </row>
     <row r="53">
@@ -7945,13 +7945,13 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>114.053872347012</v>
+        <v>114.053872422289</v>
       </c>
       <c r="C53" t="n">
         <v>10.8715443558012</v>
       </c>
       <c r="D53" t="n">
-        <v>31.3027793237491</v>
+        <v>31.3027807314851</v>
       </c>
     </row>
     <row r="54">
@@ -7959,13 +7959,13 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>142.767591641887</v>
+        <v>142.767591716327</v>
       </c>
       <c r="C54" t="n">
         <v>12.9570570133416</v>
       </c>
       <c r="D54" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
     </row>
     <row r="55">
@@ -7973,13 +7973,13 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>143.873261181657</v>
+        <v>143.873261370088</v>
       </c>
       <c r="C55" t="n">
         <v>12.7543914906828</v>
       </c>
       <c r="D55" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
     </row>
     <row r="56">
@@ -7987,13 +7987,13 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>141.957500679914</v>
+        <v>141.95750075299</v>
       </c>
       <c r="C56" t="n">
         <v>13.0397525391501</v>
       </c>
       <c r="D56" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
     </row>
     <row r="57">
@@ -8001,13 +8001,13 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>137.943384607456</v>
+        <v>137.943384271508</v>
       </c>
       <c r="C57" t="n">
         <v>14.1111817707667</v>
       </c>
       <c r="D57" t="n">
-        <v>99.8362228921252</v>
+        <v>99.8362243796026</v>
       </c>
     </row>
     <row r="58">
@@ -8015,13 +8015,13 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>150.371070847122</v>
+        <v>150.371071094008</v>
       </c>
       <c r="C58" t="n">
         <v>14.0378160523454</v>
       </c>
       <c r="D58" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
     </row>
     <row r="59">
@@ -8029,13 +8029,13 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>137.149487385303</v>
+        <v>137.149487850753</v>
       </c>
       <c r="C59" t="n">
         <v>12.2062827701092</v>
       </c>
       <c r="D59" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
     </row>
     <row r="60">
@@ -8043,13 +8043,13 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>141.854054651498</v>
+        <v>141.854054512268</v>
       </c>
       <c r="C60" t="n">
         <v>14.7690861061654</v>
       </c>
       <c r="D60" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
     </row>
     <row r="61">
@@ -8057,13 +8057,13 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>150.219212324832</v>
+        <v>150.219211751726</v>
       </c>
       <c r="C61" t="n">
         <v>17.1201723465891</v>
       </c>
       <c r="D61" t="n">
-        <v>204.941563978215</v>
+        <v>204.941567636041</v>
       </c>
     </row>
     <row r="62">
@@ -8071,13 +8071,13 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>153.119136991412</v>
+        <v>153.119136992031</v>
       </c>
       <c r="C62" t="n">
         <v>16.5595286531131</v>
       </c>
       <c r="D62" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
     </row>
     <row r="63">
@@ -8085,13 +8085,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>156.315172655529</v>
+        <v>156.315172834714</v>
       </c>
       <c r="C63" t="n">
         <v>16.1236209274397</v>
       </c>
       <c r="D63" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
     </row>
     <row r="64">
@@ -8099,13 +8099,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>160.613508184391</v>
+        <v>160.613508291697</v>
       </c>
       <c r="C64" t="n">
         <v>16.3192772141769</v>
       </c>
       <c r="D64" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
     </row>
     <row r="65">
@@ -8113,13 +8113,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>167.048736568374</v>
+        <v>167.048736281263</v>
       </c>
       <c r="C65" t="n">
         <v>17.48054614363</v>
       </c>
       <c r="D65" t="n">
-        <v>201.668742858055</v>
+        <v>201.668747653429</v>
       </c>
     </row>
     <row r="66">
@@ -8127,13 +8127,13 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>175.872617592945</v>
+        <v>175.872617615248</v>
       </c>
       <c r="C66" t="n">
         <v>17.3052064617991</v>
       </c>
       <c r="D66" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
     </row>
     <row r="67">
@@ -8141,13 +8141,13 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>176.009976375092</v>
+        <v>176.009976299679</v>
       </c>
       <c r="C67" t="n">
         <v>17.4491223381665</v>
       </c>
       <c r="D67" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
     </row>
     <row r="68">
@@ -8155,13 +8155,13 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>172.822477275217</v>
+        <v>172.822477365257</v>
       </c>
       <c r="C68" t="n">
         <v>17.259954781733</v>
       </c>
       <c r="D68" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
     </row>
     <row r="69">
@@ -8169,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>174.283382117502</v>
+        <v>174.283382080572</v>
       </c>
       <c r="C69" t="n">
         <v>19.3121047561699</v>
       </c>
       <c r="D69" t="n">
-        <v>233.311602994784</v>
+        <v>233.311609592121</v>
       </c>
     </row>
     <row r="70">
@@ -8183,13 +8183,13 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>189.814011609322</v>
+        <v>189.814011664359</v>
       </c>
       <c r="C70" t="n">
         <v>23.1154258857424</v>
       </c>
       <c r="D70" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
     </row>
     <row r="71">
@@ -8197,13 +8197,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>186.667850816256</v>
+        <v>186.667850961659</v>
       </c>
       <c r="C71" t="n">
         <v>23.8949714243776</v>
       </c>
       <c r="D71" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
     </row>
     <row r="72">
@@ -8211,13 +8211,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>179.987835255298</v>
+        <v>179.987835602129</v>
       </c>
       <c r="C72" t="n">
         <v>23.0079858138554</v>
       </c>
       <c r="D72" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
     </row>
     <row r="73">
@@ -8225,13 +8225,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>187.089740141874</v>
+        <v>187.089739594603</v>
       </c>
       <c r="C73" t="n">
         <v>26.0453739290296</v>
       </c>
       <c r="D73" t="n">
-        <v>280.202800958392</v>
+        <v>280.202808601004</v>
       </c>
     </row>
     <row r="74">
@@ -8239,13 +8239,13 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>173.853059918806</v>
+        <v>173.853060373522</v>
       </c>
       <c r="C74" t="n">
         <v>24.404052044643</v>
       </c>
       <c r="D74" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
     </row>
     <row r="75">
@@ -8253,13 +8253,13 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>178.161900579518</v>
+        <v>178.161900666382</v>
       </c>
       <c r="C75" t="n">
         <v>24.6011462830655</v>
       </c>
       <c r="D75" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
     </row>
     <row r="76">
@@ -8267,13 +8267,13 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>186.618093595414</v>
+        <v>186.618093492237</v>
       </c>
       <c r="C76" t="n">
         <v>24.7243859880522</v>
       </c>
       <c r="D76" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
     </row>
     <row r="77">
@@ -8281,13 +8281,13 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>203.856945906263</v>
+        <v>203.85694546786</v>
       </c>
       <c r="C77" t="n">
         <v>26.2704156842394</v>
       </c>
       <c r="D77" t="n">
-        <v>248.15886785686</v>
+        <v>248.158880838138</v>
       </c>
     </row>
     <row r="78">
@@ -8295,13 +8295,13 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>213.902429505026</v>
+        <v>213.902429636331</v>
       </c>
       <c r="C78" t="n">
         <v>25.0797591916903</v>
       </c>
       <c r="D78" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
     </row>
     <row r="79">
@@ -8309,13 +8309,13 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>217.654686722971</v>
+        <v>217.654686983654</v>
       </c>
       <c r="C79" t="n">
         <v>24.5716220485478</v>
       </c>
       <c r="D79" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
     </row>
     <row r="80">
@@ -8323,13 +8323,13 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>212.518276045754</v>
+        <v>212.51827611322</v>
       </c>
       <c r="C80" t="n">
         <v>24.9068420844815</v>
       </c>
       <c r="D80" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
     </row>
     <row r="81">
@@ -8337,13 +8337,13 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>198.652607726249</v>
+        <v>198.652607266795</v>
       </c>
       <c r="C81" t="n">
         <v>26.1368895656974</v>
       </c>
       <c r="D81" t="n">
-        <v>234.898362650721</v>
+        <v>234.898376481493</v>
       </c>
     </row>
     <row r="82">
@@ -8351,13 +8351,13 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>179.907031717407</v>
+        <v>179.907032096878</v>
       </c>
       <c r="C82" t="n">
         <v>22.1163428289219</v>
       </c>
       <c r="D82" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
     </row>
     <row r="83">
@@ -8365,13 +8365,13 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>169.760755217907</v>
+        <v>169.760754942314</v>
       </c>
       <c r="C83" t="n">
         <v>24.225607013601</v>
       </c>
       <c r="D83" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
     </row>
     <row r="84">
@@ -8379,13 +8379,13 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>162.72644829924</v>
+        <v>162.726448224737</v>
       </c>
       <c r="C84" t="n">
         <v>23.3046400646644</v>
       </c>
       <c r="D84" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
     </row>
     <row r="85">
@@ -8393,13 +8393,13 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>173.328956055339</v>
+        <v>173.328956025963</v>
       </c>
       <c r="C85" t="n">
         <v>24.0432133744899</v>
       </c>
       <c r="D85" t="n">
-        <v>332.98350567511</v>
+        <v>332.983519655897</v>
       </c>
     </row>
     <row r="86">
@@ -8407,13 +8407,13 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>159.095559494053</v>
+        <v>159.095559294447</v>
       </c>
       <c r="C86" t="n">
         <v>22.9199205166214</v>
       </c>
       <c r="D86" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
     </row>
     <row r="87">
@@ -8421,13 +8421,13 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>173.116934132645</v>
+        <v>173.116934325842</v>
       </c>
       <c r="C87" t="n">
         <v>22.1903787476254</v>
       </c>
       <c r="D87" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
     </row>
     <row r="88">
@@ -8435,13 +8435,13 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>185.883386757617</v>
+        <v>185.883386943967</v>
       </c>
       <c r="C88" t="n">
         <v>22.5186739517877</v>
       </c>
       <c r="D88" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
     </row>
     <row r="89">
@@ -8449,13 +8449,13 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>196.817973494608</v>
+        <v>196.817973314666</v>
       </c>
       <c r="C89" t="n">
         <v>23.7185229116645</v>
       </c>
       <c r="D89" t="n">
-        <v>197.675071561713</v>
+        <v>197.675084030659</v>
       </c>
     </row>
     <row r="90">
@@ -8463,13 +8463,13 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>201.195586847268</v>
+        <v>201.195586871065</v>
       </c>
       <c r="C90" t="n">
         <v>21.5190468048165</v>
       </c>
       <c r="D90" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
     </row>
     <row r="91">
@@ -8477,13 +8477,13 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>197.192041698394</v>
+        <v>197.192041694754</v>
       </c>
       <c r="C91" t="n">
         <v>21.1510850813716</v>
       </c>
       <c r="D91" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
     </row>
     <row r="92">
@@ -8491,13 +8491,13 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>190.038230779697</v>
+        <v>190.038230753169</v>
       </c>
       <c r="C92" t="n">
         <v>21.5583450125892</v>
       </c>
       <c r="D92" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
     </row>
     <row r="93">
@@ -8505,13 +8505,13 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>178.998892692681</v>
+        <v>178.998892699051</v>
       </c>
       <c r="C93" t="n">
         <v>22.5034259342775</v>
       </c>
       <c r="D93" t="n">
-        <v>234.120170609892</v>
+        <v>234.120182573336</v>
       </c>
     </row>
     <row r="94">
@@ -8519,13 +8519,13 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>184.607743236531</v>
+        <v>184.607742957704</v>
       </c>
       <c r="C94" t="n">
-        <v>25.5840539283816</v>
+        <v>25.5840539196353</v>
       </c>
       <c r="D94" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
     </row>
     <row r="95">
@@ -8533,13 +8533,13 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>172.694100086681</v>
+        <v>172.694099923761</v>
       </c>
       <c r="C95" t="n">
-        <v>26.4637591575308</v>
+        <v>26.463759148534</v>
       </c>
       <c r="D95" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
     </row>
     <row r="96">
@@ -8547,13 +8547,13 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>149.978906320426</v>
+        <v>149.978907263566</v>
       </c>
       <c r="C96" t="n">
-        <v>22.2804097195315</v>
+        <v>22.280409710173</v>
       </c>
       <c r="D96" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
     </row>
     <row r="97">
@@ -8561,13 +8561,13 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>167.279866295044</v>
+        <v>167.279865793651</v>
       </c>
       <c r="C97" t="n">
-        <v>29.4419889408751</v>
+        <v>29.4419889311474</v>
       </c>
       <c r="D97" t="n">
-        <v>300.926174418818</v>
+        <v>300.926185386153</v>
       </c>
     </row>
     <row r="98">
@@ -8575,13 +8575,13 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>166.48666497716</v>
+        <v>166.486665217697</v>
       </c>
       <c r="C98" t="n">
-        <v>25.931457069085</v>
+        <v>25.9314570586997</v>
       </c>
       <c r="D98" t="n">
-        <v>39.3324846851576</v>
+        <v>39.3324883166545</v>
       </c>
     </row>
     <row r="99">
@@ -8589,13 +8589,13 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>170.388451321141</v>
+        <v>170.388451293531</v>
       </c>
       <c r="C99" t="n">
-        <v>27.252662397921</v>
+        <v>27.2526623869227</v>
       </c>
       <c r="D99" t="n">
-        <v>39.1287040004663</v>
+        <v>39.1287076552146</v>
       </c>
     </row>
     <row r="100">
@@ -8603,13 +8603,13 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>158.650977331891</v>
+        <v>158.650978132251</v>
       </c>
       <c r="C100" t="n">
-        <v>23.5856741538312</v>
+        <v>23.5856741424488</v>
       </c>
       <c r="D100" t="n">
-        <v>38.7211426310837</v>
+        <v>38.7211463323348</v>
       </c>
     </row>
     <row r="101">
@@ -8617,13 +8617,13 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>178.720746952097</v>
+        <v>178.720746369567</v>
       </c>
       <c r="C101" t="n">
-        <v>30.2499849317301</v>
+        <v>30.2499849199284</v>
       </c>
       <c r="D101" t="n">
-        <v>38.1098005770098</v>
+        <v>38.109804348015</v>
       </c>
     </row>
     <row r="102">
@@ -8631,13 +8631,13 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>168.69200765167</v>
+        <v>168.692007788062</v>
       </c>
       <c r="C102" t="n">
-        <v>27.25751049652</v>
+        <v>27.2575104839305</v>
       </c>
       <c r="D102" t="n">
-        <v>37.2946778382445</v>
+        <v>37.2946817022554</v>
       </c>
     </row>
     <row r="103">
@@ -8645,13 +8645,13 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>170.353376147471</v>
+        <v>170.353376184887</v>
       </c>
       <c r="C103" t="n">
-        <v>28.0206668267677</v>
+        <v>28.0206668137277</v>
       </c>
       <c r="D103" t="n">
-        <v>36.54215924693</v>
+        <v>36.5421631939914</v>
       </c>
     </row>
     <row r="104">
@@ -8659,13 +8659,13 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>160.032405218552</v>
+        <v>160.032405987878</v>
       </c>
       <c r="C104" t="n">
-        <v>24.8961114257762</v>
+        <v>24.8961114123793</v>
       </c>
       <c r="D104" t="n">
-        <v>35.8522448030663</v>
+        <v>35.8522488232232</v>
       </c>
     </row>
     <row r="105">
@@ -8673,13 +8673,13 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>178.589140037729</v>
+        <v>178.589139522246</v>
       </c>
       <c r="C105" t="n">
-        <v>31.0767058837054</v>
+        <v>31.0767058699152</v>
       </c>
       <c r="D105" t="n">
-        <v>35.2249345066532</v>
+        <v>35.2249385899507</v>
       </c>
     </row>
     <row r="106">
@@ -8687,13 +8687,13 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>170.276514159564</v>
+        <v>170.276514225127</v>
       </c>
       <c r="C106" t="n">
-        <v>28.5628780375415</v>
+        <v>28.5628780226813</v>
       </c>
       <c r="D106" t="n">
-        <v>34.6602283576909</v>
+        <v>34.660232494174</v>
       </c>
     </row>
     <row r="107">
@@ -8701,13 +8701,13 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>170.382605505123</v>
+        <v>170.382605566025</v>
       </c>
       <c r="C107" t="n">
-        <v>28.7679787912051</v>
+        <v>28.7679787760825</v>
       </c>
       <c r="D107" t="n">
-        <v>34.0932012050712</v>
+        <v>34.0932053932477</v>
       </c>
     </row>
     <row r="108">
@@ -8715,13 +8715,13 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>161.932429467335</v>
+        <v>161.932430118163</v>
       </c>
       <c r="C108" t="n">
-        <v>26.2111374929631</v>
+        <v>26.2111374775603</v>
       </c>
       <c r="D108" t="n">
-        <v>33.5238530487941</v>
+        <v>33.5238572871718</v>
       </c>
     </row>
     <row r="109">
@@ -8729,13 +8729,13 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>179.088224439605</v>
+        <v>179.088223894483</v>
       </c>
       <c r="C109" t="n">
-        <v>31.9226327640953</v>
+        <v>31.9226327484023</v>
       </c>
       <c r="D109" t="n">
-        <v>32.9521838888596</v>
+        <v>32.9521881759465</v>
       </c>
     </row>
     <row r="110">
@@ -8743,13 +8743,13 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>172.125602280048</v>
+        <v>172.125602214255</v>
       </c>
       <c r="C110" t="n">
-        <v>29.8474904204879</v>
+        <v>29.8474904032911</v>
       </c>
       <c r="D110" t="n">
-        <v>32.3781937252677</v>
+        <v>32.3781980595716</v>
       </c>
     </row>
     <row r="111">
@@ -8757,13 +8757,13 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>174.326041402758</v>
+        <v>174.326041179765</v>
       </c>
       <c r="C111" t="n">
-        <v>30.7271956496404</v>
+        <v>30.7271956321931</v>
       </c>
       <c r="D111" t="n">
-        <v>31.8165333175774</v>
+        <v>31.8165376960058</v>
       </c>
     </row>
     <row r="112">
@@ -8771,13 +8771,13 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>160.857033297347</v>
+        <v>160.85703400677</v>
       </c>
       <c r="C112" t="n">
-        <v>26.5438462116409</v>
+        <v>26.5438461938319</v>
       </c>
       <c r="D112" t="n">
-        <v>31.2672026657887</v>
+        <v>31.2672070852491</v>
       </c>
     </row>
     <row r="113">
@@ -8785,13 +8785,13 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>182.536282321103</v>
+        <v>182.536281511811</v>
       </c>
       <c r="C113" t="n">
-        <v>33.7054254329839</v>
+        <v>33.7054254148057</v>
       </c>
       <c r="D113" t="n">
-        <v>30.7302017699016</v>
+        <v>30.7302062273016</v>
       </c>
     </row>
     <row r="114">
@@ -8799,13 +8799,13 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>171.174091135827</v>
+        <v>171.174091107399</v>
       </c>
       <c r="C114" t="n">
-        <v>30.1948935611954</v>
+        <v>30.1948935423596</v>
       </c>
       <c r="D114" t="n">
-        <v>30.2055306299161</v>
+        <v>30.2055351221632</v>
       </c>
     </row>
     <row r="115">
@@ -8813,13 +8813,13 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>174.784332469976</v>
+        <v>174.784332177757</v>
       </c>
       <c r="C115" t="n">
-        <v>31.5160988900302</v>
+        <v>31.5160988705814</v>
       </c>
       <c r="D115" t="n">
-        <v>29.6893257419247</v>
+        <v>29.6893302667087</v>
       </c>
     </row>
     <row r="116">
@@ -8827,13 +8827,13 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>162.953376023652</v>
+        <v>162.953376542831</v>
       </c>
       <c r="C116" t="n">
-        <v>27.8491106459462</v>
+        <v>27.8491106261133</v>
       </c>
       <c r="D116" t="n">
-        <v>29.1815871059276</v>
+        <v>29.1815916609381</v>
       </c>
     </row>
     <row r="117">
@@ -8841,13 +8841,13 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>183.127725739494</v>
+        <v>183.127724838288</v>
       </c>
       <c r="C117" t="n">
-        <v>34.5134214238429</v>
+        <v>34.5134214035907</v>
       </c>
       <c r="D117" t="n">
-        <v>28.6823147219246</v>
+        <v>28.6823193048514</v>
       </c>
     </row>
     <row r="118">
@@ -8855,13 +8855,13 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>173.401629087431</v>
+        <v>173.401628846726</v>
       </c>
       <c r="C118" t="n">
-        <v>31.5209469886282</v>
+        <v>31.5209469675882</v>
       </c>
       <c r="D118" t="n">
-        <v>28.1915085899159</v>
+        <v>28.1915131984486</v>
       </c>
     </row>
     <row r="119">
@@ -8869,13 +8869,13 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>175.313545536774</v>
+        <v>175.31354514518</v>
       </c>
       <c r="C119" t="n">
-        <v>32.2841033188776</v>
+        <v>32.2841032973871</v>
       </c>
       <c r="D119" t="n">
-        <v>27.7074811136374</v>
+        <v>27.7074857456212</v>
       </c>
     </row>
     <row r="120">
@@ -8883,13 +8883,13 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>165.19102786657</v>
+        <v>165.191028161482</v>
       </c>
       <c r="C120" t="n">
-        <v>29.1595479178933</v>
+        <v>29.1595478960459</v>
       </c>
       <c r="D120" t="n">
-        <v>27.2302322930891</v>
+        <v>27.2302369463691</v>
       </c>
     </row>
     <row r="121">
@@ -8897,13 +8897,13 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>183.894121249581</v>
+        <v>183.894120220789</v>
       </c>
       <c r="C121" t="n">
-        <v>35.3401423758169</v>
+        <v>35.3401423535762</v>
       </c>
       <c r="D121" t="n">
-        <v>26.7597621282711</v>
+        <v>26.7597668006924</v>
       </c>
     </row>
     <row r="122">
@@ -8911,13 +8911,13 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>175.675759240422</v>
+        <v>175.675758760289</v>
       </c>
       <c r="C122" t="n">
-        <v>32.8263145296521</v>
+        <v>32.8263145063414</v>
       </c>
       <c r="D122" t="n">
-        <v>26.2960706191834</v>
+        <v>26.296075308591</v>
       </c>
     </row>
     <row r="123">
@@ -8925,13 +8925,13 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>175.891625682238</v>
+        <v>175.891625164988</v>
       </c>
       <c r="C123" t="n">
-        <v>33.0314152833135</v>
+        <v>33.0314152597404</v>
       </c>
       <c r="D123" t="n">
-        <v>25.846680180746</v>
+        <v>25.8466848853268</v>
       </c>
     </row>
     <row r="124">
@@ -8939,13 +8939,13 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>167.566735967977</v>
+        <v>167.566736008126</v>
       </c>
       <c r="C124" t="n">
-        <v>30.4745739850742</v>
+        <v>30.474573961221</v>
       </c>
       <c r="D124" t="n">
-        <v>25.4115908129589</v>
+        <v>25.4115955308996</v>
       </c>
     </row>
     <row r="125">
@@ -8953,13 +8953,13 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>184.863328491012</v>
+        <v>184.863327302613</v>
       </c>
       <c r="C125" t="n">
-        <v>36.1860692562033</v>
+        <v>36.1860692320598</v>
       </c>
       <c r="D125" t="n">
-        <v>24.9908025158222</v>
+        <v>24.9908072453095</v>
       </c>
     </row>
     <row r="126">
@@ -8967,13 +8967,13 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>178.057015109491</v>
+        <v>178.057014367754</v>
       </c>
       <c r="C126" t="n">
-        <v>34.1109269125981</v>
+        <v>34.1109268869508</v>
       </c>
       <c r="D126" t="n">
-        <v>24.5843152893357</v>
+        <v>24.5843200285566</v>
       </c>
     </row>
     <row r="127">
@@ -8981,13 +8981,13 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>180.383010835515</v>
+        <v>180.383009904626</v>
       </c>
       <c r="C127" t="n">
-        <v>34.9906321417504</v>
+        <v>34.9906321158527</v>
       </c>
       <c r="D127" t="n">
-        <v>24.1572033062014</v>
+        <v>24.1572080533184</v>
       </c>
     </row>
     <row r="128">
@@ -8995,13 +8995,13 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>167.008807158709</v>
+        <v>167.008807129002</v>
       </c>
       <c r="C128" t="n">
-        <v>30.807282703753</v>
+        <v>30.8072826774936</v>
       </c>
       <c r="D128" t="n">
-        <v>23.7094665664191</v>
+        <v>23.7094713195951</v>
       </c>
     </row>
     <row r="129">
@@ -9009,13 +9009,13 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>188.752108436347</v>
+        <v>188.752106857407</v>
       </c>
       <c r="C129" t="n">
-        <v>37.9688619250949</v>
+        <v>37.9688618984663</v>
       </c>
       <c r="D129" t="n">
-        <v>23.241105069989</v>
+        <v>23.2411098273867</v>
       </c>
     </row>
     <row r="130">
@@ -9023,13 +9023,13 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>177.423217330224</v>
+        <v>177.423216502348</v>
       </c>
       <c r="C130" t="n">
-        <v>34.4583300533017</v>
+        <v>34.4583300260155</v>
       </c>
       <c r="D130" t="n">
-        <v>22.7521188169109</v>
+        <v>22.752123576693</v>
       </c>
     </row>
     <row r="131">
@@ -9037,13 +9037,13 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>181.172935158887</v>
+        <v>181.172934040588</v>
       </c>
       <c r="C131" t="n">
-        <v>35.779535382141</v>
+        <v>35.7795353542417</v>
       </c>
       <c r="D131" t="n">
-        <v>22.3853791271024</v>
+        <v>22.3853838886728</v>
       </c>
     </row>
     <row r="132">
@@ -9051,13 +9051,13 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>169.587631622385</v>
+        <v>169.587631292023</v>
       </c>
       <c r="C132" t="n">
-        <v>32.1125471380543</v>
+        <v>32.112547109771</v>
       </c>
       <c r="D132" t="n">
-        <v>22.1408860005633</v>
+        <v>22.140890763326</v>
       </c>
     </row>
     <row r="133">
@@ -9065,13 +9065,13 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>190.113810663391</v>
+        <v>190.11380889235</v>
       </c>
       <c r="C133" t="n">
-        <v>38.7768579159518</v>
+        <v>38.7768578872492</v>
       </c>
       <c r="D133" t="n">
-        <v>22.0186394372938</v>
+        <v>22.0186442006526</v>
       </c>
     </row>
   </sheetData>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>6.58158653671646</v>
+        <v>6.58158660432072</v>
       </c>
     </row>
     <row r="3">
@@ -9106,7 +9106,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8638342557031</v>
+        <v>16.8638338028851</v>
       </c>
     </row>
     <row r="4">
@@ -9114,7 +9114,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>-6.71784936923454</v>
+        <v>-6.7178477866303</v>
       </c>
     </row>
     <row r="5">
@@ -9122,7 +9122,7 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>41.619732411125</v>
+        <v>41.6197312137347</v>
       </c>
     </row>
     <row r="6">
@@ -9130,7 +9130,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.18604899490934</v>
+        <v>4.18604902225504</v>
       </c>
     </row>
     <row r="7">
@@ -9138,7 +9138,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>18.3346200893177</v>
+        <v>18.3346197356864</v>
       </c>
     </row>
     <row r="8">
@@ -9146,7 +9146,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.27531814589013</v>
+        <v>-4.27531649850542</v>
       </c>
     </row>
     <row r="9">
@@ -9154,7 +9154,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>41.8557362630293</v>
+        <v>41.8557349419305</v>
       </c>
     </row>
     <row r="10">
@@ -9162,7 +9162,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>19.8261309224413</v>
+        <v>19.8261312377309</v>
       </c>
     </row>
     <row r="11">
@@ -9170,7 +9170,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>29.0387584707472</v>
+        <v>29.0387581516253</v>
       </c>
     </row>
     <row r="12">
@@ -9178,7 +9178,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>2.03084525940147</v>
+        <v>2.03084677078762</v>
       </c>
     </row>
     <row r="13">
@@ -9186,7 +9186,7 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>43.7691199353152</v>
+        <v>43.7691184277618</v>
       </c>
     </row>
     <row r="14">
@@ -9194,7 +9194,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>25.7978288527819</v>
+        <v>25.7978291092536</v>
       </c>
     </row>
     <row r="15">
@@ -9202,7 +9202,7 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>34.4018765715641</v>
+        <v>34.4018762396655</v>
       </c>
     </row>
     <row r="16">
@@ -9210,7 +9210,7 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>10.498648147361</v>
+        <v>10.4986496730368</v>
       </c>
     </row>
     <row r="17">
@@ -9218,7 +9218,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>58.5536909125837</v>
+        <v>58.553689462335</v>
       </c>
     </row>
     <row r="18">
@@ -9226,7 +9226,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>52.4105899208566</v>
+        <v>52.410590135374</v>
       </c>
     </row>
     <row r="19">
@@ -9234,7 +9234,7 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>65.9391173284113</v>
+        <v>65.9391170690309</v>
       </c>
     </row>
     <row r="20">
@@ -9242,7 +9242,7 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>45.781350591238</v>
+        <v>45.7813521207111</v>
       </c>
     </row>
     <row r="21">
@@ -9250,7 +9250,7 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>93.3353744685093</v>
+        <v>93.3353729838994</v>
       </c>
     </row>
     <row r="22">
@@ -9258,7 +9258,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>107.655509496815</v>
+        <v>107.655509756284</v>
       </c>
     </row>
     <row r="23">
@@ -9266,7 +9266,7 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>110.880142462146</v>
+        <v>110.880142275346</v>
       </c>
     </row>
     <row r="24">
@@ -9274,7 +9274,7 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>77.3693880127336</v>
+        <v>77.3693895029116</v>
       </c>
     </row>
     <row r="25">
@@ -9282,7 +9282,7 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>105.472784321288</v>
+        <v>105.472782758441</v>
       </c>
     </row>
     <row r="26">
@@ -9290,7 +9290,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>101.039564467368</v>
+        <v>101.039564517578</v>
       </c>
     </row>
     <row r="27">
@@ -9298,7 +9298,7 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>90.9495597481429</v>
+        <v>90.9495594930202</v>
       </c>
     </row>
     <row r="28">
@@ -9306,7 +9306,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>59.7351165736948</v>
+        <v>59.7351180080814</v>
       </c>
     </row>
     <row r="29">
@@ -9314,7 +9314,7 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>98.4981242831451</v>
+        <v>98.4981230536709</v>
       </c>
     </row>
     <row r="30">
@@ -9322,7 +9322,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>77.8720127441485</v>
+        <v>77.872012505586</v>
       </c>
     </row>
     <row r="31">
@@ -9330,7 +9330,7 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>83.0527042663316</v>
+        <v>83.0527040338147</v>
       </c>
     </row>
     <row r="32">
@@ -9338,7 +9338,7 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>61.2120339387369</v>
+        <v>61.2120354021274</v>
       </c>
     </row>
     <row r="33">
@@ -9346,7 +9346,7 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>96.179799395674</v>
+        <v>96.1797984033627</v>
       </c>
     </row>
     <row r="34">
@@ -9354,7 +9354,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>72.0321175204987</v>
+        <v>72.0321173705735</v>
       </c>
     </row>
     <row r="35">
@@ -9362,7 +9362,7 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>69.7894290495669</v>
+        <v>69.7894289025229</v>
       </c>
     </row>
     <row r="36">
@@ -9370,7 +9370,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>52.2629558351695</v>
+        <v>52.2629568147169</v>
       </c>
     </row>
     <row r="37">
@@ -9378,7 +9378,7 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>75.5991680398029</v>
+        <v>75.5991673572246</v>
       </c>
     </row>
     <row r="38">
@@ -9386,7 +9386,7 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>54.0987427324352</v>
+        <v>54.0987426100509</v>
       </c>
     </row>
     <row r="39">
@@ -9394,7 +9394,7 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>55.9757687016194</v>
+        <v>55.9757686470956</v>
       </c>
     </row>
     <row r="40">
@@ -9402,7 +9402,7 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>52.9657771215292</v>
+        <v>52.9657776513523</v>
       </c>
     </row>
     <row r="41">
@@ -9410,7 +9410,7 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>73.5346093981822</v>
+        <v>73.534609045267</v>
       </c>
     </row>
     <row r="42">
@@ -9418,7 +9418,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>70.0131013620881</v>
+        <v>70.0131013273525</v>
       </c>
     </row>
     <row r="43">
@@ -9426,7 +9426,7 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>76.0026009775156</v>
+        <v>76.0026009989905</v>
       </c>
     </row>
     <row r="44">
@@ -9434,7 +9434,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>74.8368914848983</v>
+        <v>74.8368918082509</v>
       </c>
     </row>
     <row r="45">
@@ -9442,7 +9442,7 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>83.4641296838501</v>
+        <v>83.4641293737582</v>
       </c>
     </row>
     <row r="46">
@@ -9450,7 +9450,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>92.9176549784991</v>
+        <v>92.9176550605472</v>
       </c>
     </row>
     <row r="47">
@@ -9458,7 +9458,7 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>89.7439272622113</v>
+        <v>89.743927341452</v>
       </c>
     </row>
     <row r="48">
@@ -9466,7 +9466,7 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>87.2107700218772</v>
+        <v>87.210770114918</v>
       </c>
     </row>
     <row r="49">
@@ -9474,7 +9474,7 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>90.7396316368671</v>
+        <v>90.7396313825376</v>
       </c>
     </row>
     <row r="50">
@@ -9482,7 +9482,7 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>103.363080574898</v>
+        <v>103.363080509089</v>
       </c>
     </row>
     <row r="51">
@@ -9490,7 +9490,7 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>104.622847661863</v>
+        <v>104.62284763583</v>
       </c>
     </row>
     <row r="52">
@@ -9498,7 +9498,7 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>108.250028001507</v>
+        <v>108.250028018072</v>
       </c>
     </row>
     <row r="53">
@@ -9506,7 +9506,7 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>114.053872347012</v>
+        <v>114.053872422289</v>
       </c>
     </row>
     <row r="54">
@@ -9514,7 +9514,7 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>142.767591641887</v>
+        <v>142.767591716327</v>
       </c>
     </row>
     <row r="55">
@@ -9522,7 +9522,7 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>143.873261181657</v>
+        <v>143.873261370088</v>
       </c>
     </row>
     <row r="56">
@@ -9530,7 +9530,7 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>141.957500679914</v>
+        <v>141.95750075299</v>
       </c>
     </row>
     <row r="57">
@@ -9538,7 +9538,7 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>137.943384607456</v>
+        <v>137.943384271508</v>
       </c>
     </row>
     <row r="58">
@@ -9546,7 +9546,7 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>150.371070847122</v>
+        <v>150.371071094008</v>
       </c>
     </row>
     <row r="59">
@@ -9554,7 +9554,7 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>137.149487385303</v>
+        <v>137.149487850753</v>
       </c>
     </row>
     <row r="60">
@@ -9562,7 +9562,7 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>141.854054651498</v>
+        <v>141.854054512268</v>
       </c>
     </row>
     <row r="61">
@@ -9570,7 +9570,7 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>150.219212324832</v>
+        <v>150.219211751726</v>
       </c>
     </row>
     <row r="62">
@@ -9578,7 +9578,7 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>153.119136991412</v>
+        <v>153.119136992031</v>
       </c>
     </row>
     <row r="63">
@@ -9586,7 +9586,7 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>156.315172655529</v>
+        <v>156.315172834714</v>
       </c>
     </row>
     <row r="64">
@@ -9594,7 +9594,7 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>160.613508184391</v>
+        <v>160.613508291697</v>
       </c>
     </row>
     <row r="65">
@@ -9602,7 +9602,7 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>167.048736568374</v>
+        <v>167.048736281263</v>
       </c>
     </row>
     <row r="66">
@@ -9610,7 +9610,7 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>175.872617592945</v>
+        <v>175.872617615248</v>
       </c>
     </row>
     <row r="67">
@@ -9618,7 +9618,7 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>176.009976375092</v>
+        <v>176.009976299679</v>
       </c>
     </row>
     <row r="68">
@@ -9626,7 +9626,7 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>172.822477275217</v>
+        <v>172.822477365257</v>
       </c>
     </row>
     <row r="69">
@@ -9634,7 +9634,7 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>174.283382117502</v>
+        <v>174.283382080572</v>
       </c>
     </row>
     <row r="70">
@@ -9642,7 +9642,7 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>189.814011609322</v>
+        <v>189.814011664359</v>
       </c>
     </row>
     <row r="71">
@@ -9650,7 +9650,7 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>186.667850816256</v>
+        <v>186.667850961659</v>
       </c>
     </row>
     <row r="72">
@@ -9658,7 +9658,7 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>179.987835255298</v>
+        <v>179.987835602129</v>
       </c>
     </row>
     <row r="73">
@@ -9666,7 +9666,7 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>187.089740141874</v>
+        <v>187.089739594603</v>
       </c>
     </row>
     <row r="74">
@@ -9674,7 +9674,7 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>173.853059918806</v>
+        <v>173.853060373522</v>
       </c>
     </row>
     <row r="75">
@@ -9682,7 +9682,7 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>178.161900579518</v>
+        <v>178.161900666382</v>
       </c>
     </row>
     <row r="76">
@@ -9690,7 +9690,7 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>186.618093595414</v>
+        <v>186.618093492237</v>
       </c>
     </row>
     <row r="77">
@@ -9698,7 +9698,7 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>203.856945906263</v>
+        <v>203.85694546786</v>
       </c>
     </row>
     <row r="78">
@@ -9706,7 +9706,7 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>213.902429505026</v>
+        <v>213.902429636331</v>
       </c>
     </row>
     <row r="79">
@@ -9714,7 +9714,7 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>217.654686722971</v>
+        <v>217.654686983654</v>
       </c>
     </row>
     <row r="80">
@@ -9722,7 +9722,7 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>212.518276045754</v>
+        <v>212.51827611322</v>
       </c>
     </row>
     <row r="81">
@@ -9730,7 +9730,7 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>198.652607726249</v>
+        <v>198.652607266795</v>
       </c>
     </row>
     <row r="82">
@@ -9738,7 +9738,7 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>179.907031717407</v>
+        <v>179.907032096878</v>
       </c>
     </row>
     <row r="83">
@@ -9746,7 +9746,7 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>169.760755217907</v>
+        <v>169.760754942314</v>
       </c>
     </row>
     <row r="84">
@@ -9754,7 +9754,7 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>162.72644829924</v>
+        <v>162.726448224737</v>
       </c>
     </row>
     <row r="85">
@@ -9762,7 +9762,7 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>173.328956055339</v>
+        <v>173.328956025963</v>
       </c>
     </row>
     <row r="86">
@@ -9770,7 +9770,7 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>159.095559494053</v>
+        <v>159.095559294447</v>
       </c>
     </row>
     <row r="87">
@@ -9778,7 +9778,7 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>173.116934132645</v>
+        <v>173.116934325842</v>
       </c>
     </row>
     <row r="88">
@@ -9786,7 +9786,7 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>185.883386757617</v>
+        <v>185.883386943967</v>
       </c>
     </row>
     <row r="89">
@@ -9794,7 +9794,7 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>196.817973494608</v>
+        <v>196.817973314666</v>
       </c>
     </row>
     <row r="90">
@@ -9802,7 +9802,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>201.195586847268</v>
+        <v>201.195586871065</v>
       </c>
     </row>
     <row r="91">
@@ -9810,7 +9810,7 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>197.192041698394</v>
+        <v>197.192041694754</v>
       </c>
     </row>
     <row r="92">
@@ -9818,7 +9818,7 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>190.038230779697</v>
+        <v>190.038230753169</v>
       </c>
     </row>
     <row r="93">
@@ -9826,7 +9826,7 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>178.998892692681</v>
+        <v>178.998892699051</v>
       </c>
     </row>
     <row r="94">
@@ -9834,7 +9834,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>184.607743236531</v>
+        <v>184.607742957704</v>
       </c>
     </row>
     <row r="95">
@@ -9842,7 +9842,7 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>172.694100086681</v>
+        <v>172.694099923761</v>
       </c>
     </row>
     <row r="96">
@@ -9850,7 +9850,7 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>149.978906320426</v>
+        <v>149.978907263566</v>
       </c>
     </row>
     <row r="97">
@@ -9858,7 +9858,7 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>167.279866295044</v>
+        <v>167.279865793651</v>
       </c>
     </row>
     <row r="98">
@@ -9866,7 +9866,7 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>166.48666497716</v>
+        <v>166.486665217697</v>
       </c>
     </row>
     <row r="99">
@@ -9874,7 +9874,7 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>170.388451321141</v>
+        <v>170.388451293531</v>
       </c>
     </row>
     <row r="100">
@@ -9882,7 +9882,7 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>158.650977331891</v>
+        <v>158.650978132251</v>
       </c>
     </row>
     <row r="101">
@@ -9890,7 +9890,7 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>178.720746952097</v>
+        <v>178.720746369567</v>
       </c>
     </row>
     <row r="102">
@@ -9898,7 +9898,7 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>168.69200765167</v>
+        <v>168.692007788062</v>
       </c>
     </row>
     <row r="103">
@@ -9906,7 +9906,7 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>170.353376147471</v>
+        <v>170.353376184887</v>
       </c>
     </row>
     <row r="104">
@@ -9914,7 +9914,7 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>160.032405218552</v>
+        <v>160.032405987878</v>
       </c>
     </row>
     <row r="105">
@@ -9922,7 +9922,7 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>178.589140037729</v>
+        <v>178.589139522246</v>
       </c>
     </row>
     <row r="106">
@@ -9930,7 +9930,7 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>170.276514159564</v>
+        <v>170.276514225127</v>
       </c>
     </row>
     <row r="107">
@@ -9938,7 +9938,7 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>170.382605505123</v>
+        <v>170.382605566025</v>
       </c>
     </row>
     <row r="108">
@@ -9946,7 +9946,7 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>161.932429467335</v>
+        <v>161.932430118163</v>
       </c>
     </row>
     <row r="109">
@@ -9954,7 +9954,7 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>179.088224439605</v>
+        <v>179.088223894483</v>
       </c>
     </row>
     <row r="110">
@@ -9962,7 +9962,7 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>172.125602280048</v>
+        <v>172.125602214255</v>
       </c>
     </row>
     <row r="111">
@@ -9970,7 +9970,7 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>174.326041402758</v>
+        <v>174.326041179765</v>
       </c>
     </row>
     <row r="112">
@@ -9978,7 +9978,7 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>160.857033297347</v>
+        <v>160.85703400677</v>
       </c>
     </row>
     <row r="113">
@@ -9986,7 +9986,7 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>182.536282321103</v>
+        <v>182.536281511811</v>
       </c>
     </row>
     <row r="114">
@@ -9994,7 +9994,7 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>171.174091135827</v>
+        <v>171.174091107399</v>
       </c>
     </row>
     <row r="115">
@@ -10002,7 +10002,7 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>174.784332469976</v>
+        <v>174.784332177757</v>
       </c>
     </row>
     <row r="116">
@@ -10010,7 +10010,7 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>162.953376023652</v>
+        <v>162.953376542831</v>
       </c>
     </row>
     <row r="117">
@@ -10018,7 +10018,7 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>183.127725739494</v>
+        <v>183.127724838288</v>
       </c>
     </row>
     <row r="118">
@@ -10026,7 +10026,7 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>173.401629087431</v>
+        <v>173.401628846726</v>
       </c>
     </row>
     <row r="119">
@@ -10034,7 +10034,7 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>175.313545536774</v>
+        <v>175.31354514518</v>
       </c>
     </row>
     <row r="120">
@@ -10042,7 +10042,7 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>165.19102786657</v>
+        <v>165.191028161482</v>
       </c>
     </row>
     <row r="121">
@@ -10050,7 +10050,7 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>183.894121249581</v>
+        <v>183.894120220789</v>
       </c>
     </row>
     <row r="122">
@@ -10058,7 +10058,7 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>175.675759240422</v>
+        <v>175.675758760289</v>
       </c>
     </row>
     <row r="123">
@@ -10066,7 +10066,7 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>175.891625682238</v>
+        <v>175.891625164988</v>
       </c>
     </row>
     <row r="124">
@@ -10074,7 +10074,7 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>167.566735967977</v>
+        <v>167.566736008126</v>
       </c>
     </row>
     <row r="125">
@@ -10082,7 +10082,7 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>184.863328491012</v>
+        <v>184.863327302613</v>
       </c>
     </row>
     <row r="126">
@@ -10090,7 +10090,7 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>178.057015109491</v>
+        <v>178.057014367754</v>
       </c>
     </row>
     <row r="127">
@@ -10098,7 +10098,7 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>180.383010835515</v>
+        <v>180.383009904626</v>
       </c>
     </row>
     <row r="128">
@@ -10106,7 +10106,7 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>167.008807158709</v>
+        <v>167.008807129002</v>
       </c>
     </row>
     <row r="129">
@@ -10114,7 +10114,7 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>188.752108436347</v>
+        <v>188.752106857407</v>
       </c>
     </row>
     <row r="130">
@@ -10122,7 +10122,7 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>177.423217330224</v>
+        <v>177.423216502348</v>
       </c>
     </row>
     <row r="131">
@@ -10130,7 +10130,7 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>181.172935158887</v>
+        <v>181.172934040588</v>
       </c>
     </row>
     <row r="132">
@@ -10138,7 +10138,7 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>169.587631622385</v>
+        <v>169.587631292023</v>
       </c>
     </row>
     <row r="133">
@@ -10146,7 +10146,7 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>190.113810663391</v>
+        <v>190.11380889235</v>
       </c>
     </row>
   </sheetData>

--- a/VA_result_TEL.xlsx
+++ b/VA_result_TEL.xlsx
@@ -1088,10 +1088,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>376576.054202336</v>
+        <v>376576.054201833</v>
       </c>
       <c r="C2" t="n">
-        <v>37.6576054202336</v>
+        <v>37.6576054201833</v>
       </c>
     </row>
     <row r="3">
@@ -1102,7 +1102,7 @@
         <v>487847.416454892</v>
       </c>
       <c r="C3" t="n">
-        <v>48.7847416454891</v>
+        <v>48.7847416454892</v>
       </c>
     </row>
     <row r="4">
@@ -1110,10 +1110,10 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>137930.497384738</v>
+        <v>137930.497384685</v>
       </c>
       <c r="C4" t="n">
-        <v>13.7930497384738</v>
+        <v>13.7930497384685</v>
       </c>
     </row>
     <row r="5">
@@ -1121,10 +1121,10 @@
         <v>31</v>
       </c>
       <c r="B5" t="n">
-        <v>696734.250950203</v>
+        <v>696734.250950812</v>
       </c>
       <c r="C5" t="n">
-        <v>69.6734250950203</v>
+        <v>69.6734250950812</v>
       </c>
     </row>
     <row r="6">
@@ -1132,10 +1132,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>377371.840804729</v>
+        <v>377371.84080423</v>
       </c>
       <c r="C6" t="n">
-        <v>37.7371840804729</v>
+        <v>37.737184080423</v>
       </c>
     </row>
     <row r="7">
@@ -1143,10 +1143,10 @@
         <v>32</v>
       </c>
       <c r="B7" t="n">
-        <v>487751.637279191</v>
+        <v>487751.637279192</v>
       </c>
       <c r="C7" t="n">
-        <v>48.7751637279191</v>
+        <v>48.7751637279192</v>
       </c>
     </row>
     <row r="8">
@@ -1154,10 +1154,10 @@
         <v>33</v>
       </c>
       <c r="B8" t="n">
-        <v>138355.786055678</v>
+        <v>138355.786055623</v>
       </c>
       <c r="C8" t="n">
-        <v>13.8355786055678</v>
+        <v>13.8355786055623</v>
       </c>
     </row>
     <row r="9">
@@ -1165,10 +1165,10 @@
         <v>34</v>
       </c>
       <c r="B9" t="n">
-        <v>695392.344294446</v>
+        <v>695392.344295051</v>
       </c>
       <c r="C9" t="n">
-        <v>69.5392344294446</v>
+        <v>69.5392344295051</v>
       </c>
     </row>
     <row r="10">
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>378236.89589221</v>
+        <v>378236.895891716</v>
       </c>
       <c r="C10" t="n">
-        <v>37.823689589221</v>
+        <v>37.8236895891716</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
         <v>487670.505777647</v>
       </c>
       <c r="C11" t="n">
-        <v>48.7670505777646</v>
+        <v>48.7670505777647</v>
       </c>
     </row>
     <row r="12">
@@ -1198,10 +1198,10 @@
         <v>36</v>
       </c>
       <c r="B12" t="n">
-        <v>138732.842726596</v>
+        <v>138732.842726539</v>
       </c>
       <c r="C12" t="n">
-        <v>13.8732842726596</v>
+        <v>13.8732842726539</v>
       </c>
     </row>
     <row r="13">
@@ -1209,10 +1209,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="n">
-        <v>693967.997409902</v>
+        <v>693967.997410502</v>
       </c>
       <c r="C13" t="n">
-        <v>69.3967997409902</v>
+        <v>69.3967997410502</v>
       </c>
     </row>
     <row r="14">
@@ -1220,10 +1220,10 @@
         <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>379922.127217224</v>
+        <v>379922.12721674</v>
       </c>
       <c r="C14" t="n">
-        <v>37.9922127217224</v>
+        <v>37.992212721674</v>
       </c>
     </row>
     <row r="15">
@@ -1242,10 +1242,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="n">
-        <v>139289.895422058</v>
+        <v>139289.895421997</v>
       </c>
       <c r="C16" t="n">
-        <v>13.9289895422058</v>
+        <v>13.9289895421997</v>
       </c>
     </row>
     <row r="17">
@@ -1253,10 +1253,10 @@
         <v>40</v>
       </c>
       <c r="B17" t="n">
-        <v>691727.904717987</v>
+        <v>691727.904718579</v>
       </c>
       <c r="C17" t="n">
-        <v>69.1727904717987</v>
+        <v>69.1727904718579</v>
       </c>
     </row>
     <row r="18">
@@ -1264,10 +1264,10 @@
         <v>6</v>
       </c>
       <c r="B18" t="n">
-        <v>381287.933904503</v>
+        <v>381287.933904026</v>
       </c>
       <c r="C18" t="n">
-        <v>38.1287933904503</v>
+        <v>38.1287933904026</v>
       </c>
     </row>
     <row r="19">
@@ -1275,10 +1275,10 @@
         <v>41</v>
       </c>
       <c r="B19" t="n">
-        <v>485794.669870252</v>
+        <v>485794.669870245</v>
       </c>
       <c r="C19" t="n">
-        <v>48.5794669870252</v>
+        <v>48.5794669870245</v>
       </c>
     </row>
     <row r="20">
@@ -1286,10 +1286,10 @@
         <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>137945.575804048</v>
+        <v>137945.575803972</v>
       </c>
       <c r="C20" t="n">
-        <v>13.7945575804048</v>
+        <v>13.7945575803971</v>
       </c>
     </row>
     <row r="21">
@@ -1297,10 +1297,10 @@
         <v>43</v>
       </c>
       <c r="B21" t="n">
-        <v>686931.0415515</v>
+        <v>686931.041552067</v>
       </c>
       <c r="C21" t="n">
-        <v>68.69310415515</v>
+        <v>68.6931041552067</v>
       </c>
     </row>
     <row r="22">
@@ -1308,10 +1308,10 @@
         <v>7</v>
       </c>
       <c r="B22" t="n">
-        <v>397755.939876537</v>
+        <v>397755.939876154</v>
       </c>
       <c r="C22" t="n">
-        <v>39.7755939876537</v>
+        <v>39.7755939876154</v>
       </c>
     </row>
     <row r="23">
@@ -1319,10 +1319,10 @@
         <v>44</v>
       </c>
       <c r="B23" t="n">
-        <v>478996.71885631</v>
+        <v>478996.718856279</v>
       </c>
       <c r="C23" t="n">
-        <v>47.899671885631</v>
+        <v>47.8996718856279</v>
       </c>
     </row>
     <row r="24">
@@ -1330,10 +1330,10 @@
         <v>45</v>
       </c>
       <c r="B24" t="n">
-        <v>135863.216936083</v>
+        <v>135863.216935976</v>
       </c>
       <c r="C24" t="n">
-        <v>13.5863216936083</v>
+        <v>13.5863216935976</v>
       </c>
     </row>
     <row r="25">
@@ -1341,10 +1341,10 @@
         <v>46</v>
       </c>
       <c r="B25" t="n">
-        <v>677929.020807724</v>
+        <v>677929.020808246</v>
       </c>
       <c r="C25" t="n">
-        <v>67.7929020807724</v>
+        <v>67.7929020808246</v>
       </c>
     </row>
     <row r="26">
@@ -1352,10 +1352,10 @@
         <v>8</v>
       </c>
       <c r="B26" t="n">
-        <v>414821.778162503</v>
+        <v>414821.778162214</v>
       </c>
       <c r="C26" t="n">
-        <v>41.4821778162503</v>
+        <v>41.4821778162214</v>
       </c>
     </row>
     <row r="27">
@@ -1363,10 +1363,10 @@
         <v>47</v>
       </c>
       <c r="B27" t="n">
-        <v>472967.8502742</v>
+        <v>472967.850274146</v>
       </c>
       <c r="C27" t="n">
-        <v>47.29678502742</v>
+        <v>47.2967850274146</v>
       </c>
     </row>
     <row r="28">
@@ -1374,10 +1374,10 @@
         <v>48</v>
       </c>
       <c r="B28" t="n">
-        <v>134582.080417652</v>
+        <v>134582.080417518</v>
       </c>
       <c r="C28" t="n">
-        <v>13.4582080417652</v>
+        <v>13.4582080417518</v>
       </c>
     </row>
     <row r="29">
@@ -1385,10 +1385,10 @@
         <v>49</v>
       </c>
       <c r="B29" t="n">
-        <v>669865.555331655</v>
+        <v>669865.555332135</v>
       </c>
       <c r="C29" t="n">
-        <v>66.9865555331655</v>
+        <v>66.9865555332135</v>
       </c>
     </row>
     <row r="30">
@@ -1396,10 +1396,10 @@
         <v>9</v>
       </c>
       <c r="B30" t="n">
-        <v>429632.858872865</v>
+        <v>429632.858872673</v>
       </c>
       <c r="C30" t="n">
-        <v>42.9632858872865</v>
+        <v>42.9632858872673</v>
       </c>
     </row>
     <row r="31">
@@ -1407,10 +1407,10 @@
         <v>50</v>
       </c>
       <c r="B31" t="n">
-        <v>465865.674859121</v>
+        <v>465865.67485906</v>
       </c>
       <c r="C31" t="n">
-        <v>46.5865674859121</v>
+        <v>46.5865674859059</v>
       </c>
     </row>
     <row r="32">
@@ -1418,10 +1418,10 @@
         <v>51</v>
       </c>
       <c r="B32" t="n">
-        <v>145584.437396233</v>
+        <v>145584.43739607</v>
       </c>
       <c r="C32" t="n">
-        <v>14.5584437396233</v>
+        <v>14.558443739607</v>
       </c>
     </row>
     <row r="33">
@@ -1429,10 +1429,10 @@
         <v>52</v>
       </c>
       <c r="B33" t="n">
-        <v>645385.610407632</v>
+        <v>645385.610408032</v>
       </c>
       <c r="C33" t="n">
-        <v>64.5385610407632</v>
+        <v>64.5385610408032</v>
       </c>
     </row>
     <row r="34">
@@ -1440,10 +1440,10 @@
         <v>10</v>
       </c>
       <c r="B34" t="n">
-        <v>447264.148739515</v>
+        <v>447264.148739431</v>
       </c>
       <c r="C34" t="n">
-        <v>44.7264148739514</v>
+        <v>44.7264148739431</v>
       </c>
     </row>
     <row r="35">
@@ -1451,10 +1451,10 @@
         <v>53</v>
       </c>
       <c r="B35" t="n">
-        <v>461101.054972258</v>
+        <v>461101.054972202</v>
       </c>
       <c r="C35" t="n">
-        <v>46.1101054972258</v>
+        <v>46.1101054972202</v>
       </c>
     </row>
     <row r="36">
@@ -1462,10 +1462,10 @@
         <v>54</v>
       </c>
       <c r="B36" t="n">
-        <v>157397.86258703</v>
+        <v>157397.862586852</v>
       </c>
       <c r="C36" t="n">
-        <v>15.739786258703</v>
+        <v>15.7397862586852</v>
       </c>
     </row>
     <row r="37">
@@ -1473,10 +1473,10 @@
         <v>55</v>
       </c>
       <c r="B37" t="n">
-        <v>618830.728834432</v>
+        <v>618830.728834767</v>
       </c>
       <c r="C37" t="n">
-        <v>61.8830728834432</v>
+        <v>61.8830728834767</v>
       </c>
     </row>
     <row r="38">
@@ -1484,10 +1484,10 @@
         <v>11</v>
       </c>
       <c r="B38" t="n">
-        <v>443918.182565253</v>
+        <v>443918.182565187</v>
       </c>
       <c r="C38" t="n">
-        <v>44.3918182565253</v>
+        <v>44.3918182565187</v>
       </c>
     </row>
     <row r="39">
@@ -1495,10 +1495,10 @@
         <v>56</v>
       </c>
       <c r="B39" t="n">
-        <v>447075.477303055</v>
+        <v>447075.477303017</v>
       </c>
       <c r="C39" t="n">
-        <v>44.7075477303055</v>
+        <v>44.7075477303017</v>
       </c>
     </row>
     <row r="40">
@@ -1506,10 +1506,10 @@
         <v>57</v>
       </c>
       <c r="B40" t="n">
-        <v>243698.473039615</v>
+        <v>243698.473039501</v>
       </c>
       <c r="C40" t="n">
-        <v>24.3698473039615</v>
+        <v>24.3698473039501</v>
       </c>
     </row>
     <row r="41">
@@ -1517,10 +1517,10 @@
         <v>58</v>
       </c>
       <c r="B41" t="n">
-        <v>558928.423531672</v>
+        <v>558928.423531906</v>
       </c>
       <c r="C41" t="n">
-        <v>55.8928423531672</v>
+        <v>55.8928423531906</v>
       </c>
     </row>
     <row r="42">
@@ -1528,10 +1528,10 @@
         <v>12</v>
       </c>
       <c r="B42" t="n">
-        <v>434581.342443047</v>
+        <v>434581.342443</v>
       </c>
       <c r="C42" t="n">
-        <v>43.4581342443047</v>
+        <v>43.4581342443</v>
       </c>
     </row>
     <row r="43">
@@ -1539,10 +1539,10 @@
         <v>59</v>
       </c>
       <c r="B43" t="n">
-        <v>430656.155081479</v>
+        <v>430656.155081458</v>
       </c>
       <c r="C43" t="n">
-        <v>43.0656155081479</v>
+        <v>43.0656155081458</v>
       </c>
     </row>
     <row r="44">
@@ -1550,10 +1550,10 @@
         <v>60</v>
       </c>
       <c r="B44" t="n">
-        <v>330749.82758454</v>
+        <v>330749.82758449</v>
       </c>
       <c r="C44" t="n">
-        <v>33.074982758454</v>
+        <v>33.074982758449</v>
       </c>
     </row>
     <row r="45">
@@ -1561,10 +1561,10 @@
         <v>61</v>
       </c>
       <c r="B45" t="n">
-        <v>502503.56458468</v>
+        <v>502503.564584814</v>
       </c>
       <c r="C45" t="n">
-        <v>50.250356458468</v>
+        <v>50.2503564584814</v>
       </c>
     </row>
     <row r="46">
@@ -1572,10 +1572,10 @@
         <v>13</v>
       </c>
       <c r="B46" t="n">
-        <v>431155.364883295</v>
+        <v>431155.364883267</v>
       </c>
       <c r="C46" t="n">
-        <v>43.1155364883295</v>
+        <v>43.1155364883267</v>
       </c>
     </row>
     <row r="47">
@@ -1583,10 +1583,10 @@
         <v>62</v>
       </c>
       <c r="B47" t="n">
-        <v>423402.711361443</v>
+        <v>423402.711361439</v>
       </c>
       <c r="C47" t="n">
-        <v>42.3402711361443</v>
+        <v>42.3402711361439</v>
       </c>
     </row>
     <row r="48">
@@ -1594,10 +1594,10 @@
         <v>63</v>
       </c>
       <c r="B48" t="n">
-        <v>364891.96491201</v>
+        <v>364891.964911993</v>
       </c>
       <c r="C48" t="n">
-        <v>36.4891964912009</v>
+        <v>36.4891964911993</v>
       </c>
     </row>
     <row r="49">
@@ -1605,10 +1605,10 @@
         <v>64</v>
       </c>
       <c r="B49" t="n">
-        <v>474511.465887826</v>
+        <v>474511.465887906</v>
       </c>
       <c r="C49" t="n">
-        <v>47.4511465887826</v>
+        <v>47.4511465887906</v>
       </c>
     </row>
     <row r="50">
@@ -1616,10 +1616,10 @@
         <v>14</v>
       </c>
       <c r="B50" t="n">
-        <v>431291.541665506</v>
+        <v>431291.541665491</v>
       </c>
       <c r="C50" t="n">
-        <v>43.1291541665506</v>
+        <v>43.1291541665491</v>
       </c>
     </row>
     <row r="51">
@@ -1627,10 +1627,10 @@
         <v>65</v>
       </c>
       <c r="B51" t="n">
-        <v>417753.25948703</v>
+        <v>417753.259487038</v>
       </c>
       <c r="C51" t="n">
-        <v>41.775325948703</v>
+        <v>41.7753259487038</v>
       </c>
     </row>
     <row r="52">
@@ -1638,10 +1638,10 @@
         <v>66</v>
       </c>
       <c r="B52" t="n">
-        <v>400089.10701706</v>
+        <v>400089.107017075</v>
       </c>
       <c r="C52" t="n">
-        <v>40.008910701706</v>
+        <v>40.0089107017075</v>
       </c>
     </row>
     <row r="53">
@@ -1649,10 +1649,10 @@
         <v>67</v>
       </c>
       <c r="B53" t="n">
-        <v>448318.016231512</v>
+        <v>448318.016231539</v>
       </c>
       <c r="C53" t="n">
-        <v>44.8318016231512</v>
+        <v>44.8318016231539</v>
       </c>
     </row>
     <row r="54">
@@ -2144,10 +2144,10 @@
         <v>26</v>
       </c>
       <c r="B98" t="n">
-        <v>1023362.15678541</v>
+        <v>1023362.15713526</v>
       </c>
       <c r="C98" t="n">
-        <v>102.336215678541</v>
+        <v>102.336215713526</v>
       </c>
     </row>
     <row r="99">
@@ -2155,10 +2155,10 @@
         <v>101</v>
       </c>
       <c r="B99" t="n">
-        <v>1058550.36594136</v>
+        <v>1058550.36630123</v>
       </c>
       <c r="C99" t="n">
-        <v>105.855036594136</v>
+        <v>105.855036630123</v>
       </c>
     </row>
     <row r="100">
@@ -2166,10 +2166,10 @@
         <v>102</v>
       </c>
       <c r="B100" t="n">
-        <v>891216.38840692</v>
+        <v>891216.388781259</v>
       </c>
       <c r="C100" t="n">
-        <v>89.121638840692</v>
+        <v>89.1216388781259</v>
       </c>
     </row>
     <row r="101">
@@ -2177,10 +2177,10 @@
         <v>103</v>
       </c>
       <c r="B101" t="n">
-        <v>1177679.5572459</v>
+        <v>1177679.557635</v>
       </c>
       <c r="C101" t="n">
-        <v>117.76795572459</v>
+        <v>117.7679557635</v>
       </c>
     </row>
     <row r="102">
@@ -2188,10 +2188,10 @@
         <v>104</v>
       </c>
       <c r="B102" t="n">
-        <v>1037258.28234799</v>
+        <v>1037258.2827634</v>
       </c>
       <c r="C102" t="n">
-        <v>103.725828234799</v>
+        <v>103.72582827634</v>
       </c>
     </row>
     <row r="103">
@@ -2199,10 +2199,10 @@
         <v>105</v>
       </c>
       <c r="B103" t="n">
-        <v>1090106.49547691</v>
+        <v>1090106.49591684</v>
       </c>
       <c r="C103" t="n">
-        <v>109.010649547691</v>
+        <v>109.010649591684</v>
       </c>
     </row>
     <row r="104">
@@ -2210,10 +2210,10 @@
         <v>106</v>
       </c>
       <c r="B104" t="n">
-        <v>943426.965697953</v>
+        <v>943426.96615325</v>
       </c>
       <c r="C104" t="n">
-        <v>94.3426965697953</v>
+        <v>94.342696615325</v>
       </c>
     </row>
     <row r="105">
@@ -2221,10 +2221,10 @@
         <v>107</v>
       </c>
       <c r="B105" t="n">
-        <v>1209999.39679714</v>
+        <v>1209999.3972692</v>
       </c>
       <c r="C105" t="n">
-        <v>120.999939679714</v>
+        <v>120.99993972692</v>
       </c>
     </row>
     <row r="106">
@@ -2232,10 +2232,10 @@
         <v>108</v>
       </c>
       <c r="B106" t="n">
-        <v>1090300.41935722</v>
+        <v>1090300.4198608</v>
       </c>
       <c r="C106" t="n">
-        <v>109.030041935722</v>
+        <v>109.03004198608</v>
       </c>
     </row>
     <row r="107">
@@ -2243,10 +2243,10 @@
         <v>109</v>
       </c>
       <c r="B107" t="n">
-        <v>1120826.67254911</v>
+        <v>1120826.67307071</v>
       </c>
       <c r="C107" t="n">
-        <v>112.082667254911</v>
+        <v>112.082667307071</v>
       </c>
     </row>
     <row r="108">
@@ -2254,10 +2254,10 @@
         <v>110</v>
       </c>
       <c r="B108" t="n">
-        <v>995844.456495172</v>
+        <v>995844.45703105</v>
       </c>
       <c r="C108" t="n">
-        <v>99.5844456495172</v>
+        <v>99.5844457031049</v>
       </c>
     </row>
     <row r="109">
@@ -2265,10 +2265,10 @@
         <v>111</v>
       </c>
       <c r="B109" t="n">
-        <v>1243068.23479661</v>
+        <v>1243068.23534822</v>
       </c>
       <c r="C109" t="n">
-        <v>124.306823479661</v>
+        <v>124.306823534822</v>
       </c>
     </row>
     <row r="110">
@@ -2276,10 +2276,10 @@
         <v>112</v>
       </c>
       <c r="B110" t="n">
-        <v>1142515.12090725</v>
+        <v>1142515.12150166</v>
       </c>
       <c r="C110" t="n">
-        <v>114.251512090725</v>
+        <v>114.251512150166</v>
       </c>
     </row>
     <row r="111">
@@ -2287,10 +2287,10 @@
         <v>113</v>
       </c>
       <c r="B111" t="n">
-        <v>1150719.1510433</v>
+        <v>1150719.15164821</v>
       </c>
       <c r="C111" t="n">
-        <v>115.07191510433</v>
+        <v>115.071915164821</v>
       </c>
     </row>
     <row r="112">
@@ -2298,10 +2298,10 @@
         <v>114</v>
       </c>
       <c r="B112" t="n">
-        <v>1048445.49910241</v>
+        <v>1048445.49971852</v>
       </c>
       <c r="C112" t="n">
-        <v>104.844549910241</v>
+        <v>104.844549971852</v>
       </c>
     </row>
     <row r="113">
@@ -2309,10 +2309,10 @@
         <v>115</v>
       </c>
       <c r="B113" t="n">
-        <v>1276905.30993609</v>
+        <v>1276905.31056381</v>
       </c>
       <c r="C113" t="n">
-        <v>127.690530993609</v>
+        <v>127.690531056381</v>
       </c>
     </row>
     <row r="114">
@@ -2320,10 +2320,10 @@
         <v>116</v>
       </c>
       <c r="B114" t="n">
-        <v>1193899.61613164</v>
+        <v>1193899.61681952</v>
       </c>
       <c r="C114" t="n">
-        <v>119.389961613164</v>
+        <v>119.389961681952</v>
       </c>
     </row>
     <row r="115">
@@ -2331,10 +2331,10 @@
         <v>117</v>
       </c>
       <c r="B115" t="n">
-        <v>1229087.82528772</v>
+        <v>1229087.82598562</v>
       </c>
       <c r="C115" t="n">
-        <v>122.908782528772</v>
+        <v>122.908782598562</v>
       </c>
     </row>
     <row r="116">
@@ -2342,10 +2342,10 @@
         <v>118</v>
       </c>
       <c r="B116" t="n">
-        <v>1061753.84775328</v>
+        <v>1061753.84846564</v>
       </c>
       <c r="C116" t="n">
-        <v>106.175384775328</v>
+        <v>106.175384846564</v>
       </c>
     </row>
     <row r="117">
@@ -2353,10 +2353,10 @@
         <v>119</v>
       </c>
       <c r="B117" t="n">
-        <v>1348217.01659223</v>
+        <v>1348217.01731935</v>
       </c>
       <c r="C117" t="n">
-        <v>134.821701659223</v>
+        <v>134.821701731935</v>
       </c>
     </row>
     <row r="118">
@@ -2364,10 +2364,10 @@
         <v>120</v>
       </c>
       <c r="B118" t="n">
-        <v>1207795.74169438</v>
+        <v>1207795.74244781</v>
       </c>
       <c r="C118" t="n">
-        <v>120.779574169438</v>
+        <v>120.779574244781</v>
       </c>
     </row>
     <row r="119">
@@ -2375,10 +2375,10 @@
         <v>121</v>
       </c>
       <c r="B119" t="n">
-        <v>1260643.95482326</v>
+        <v>1260643.95560121</v>
       </c>
       <c r="C119" t="n">
-        <v>126.064395482326</v>
+        <v>126.064395560121</v>
       </c>
     </row>
     <row r="120">
@@ -2386,10 +2386,10 @@
         <v>122</v>
       </c>
       <c r="B120" t="n">
-        <v>1113964.42504453</v>
+        <v>1113964.42583785</v>
       </c>
       <c r="C120" t="n">
-        <v>111.396442504453</v>
+        <v>111.396442583785</v>
       </c>
     </row>
     <row r="121">
@@ -2397,10 +2397,10 @@
         <v>123</v>
       </c>
       <c r="B121" t="n">
-        <v>1380536.85614363</v>
+        <v>1380536.85695371</v>
       </c>
       <c r="C121" t="n">
-        <v>138.053685614363</v>
+        <v>138.053685695371</v>
       </c>
     </row>
     <row r="122">
@@ -2408,10 +2408,10 @@
         <v>124</v>
       </c>
       <c r="B122" t="n">
-        <v>1260837.87870353</v>
+        <v>1260837.87954513</v>
       </c>
       <c r="C122" t="n">
-        <v>126.083787870353</v>
+        <v>126.083787954513</v>
       </c>
     </row>
     <row r="123">
@@ -2419,10 +2419,10 @@
         <v>125</v>
       </c>
       <c r="B123" t="n">
-        <v>1291364.13189548</v>
+        <v>1291364.13275511</v>
       </c>
       <c r="C123" t="n">
-        <v>129.136413189548</v>
+        <v>129.136413275511</v>
       </c>
     </row>
     <row r="124">
@@ -2430,10 +2430,10 @@
         <v>126</v>
       </c>
       <c r="B124" t="n">
-        <v>1166381.91584184</v>
+        <v>1166381.91671573</v>
       </c>
       <c r="C124" t="n">
-        <v>116.638191584184</v>
+        <v>116.638191671573</v>
       </c>
     </row>
     <row r="125">
@@ -2441,10 +2441,10 @@
         <v>127</v>
       </c>
       <c r="B125" t="n">
-        <v>1413605.69414305</v>
+        <v>1413605.69503267</v>
       </c>
       <c r="C125" t="n">
-        <v>141.360569414305</v>
+        <v>141.360569503267</v>
       </c>
     </row>
     <row r="126">
@@ -2452,10 +2452,10 @@
         <v>128</v>
       </c>
       <c r="B126" t="n">
-        <v>1313052.58025365</v>
+        <v>1313052.58118608</v>
       </c>
       <c r="C126" t="n">
-        <v>131.305258025365</v>
+        <v>131.305258118608</v>
       </c>
     </row>
     <row r="127">
@@ -2463,10 +2463,10 @@
         <v>129</v>
       </c>
       <c r="B127" t="n">
-        <v>1321256.61038962</v>
+        <v>1321256.61133254</v>
       </c>
       <c r="C127" t="n">
-        <v>132.125661038962</v>
+        <v>132.125661133254</v>
       </c>
     </row>
     <row r="128">
@@ -2474,10 +2474,10 @@
         <v>130</v>
       </c>
       <c r="B128" t="n">
-        <v>1218982.95844884</v>
+        <v>1218982.95940297</v>
       </c>
       <c r="C128" t="n">
-        <v>121.898295844884</v>
+        <v>121.898295940297</v>
       </c>
     </row>
     <row r="129">
@@ -2485,10 +2485,10 @@
         <v>131</v>
       </c>
       <c r="B129" t="n">
-        <v>1447442.76928239</v>
+        <v>1447442.77024813</v>
       </c>
       <c r="C129" t="n">
-        <v>144.744276928239</v>
+        <v>144.744277024813</v>
       </c>
     </row>
     <row r="130">
@@ -2496,10 +2496,10 @@
         <v>132</v>
       </c>
       <c r="B130" t="n">
-        <v>1364437.07547803</v>
+        <v>1364437.07650392</v>
       </c>
       <c r="C130" t="n">
-        <v>136.443707547803</v>
+        <v>136.443707650392</v>
       </c>
     </row>
     <row r="131">
@@ -2507,10 +2507,10 @@
         <v>133</v>
       </c>
       <c r="B131" t="n">
-        <v>1399625.28463411</v>
+        <v>1399625.28567002</v>
       </c>
       <c r="C131" t="n">
-        <v>139.962528463411</v>
+        <v>139.962528567002</v>
       </c>
     </row>
     <row r="132">
@@ -2518,10 +2518,10 @@
         <v>134</v>
       </c>
       <c r="B132" t="n">
-        <v>1232291.30709974</v>
+        <v>1232291.30815012</v>
       </c>
       <c r="C132" t="n">
-        <v>123.229130709974</v>
+        <v>123.229130815012</v>
       </c>
     </row>
     <row r="133">
@@ -2529,10 +2529,10 @@
         <v>135</v>
       </c>
       <c r="B133" t="n">
-        <v>1518754.47593865</v>
+        <v>1518754.4770038</v>
       </c>
       <c r="C133" t="n">
-        <v>151.875447593865</v>
+        <v>151.87544770038</v>
       </c>
     </row>
     <row r="134">
@@ -2540,10 +2540,10 @@
         <v>136</v>
       </c>
       <c r="B134" t="n">
-        <v>1378333.20104062</v>
+        <v>1378333.20213207</v>
       </c>
       <c r="C134" t="n">
-        <v>137.833320104062</v>
+        <v>137.833320213207</v>
       </c>
     </row>
     <row r="135">
@@ -2551,10 +2551,10 @@
         <v>137</v>
       </c>
       <c r="B135" t="n">
-        <v>1431181.41416967</v>
+        <v>1431181.41528564</v>
       </c>
       <c r="C135" t="n">
-        <v>143.118141416967</v>
+        <v>143.118141528564</v>
       </c>
     </row>
     <row r="136">
@@ -2562,10 +2562,10 @@
         <v>138</v>
       </c>
       <c r="B136" t="n">
-        <v>1284501.88439084</v>
+        <v>1284501.88552217</v>
       </c>
       <c r="C136" t="n">
-        <v>128.450188439084</v>
+        <v>128.450188552217</v>
       </c>
     </row>
     <row r="137">
@@ -2573,10 +2573,10 @@
         <v>139</v>
       </c>
       <c r="B137" t="n">
-        <v>1551074.31548997</v>
+        <v>1551074.31663807</v>
       </c>
       <c r="C137" t="n">
-        <v>155.107431548997</v>
+        <v>155.107431663807</v>
       </c>
     </row>
   </sheetData>
@@ -2618,7 +2618,7 @@
         <v>101.165037376644</v>
       </c>
       <c r="C2" t="n">
-        <v>42.4772054748042</v>
+        <v>42.4772054748055</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -2629,16 +2629,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>58.3473038343102</v>
+        <v>58.34730383431</v>
       </c>
       <c r="C3" t="n">
-        <v>42.4717902108511</v>
+        <v>42.4717902108524</v>
       </c>
       <c r="D3" t="n">
-        <v>-42.3246357167058</v>
+        <v>-42.324635716706</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0127486351623407</v>
+        <v>-0.0127486351624073</v>
       </c>
       <c r="F3" t="s">
         <v>145</v>
@@ -2649,16 +2649,16 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>60.1010872013666</v>
+        <v>60.1010872013662</v>
       </c>
       <c r="C4" t="n">
-        <v>42.4652060451589</v>
+        <v>42.4652060451601</v>
       </c>
       <c r="D4" t="n">
-        <v>3.00576590828703</v>
+        <v>3.00576590828681</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0155024444685403</v>
+        <v>-0.015502444468618</v>
       </c>
       <c r="F4" t="s">
         <v>146</v>
@@ -2669,16 +2669,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>94.6648545879056</v>
+        <v>94.6648545879052</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4545576914779</v>
+        <v>42.4545576914791</v>
       </c>
       <c r="D5" t="n">
-        <v>57.5093879262688</v>
+        <v>57.509387926269</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0250754786628282</v>
+        <v>-0.0250754786629614</v>
       </c>
       <c r="F5" t="s">
         <v>146</v>
@@ -2692,13 +2692,13 @@
         <v>129.252044484291</v>
       </c>
       <c r="C6" t="n">
-        <v>42.2989805282576</v>
+        <v>42.2989805282577</v>
       </c>
       <c r="D6" t="n">
-        <v>36.5364633442369</v>
+        <v>36.5364633442373</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.366455739218585</v>
+        <v>-0.366455739221005</v>
       </c>
       <c r="F6" t="s">
         <v>146</v>
@@ -2712,13 +2712,13 @@
         <v>257.466432309015</v>
       </c>
       <c r="C7" t="n">
-        <v>42.2636224119163</v>
+        <v>42.2636224119164</v>
       </c>
       <c r="D7" t="n">
-        <v>99.1971835620036</v>
+        <v>99.1971835620037</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0835909421448955</v>
+        <v>-0.0835909421451175</v>
       </c>
       <c r="F7" t="s">
         <v>146</v>
@@ -2752,13 +2752,13 @@
         <v>350.222365072351</v>
       </c>
       <c r="C9" t="n">
-        <v>42.1617145383963</v>
+        <v>42.1617145383959</v>
       </c>
       <c r="D9" t="n">
-        <v>-12.7449640026181</v>
+        <v>-12.744964002618</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.34089088878051</v>
+        <v>-0.340890888781609</v>
       </c>
       <c r="F9" t="s">
         <v>145</v>
@@ -2772,13 +2772,13 @@
         <v>318.316550344891</v>
       </c>
       <c r="C10" t="n">
-        <v>42.1148448783309</v>
+        <v>42.1148448783313</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.11015911872699</v>
+        <v>-9.11015911872697</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.111166399608209</v>
+        <v>-0.111166399606233</v>
       </c>
       <c r="F10" t="s">
         <v>145</v>
@@ -2792,13 +2792,13 @@
         <v>269.683670445038</v>
       </c>
       <c r="C11" t="n">
-        <v>42.3405139109899</v>
+        <v>42.3405139109903</v>
       </c>
       <c r="D11" t="n">
         <v>-15.2781499570663</v>
       </c>
       <c r="E11" t="n">
-        <v>0.535842013216437</v>
+        <v>0.535842013216392</v>
       </c>
       <c r="F11" t="s">
         <v>146</v>
@@ -2812,13 +2812,13 @@
         <v>236.574897953766</v>
       </c>
       <c r="C12" t="n">
-        <v>42.4622722423436</v>
+        <v>42.462272242344</v>
       </c>
       <c r="D12" t="n">
         <v>-12.2768918253876</v>
       </c>
       <c r="E12" t="n">
-        <v>0.287569328066506</v>
+        <v>0.287569328066528</v>
       </c>
       <c r="F12" t="s">
         <v>146</v>
@@ -2832,13 +2832,13 @@
         <v>304.316723508352</v>
       </c>
       <c r="C13" t="n">
-        <v>42.3490376761143</v>
+        <v>42.3490376761151</v>
       </c>
       <c r="D13" t="n">
         <v>28.6344097114754</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.266671000513174</v>
+        <v>-0.26667100051232</v>
       </c>
       <c r="F13" t="s">
         <v>146</v>
@@ -2852,13 +2852,13 @@
         <v>360.611983899455</v>
       </c>
       <c r="C14" t="n">
-        <v>42.4362981100277</v>
+        <v>42.4362981100286</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4989046090192</v>
+        <v>18.4989046090191</v>
       </c>
       <c r="E14" t="n">
-        <v>0.206050570926108</v>
+        <v>0.206050570926331</v>
       </c>
       <c r="F14" t="s">
         <v>145</v>
@@ -2869,7 +2869,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>430.28982858528</v>
+        <v>430.289828585279</v>
       </c>
       <c r="C15" t="n">
         <v>42.8058015083304</v>
@@ -2878,7 +2878,7 @@
         <v>19.3221101341025</v>
       </c>
       <c r="E15" t="n">
-        <v>0.87072486234463</v>
+        <v>0.870724862342565</v>
       </c>
       <c r="F15" t="s">
         <v>145</v>
@@ -2915,7 +2915,7 @@
         <v>58.133357275209</v>
       </c>
       <c r="D17" t="n">
-        <v>2.30381739240648</v>
+        <v>2.3038173924065</v>
       </c>
       <c r="E17" t="n">
         <v>9.97112536493081</v>
@@ -2955,7 +2955,7 @@
         <v>71.3263883378685</v>
       </c>
       <c r="D19" t="n">
-        <v>9.71468116310361</v>
+        <v>9.71468116310366</v>
       </c>
       <c r="E19" t="n">
         <v>7.28519677361497</v>
@@ -2975,7 +2975,7 @@
         <v>96.0637570530051</v>
       </c>
       <c r="D20" t="n">
-        <v>6.37649795897122</v>
+        <v>6.37649795897119</v>
       </c>
       <c r="E20" t="n">
         <v>34.6819308976607</v>
@@ -3035,7 +3035,7 @@
         <v>93.6898032816772</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.6305437472241</v>
+        <v>-18.6305437472242</v>
       </c>
       <c r="E23" t="n">
         <v>-6.95695094593462</v>
@@ -3075,7 +3075,7 @@
         <v>86.7319028330548</v>
       </c>
       <c r="D25" t="n">
-        <v>7.34506652154057</v>
+        <v>7.34506652154054</v>
       </c>
       <c r="E25" t="n">
         <v>-5.05278577990997</v>
@@ -3092,13 +3092,13 @@
         <v>674.560615938682</v>
       </c>
       <c r="C26" t="n">
-        <v>103.77021170949</v>
+        <v>103.770211746319</v>
       </c>
       <c r="D26" t="n">
         <v>-12.1007480974727</v>
       </c>
       <c r="E26" t="n">
-        <v>19.6448000330754</v>
+        <v>19.6448000755388</v>
       </c>
       <c r="F26" t="s">
         <v>146</v>
@@ -3109,16 +3109,16 @@
         <v>104</v>
       </c>
       <c r="B27" t="n">
-        <v>674.246841013046</v>
+        <v>674.246840582289</v>
       </c>
       <c r="C27" t="n">
-        <v>107.019778508</v>
+        <v>107.019778552567</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0465154529069145</v>
+        <v>-0.0465155167643116</v>
       </c>
       <c r="E27" t="n">
-        <v>3.13150252367922</v>
+        <v>3.13150253002508</v>
       </c>
       <c r="F27" t="s">
         <v>146</v>
@@ -3129,16 +3129,16 @@
         <v>108</v>
       </c>
       <c r="B28" t="n">
-        <v>677.666929483074</v>
+        <v>677.666929055423</v>
       </c>
       <c r="C28" t="n">
-        <v>111.250994579953</v>
+        <v>111.250994632769</v>
       </c>
       <c r="D28" t="n">
-        <v>0.507245753630747</v>
+        <v>0.507245754415386</v>
       </c>
       <c r="E28" t="n">
-        <v>3.95367672307119</v>
+        <v>3.95367672913256</v>
       </c>
       <c r="F28" t="s">
         <v>145</v>
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="B29" t="n">
-        <v>681.679773803798</v>
+        <v>681.679773571627</v>
       </c>
       <c r="C29" t="n">
-        <v>115.464627024726</v>
+        <v>115.464627085805</v>
       </c>
       <c r="D29" t="n">
-        <v>0.592155843252473</v>
+        <v>0.592155872472211</v>
       </c>
       <c r="E29" t="n">
-        <v>3.78750092139213</v>
+        <v>3.78750092702054</v>
       </c>
       <c r="F29" t="s">
         <v>145</v>
@@ -3169,16 +3169,16 @@
         <v>116</v>
       </c>
       <c r="B30" t="n">
-        <v>689.844958912601</v>
+        <v>689.844959301256</v>
       </c>
       <c r="C30" t="n">
-        <v>120.823957644122</v>
+        <v>120.823957714753</v>
       </c>
       <c r="D30" t="n">
-        <v>1.19780363487105</v>
+        <v>1.19780372635208</v>
       </c>
       <c r="E30" t="n">
-        <v>4.64153460457446</v>
+        <v>4.64153461039221</v>
       </c>
       <c r="F30" t="s">
         <v>145</v>
@@ -3189,16 +3189,16 @@
         <v>120</v>
       </c>
       <c r="B31" t="n">
-        <v>692.039524666275</v>
+        <v>692.039525368949</v>
       </c>
       <c r="C31" t="n">
-        <v>124.073524442645</v>
+        <v>124.073524521015</v>
       </c>
       <c r="D31" t="n">
-        <v>0.318124489469884</v>
+        <v>0.318124534810837</v>
       </c>
       <c r="E31" t="n">
-        <v>2.68950534470533</v>
+        <v>2.6895053495378</v>
       </c>
       <c r="F31" t="s">
         <v>145</v>
@@ -3209,16 +3209,16 @@
         <v>124</v>
       </c>
       <c r="B32" t="n">
-        <v>697.800322374177</v>
+        <v>697.800323740355</v>
       </c>
       <c r="C32" t="n">
-        <v>128.304740514597</v>
+        <v>128.304740601216</v>
       </c>
       <c r="D32" t="n">
-        <v>0.832437671920605</v>
+        <v>0.832437766951988</v>
       </c>
       <c r="E32" t="n">
-        <v>3.41024895597961</v>
+        <v>3.41024896047399</v>
       </c>
       <c r="F32" t="s">
         <v>145</v>
@@ -3229,16 +3229,16 @@
         <v>128</v>
       </c>
       <c r="B33" t="n">
-        <v>703.997447236016</v>
+        <v>703.997449381648</v>
       </c>
       <c r="C33" t="n">
-        <v>132.518372959363</v>
+        <v>132.518373054243</v>
       </c>
       <c r="D33" t="n">
-        <v>0.888094296195541</v>
+        <v>0.888094406158335</v>
       </c>
       <c r="E33" t="n">
-        <v>3.2840816542439</v>
+        <v>3.28408165846625</v>
       </c>
       <c r="F33" t="s">
         <v>145</v>
@@ -3249,16 +3249,16 @@
         <v>132</v>
       </c>
       <c r="B34" t="n">
-        <v>714.20093825879</v>
+        <v>714.200941540062</v>
       </c>
       <c r="C34" t="n">
-        <v>137.877703578763</v>
+        <v>137.877703683196</v>
       </c>
       <c r="D34" t="n">
-        <v>1.44936477580049</v>
+        <v>1.44936493269621</v>
       </c>
       <c r="E34" t="n">
-        <v>4.04421703928128</v>
+        <v>4.04421704359408</v>
       </c>
       <c r="F34" t="s">
         <v>145</v>
@@ -3269,16 +3269,16 @@
         <v>136</v>
       </c>
       <c r="B35" t="n">
-        <v>718.297590727308</v>
+        <v>718.297594774888</v>
       </c>
       <c r="C35" t="n">
-        <v>141.127270377277</v>
+        <v>141.127270489449</v>
       </c>
       <c r="D35" t="n">
-        <v>0.573599424064875</v>
+        <v>0.573599528725444</v>
       </c>
       <c r="E35" t="n">
-        <v>2.35684720166347</v>
+        <v>2.35684720549085</v>
       </c>
       <c r="F35" t="s">
         <v>145</v>
@@ -3323,16 +3323,16 @@
         <v>58.3473038343098</v>
       </c>
       <c r="C2" t="n">
-        <v>155.742015536094</v>
+        <v>155.742016221748</v>
       </c>
       <c r="D2" t="n">
-        <v>-97.3947117017838</v>
+        <v>-97.3947123874381</v>
       </c>
       <c r="E2" t="n">
-        <v>42.4717902108511</v>
+        <v>42.4717902108524</v>
       </c>
       <c r="F2" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
     </row>
     <row r="3">
@@ -3343,16 +3343,16 @@
         <v>60.101087201366</v>
       </c>
       <c r="C3" t="n">
-        <v>76.4322652008593</v>
+        <v>76.4322657663486</v>
       </c>
       <c r="D3" t="n">
-        <v>-16.3311779994933</v>
+        <v>-16.3311785649827</v>
       </c>
       <c r="E3" t="n">
-        <v>42.4652060451589</v>
+        <v>42.4652060451601</v>
       </c>
       <c r="F3" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
     </row>
     <row r="4">
@@ -3363,16 +3363,16 @@
         <v>94.6648545879048</v>
       </c>
       <c r="C4" t="n">
-        <v>78.0549348248787</v>
+        <v>78.0549353838344</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6099197630261</v>
+        <v>16.6099192040704</v>
       </c>
       <c r="E4" t="n">
-        <v>42.4545576914779</v>
+        <v>42.4545576914791</v>
       </c>
       <c r="F4" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
     </row>
     <row r="5">
@@ -3383,16 +3383,16 @@
         <v>129.25204448429</v>
       </c>
       <c r="C5" t="n">
-        <v>109.858551589212</v>
+        <v>109.858552008284</v>
       </c>
       <c r="D5" t="n">
-        <v>19.3934928950776</v>
+        <v>19.3934924760064</v>
       </c>
       <c r="E5" t="n">
-        <v>42.2989805282576</v>
+        <v>42.2989805282577</v>
       </c>
       <c r="F5" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
     </row>
     <row r="6">
@@ -3403,16 +3403,16 @@
         <v>257.466432309015</v>
       </c>
       <c r="C6" t="n">
-        <v>142.475237163069</v>
+        <v>142.475237495913</v>
       </c>
       <c r="D6" t="n">
-        <v>114.991195145946</v>
+        <v>114.991194813101</v>
       </c>
       <c r="E6" t="n">
-        <v>42.2636224119163</v>
+        <v>42.2636224119164</v>
       </c>
       <c r="F6" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
     </row>
     <row r="7">
@@ -3423,16 +3423,16 @@
         <v>401.377824292983</v>
       </c>
       <c r="C7" t="n">
-        <v>262.357303095958</v>
+        <v>262.357303042798</v>
       </c>
       <c r="D7" t="n">
-        <v>139.020521197024</v>
+        <v>139.020521250184</v>
       </c>
       <c r="E7" t="n">
         <v>42.3059316046503</v>
       </c>
       <c r="F7" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
     </row>
     <row r="8">
@@ -3443,16 +3443,16 @@
         <v>350.222365072351</v>
       </c>
       <c r="C8" t="n">
-        <v>396.08553909568</v>
+        <v>396.085538552166</v>
       </c>
       <c r="D8" t="n">
-        <v>-45.8631740233296</v>
+        <v>-45.863173479815</v>
       </c>
       <c r="E8" t="n">
-        <v>42.1617145383963</v>
+        <v>42.1617145383959</v>
       </c>
       <c r="F8" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
     </row>
     <row r="9">
@@ -3463,16 +3463,16 @@
         <v>318.31655034489</v>
       </c>
       <c r="C9" t="n">
-        <v>348.61925413418</v>
+        <v>348.619253768556</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.3027037892898</v>
+        <v>-30.3027034236657</v>
       </c>
       <c r="E9" t="n">
-        <v>42.1148448783309</v>
+        <v>42.1148448783313</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
     </row>
     <row r="10">
@@ -3483,16 +3483,16 @@
         <v>269.683670445038</v>
       </c>
       <c r="C10" t="n">
-        <v>319.679345334844</v>
+        <v>319.67934512692</v>
       </c>
       <c r="D10" t="n">
-        <v>-49.9956748898066</v>
+        <v>-49.995674681882</v>
       </c>
       <c r="E10" t="n">
-        <v>42.3405139109899</v>
+        <v>42.3405139109903</v>
       </c>
       <c r="F10" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
     </row>
     <row r="11">
@@ -3503,16 +3503,16 @@
         <v>236.574897953765</v>
       </c>
       <c r="C11" t="n">
-        <v>274.020324583041</v>
+        <v>274.020324510585</v>
       </c>
       <c r="D11" t="n">
-        <v>-37.4454266292758</v>
+        <v>-37.4454265568199</v>
       </c>
       <c r="E11" t="n">
-        <v>42.4622722423436</v>
+        <v>42.462272242344</v>
       </c>
       <c r="F11" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
     </row>
     <row r="12">
@@ -3523,16 +3523,16 @@
         <v>304.316723508352</v>
       </c>
       <c r="C12" t="n">
-        <v>242.420821306542</v>
+        <v>242.420821290097</v>
       </c>
       <c r="D12" t="n">
-        <v>61.8959022018096</v>
+        <v>61.8959022182555</v>
       </c>
       <c r="E12" t="n">
-        <v>42.3490376761143</v>
+        <v>42.3490376761151</v>
       </c>
       <c r="F12" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
     </row>
     <row r="13">
@@ -3543,16 +3543,16 @@
         <v>360.611983899455</v>
       </c>
       <c r="C13" t="n">
-        <v>306.234584349886</v>
+        <v>306.234584161626</v>
       </c>
       <c r="D13" t="n">
-        <v>54.3773995495691</v>
+        <v>54.3773997378284</v>
       </c>
       <c r="E13" t="n">
-        <v>42.4362981100277</v>
+        <v>42.4362981100286</v>
       </c>
       <c r="F13" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
     </row>
     <row r="14">
@@ -3563,16 +3563,16 @@
         <v>430.289828585279</v>
       </c>
       <c r="C14" t="n">
-        <v>359.66115537275</v>
+        <v>359.661155071036</v>
       </c>
       <c r="D14" t="n">
-        <v>70.6286732125293</v>
+        <v>70.6286735142429</v>
       </c>
       <c r="E14" t="n">
         <v>42.8058015083304</v>
       </c>
       <c r="F14" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
     </row>
     <row r="15">
@@ -3583,16 +3583,16 @@
         <v>566.541738110914</v>
       </c>
       <c r="C15" t="n">
-        <v>454.762687147777</v>
+        <v>454.762688727166</v>
       </c>
       <c r="D15" t="n">
-        <v>111.779050963137</v>
+        <v>111.779049383748</v>
       </c>
       <c r="E15" t="n">
         <v>52.8623828139412</v>
       </c>
       <c r="F15" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
     </row>
     <row r="16">
@@ -3603,16 +3603,16 @@
         <v>579.593825208755</v>
       </c>
       <c r="C16" t="n">
-        <v>569.171219457365</v>
+        <v>569.171219819474</v>
       </c>
       <c r="D16" t="n">
-        <v>10.4226057513901</v>
+        <v>10.422605389281</v>
       </c>
       <c r="E16" t="n">
         <v>58.133357275209</v>
       </c>
       <c r="F16" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
     </row>
     <row r="17">
@@ -3623,16 +3623,16 @@
         <v>637.096554399705</v>
       </c>
       <c r="C17" t="n">
-        <v>591.976912310196</v>
+        <v>591.976913422973</v>
       </c>
       <c r="D17" t="n">
-        <v>45.1196420895098</v>
+        <v>45.1196409767326</v>
       </c>
       <c r="E17" t="n">
         <v>66.4829729383598</v>
       </c>
       <c r="F17" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
     </row>
     <row r="18">
@@ -3643,16 +3643,16 @@
         <v>698.988453360756</v>
       </c>
       <c r="C18" t="n">
-        <v>636.506525973244</v>
+        <v>636.506526350527</v>
       </c>
       <c r="D18" t="n">
-        <v>62.4819273875117</v>
+        <v>62.481927010229</v>
       </c>
       <c r="E18" t="n">
         <v>71.3263883378685</v>
       </c>
       <c r="F18" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
     </row>
     <row r="19">
@@ -3663,16 +3663,16 @@
         <v>743.559437822749</v>
       </c>
       <c r="C19" t="n">
-        <v>756.880001251466</v>
+        <v>756.880005844979</v>
       </c>
       <c r="D19" t="n">
-        <v>-13.3205634287168</v>
+        <v>-13.32056802223</v>
       </c>
       <c r="E19" t="n">
         <v>96.0637570530051</v>
       </c>
       <c r="F19" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
     </row>
     <row r="20">
@@ -3683,16 +3683,16 @@
         <v>742.49</v>
       </c>
       <c r="C20" t="n">
-        <v>739.167882046324</v>
+        <v>739.167882607774</v>
       </c>
       <c r="D20" t="n">
-        <v>3.32211795367564</v>
+        <v>3.32211739222626</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
     </row>
     <row r="21">
@@ -3703,16 +3703,16 @@
         <v>842.728</v>
       </c>
       <c r="C21" t="n">
-        <v>728.946122136279</v>
+        <v>728.946122096568</v>
       </c>
       <c r="D21" t="n">
-        <v>113.781877863721</v>
+        <v>113.781877903432</v>
       </c>
       <c r="E21" t="n">
         <v>100.695112890417</v>
       </c>
       <c r="F21" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
     </row>
     <row r="22">
@@ -3723,16 +3723,16 @@
         <v>685.723191289893</v>
       </c>
       <c r="C22" t="n">
-        <v>798.7821690559</v>
+        <v>798.782167056885</v>
       </c>
       <c r="D22" t="n">
-        <v>-113.058977766007</v>
+        <v>-113.058975766993</v>
       </c>
       <c r="E22" t="n">
         <v>93.6898032816772</v>
       </c>
       <c r="F22" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
     </row>
     <row r="23">
@@ -3743,16 +3743,16 @@
         <v>714.913853878923</v>
       </c>
       <c r="C23" t="n">
-        <v>665.258777794945</v>
+        <v>665.258777125421</v>
       </c>
       <c r="D23" t="n">
-        <v>49.6550760839779</v>
+        <v>49.6550767535016</v>
       </c>
       <c r="E23" t="n">
         <v>91.347496127699</v>
       </c>
       <c r="F23" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
     </row>
     <row r="24">
@@ -3763,16 +3763,16 @@
         <v>767.424752018039</v>
       </c>
       <c r="C24" t="n">
-        <v>684.974002911779</v>
+        <v>684.974001603633</v>
       </c>
       <c r="D24" t="n">
-        <v>82.45074910626</v>
+        <v>82.4507504144055</v>
       </c>
       <c r="E24" t="n">
         <v>86.7319028330548</v>
       </c>
       <c r="F24" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
     </row>
     <row r="25">
@@ -3783,16 +3783,16 @@
         <v>674.560615938681</v>
       </c>
       <c r="C25" t="n">
-        <v>800.086834478748</v>
+        <v>800.086837681915</v>
       </c>
       <c r="D25" t="n">
-        <v>-125.526218540067</v>
+        <v>-125.526221743234</v>
       </c>
       <c r="E25" t="n">
-        <v>103.77021170949</v>
+        <v>103.770211746319</v>
       </c>
       <c r="F25" t="n">
-        <v>155.292146652219</v>
+        <v>155.292131893717</v>
       </c>
     </row>
   </sheetData>
@@ -3846,34 +3846,34 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>9.43429602011821</v>
+        <v>9.43429602010574</v>
       </c>
       <c r="C2" t="n">
-        <v>-186.115112664519</v>
+        <v>-186.115116197947</v>
       </c>
       <c r="D2" t="n">
-        <v>35.2695780808856</v>
+        <v>35.2695779968113</v>
       </c>
       <c r="E2" t="n">
-        <v>155.742015536094</v>
+        <v>155.742016221748</v>
       </c>
       <c r="F2" t="n">
         <v>58.3473038343098</v>
       </c>
       <c r="G2" t="n">
-        <v>-97.3947117017838</v>
+        <v>-97.3947123874381</v>
       </c>
       <c r="H2" t="n">
-        <v>-28.6879914765649</v>
+        <v>-28.6879914600948</v>
       </c>
       <c r="I2" t="n">
-        <v>6.58158660432072</v>
+        <v>6.58158653671646</v>
       </c>
       <c r="J2" t="n">
-        <v>58.3473038343102</v>
+        <v>58.34730383431</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000184741111297626</v>
       </c>
     </row>
     <row r="3">
@@ -3884,31 +3884,31 @@
         <v>12.1937909319798</v>
       </c>
       <c r="C3" t="n">
-        <v>-186.115112664519</v>
+        <v>-186.115116197947</v>
       </c>
       <c r="D3" t="n">
-        <v>43.8160998590024</v>
+        <v>43.8161003705038</v>
       </c>
       <c r="E3" t="n">
-        <v>155.742015536094</v>
+        <v>155.742016221748</v>
       </c>
       <c r="F3" t="n">
         <v>58.3473038343098</v>
       </c>
       <c r="G3" t="n">
-        <v>-97.3947117017838</v>
+        <v>-97.3947123874381</v>
       </c>
       <c r="H3" t="n">
-        <v>-26.9522660561173</v>
+        <v>-26.9522661148007</v>
       </c>
       <c r="I3" t="n">
-        <v>16.8638338028851</v>
+        <v>16.8638342557031</v>
       </c>
       <c r="J3" t="n">
-        <v>58.3473038343102</v>
+        <v>58.34730383431</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000184741111297626</v>
       </c>
     </row>
     <row r="4">
@@ -3916,34 +3916,34 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>3.45889465139194</v>
+        <v>3.45889465139056</v>
       </c>
       <c r="C4" t="n">
-        <v>-186.115112664519</v>
+        <v>-186.115116197947</v>
       </c>
       <c r="D4" t="n">
-        <v>16.7629674285917</v>
+        <v>16.7629660549779</v>
       </c>
       <c r="E4" t="n">
-        <v>155.742015536094</v>
+        <v>155.742016221748</v>
       </c>
       <c r="F4" t="n">
         <v>58.3473038343098</v>
       </c>
       <c r="G4" t="n">
-        <v>-97.3947117017838</v>
+        <v>-97.3947123874381</v>
       </c>
       <c r="H4" t="n">
-        <v>-23.480815215222</v>
+        <v>-23.4808154242124</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.7178477866303</v>
+        <v>-6.71784936923454</v>
       </c>
       <c r="J4" t="n">
-        <v>58.3473038343102</v>
+        <v>58.34730383431</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000184741111297626</v>
       </c>
     </row>
     <row r="5">
@@ -3951,34 +3951,34 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>17.3848086073612</v>
+        <v>17.3848086073763</v>
       </c>
       <c r="C5" t="n">
-        <v>-186.115112664519</v>
+        <v>-186.115116197947</v>
       </c>
       <c r="D5" t="n">
-        <v>59.8933701676138</v>
+        <v>59.893371799455</v>
       </c>
       <c r="E5" t="n">
-        <v>155.742015536094</v>
+        <v>155.742016221748</v>
       </c>
       <c r="F5" t="n">
         <v>58.3473038343098</v>
       </c>
       <c r="G5" t="n">
-        <v>-97.3947117017838</v>
+        <v>-97.3947123874381</v>
       </c>
       <c r="H5" t="n">
-        <v>-18.2736389538792</v>
+        <v>-18.27363938833</v>
       </c>
       <c r="I5" t="n">
-        <v>41.6197312137347</v>
+        <v>41.619732411125</v>
       </c>
       <c r="J5" t="n">
-        <v>58.3473038343102</v>
+        <v>58.34730383431</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000184741111297626</v>
       </c>
     </row>
     <row r="6">
@@ -3986,34 +3986,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.45592239730524</v>
+        <v>9.45592239729289</v>
       </c>
       <c r="C6" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
       <c r="D6" t="n">
-        <v>15.5167862943437</v>
+        <v>15.5167870020628</v>
       </c>
       <c r="E6" t="n">
-        <v>76.4425373202073</v>
+        <v>76.4425411529435</v>
       </c>
       <c r="F6" t="n">
         <v>60.101087201366</v>
       </c>
       <c r="G6" t="n">
-        <v>-16.3414501188413</v>
+        <v>-16.3414539515776</v>
       </c>
       <c r="H6" t="n">
-        <v>-11.3307372720887</v>
+        <v>-11.3307380071534</v>
       </c>
       <c r="I6" t="n">
-        <v>4.18604902225504</v>
+        <v>4.18604899490934</v>
       </c>
       <c r="J6" t="n">
-        <v>60.1010872013666</v>
+        <v>60.1010872013662</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000000000000611066752753686</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="7">
@@ -4024,31 +4024,31 @@
         <v>12.1917626444412</v>
       </c>
       <c r="C7" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
       <c r="D7" t="n">
-        <v>23.9900464381075</v>
+        <v>23.9900477362969</v>
       </c>
       <c r="E7" t="n">
-        <v>76.4425373202073</v>
+        <v>76.4425411529435</v>
       </c>
       <c r="F7" t="n">
         <v>60.101087201366</v>
       </c>
       <c r="G7" t="n">
-        <v>-16.3414501188413</v>
+        <v>-16.3414539515776</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.65542670242108</v>
+        <v>-5.65542764697917</v>
       </c>
       <c r="I7" t="n">
-        <v>18.3346197356864</v>
+        <v>18.3346200893177</v>
       </c>
       <c r="J7" t="n">
-        <v>60.1010872013666</v>
+        <v>60.1010872013662</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000000000000611066752753686</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="8">
@@ -4056,34 +4056,34 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>3.46832106816489</v>
+        <v>3.46832106816347</v>
       </c>
       <c r="C8" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.02760925362905</v>
+        <v>-3.02760983808295</v>
       </c>
       <c r="E8" t="n">
-        <v>76.4425373202073</v>
+        <v>76.4425411529435</v>
       </c>
       <c r="F8" t="n">
         <v>60.101087201366</v>
       </c>
       <c r="G8" t="n">
-        <v>-16.3414501188413</v>
+        <v>-16.3414539515776</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.24770724487637</v>
+        <v>-1.24770830780718</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.27531649850542</v>
+        <v>-4.27531814589013</v>
       </c>
       <c r="J8" t="n">
-        <v>60.1010872013666</v>
+        <v>60.1010872013662</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000000000000611066752753686</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="9">
@@ -4091,34 +4091,34 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>17.3491999352476</v>
+        <v>17.3491999352625</v>
       </c>
       <c r="C9" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
       <c r="D9" t="n">
-        <v>39.9633138413851</v>
+        <v>39.9633162526668</v>
       </c>
       <c r="E9" t="n">
-        <v>76.4425373202073</v>
+        <v>76.4425411529435</v>
       </c>
       <c r="F9" t="n">
         <v>60.101087201366</v>
       </c>
       <c r="G9" t="n">
-        <v>-16.3414501188413</v>
+        <v>-16.3414539515776</v>
       </c>
       <c r="H9" t="n">
-        <v>1.89242110054546</v>
+        <v>1.89242001036252</v>
       </c>
       <c r="I9" t="n">
-        <v>41.8557349419305</v>
+        <v>41.8557362630293</v>
       </c>
       <c r="J9" t="n">
-        <v>60.1010872013666</v>
+        <v>60.1010872013662</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000000000000611066752753686</v>
+        <v>0.000000000000270006239588838</v>
       </c>
     </row>
     <row r="10">
@@ -4126,34 +4126,34 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>9.4980531804306</v>
+        <v>9.49805318041849</v>
       </c>
       <c r="C10" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
       <c r="D10" t="n">
-        <v>16.0611729038865</v>
+        <v>16.0611736149113</v>
       </c>
       <c r="E10" t="n">
-        <v>78.0651658992828</v>
+        <v>78.0651697065713</v>
       </c>
       <c r="F10" t="n">
         <v>94.6648545879048</v>
       </c>
       <c r="G10" t="n">
-        <v>16.599688688622</v>
+        <v>16.5996848813335</v>
       </c>
       <c r="H10" t="n">
-        <v>3.76495833384439</v>
+        <v>3.76495730752994</v>
       </c>
       <c r="I10" t="n">
-        <v>19.8261312377309</v>
+        <v>19.8261309224413</v>
       </c>
       <c r="J10" t="n">
-        <v>94.6648545879056</v>
+        <v>94.6648545879052</v>
       </c>
       <c r="K10" t="n">
-        <v>0.000000000000810018718766514</v>
+        <v>0.000000000000383693077310454</v>
       </c>
     </row>
     <row r="11">
@@ -4164,31 +4164,31 @@
         <v>12.1810595075462</v>
       </c>
       <c r="C11" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
       <c r="D11" t="n">
-        <v>24.3707993891368</v>
+        <v>24.3708006792289</v>
       </c>
       <c r="E11" t="n">
-        <v>78.0651658992828</v>
+        <v>78.0651697065713</v>
       </c>
       <c r="F11" t="n">
         <v>94.6648545879048</v>
       </c>
       <c r="G11" t="n">
-        <v>16.599688688622</v>
+        <v>16.5996848813335</v>
       </c>
       <c r="H11" t="n">
-        <v>4.66795876248848</v>
+        <v>4.66795779151832</v>
       </c>
       <c r="I11" t="n">
-        <v>29.0387581516253</v>
+        <v>29.0387584707472</v>
       </c>
       <c r="J11" t="n">
-        <v>94.6648545879056</v>
+        <v>94.6648545879052</v>
       </c>
       <c r="K11" t="n">
-        <v>0.000000000000810018718766514</v>
+        <v>0.000000000000383693077310454</v>
       </c>
     </row>
     <row r="12">
@@ -4196,34 +4196,34 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>3.48224738555144</v>
+        <v>3.48224738554993</v>
       </c>
       <c r="C12" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.57057561569012</v>
+        <v>-2.57057620292619</v>
       </c>
       <c r="E12" t="n">
-        <v>78.0651658992828</v>
+        <v>78.0651697065713</v>
       </c>
       <c r="F12" t="n">
         <v>94.6648545879048</v>
       </c>
       <c r="G12" t="n">
-        <v>16.599688688622</v>
+        <v>16.5996848813335</v>
       </c>
       <c r="H12" t="n">
-        <v>4.60142238647773</v>
+        <v>4.60142146232766</v>
       </c>
       <c r="I12" t="n">
-        <v>2.03084677078762</v>
+        <v>2.03084525940147</v>
       </c>
       <c r="J12" t="n">
-        <v>94.6648545879056</v>
+        <v>94.6648545879052</v>
       </c>
       <c r="K12" t="n">
-        <v>0.000000000000810018718766514</v>
+        <v>0.000000000000383693077310454</v>
       </c>
     </row>
     <row r="13">
@@ -4231,34 +4231,34 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>17.2931976179497</v>
+        <v>17.2931976179645</v>
       </c>
       <c r="C13" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
       <c r="D13" t="n">
-        <v>40.2037692219496</v>
+        <v>40.2037716153573</v>
       </c>
       <c r="E13" t="n">
-        <v>78.0651658992828</v>
+        <v>78.0651697065713</v>
       </c>
       <c r="F13" t="n">
         <v>94.6648545879048</v>
       </c>
       <c r="G13" t="n">
-        <v>16.599688688622</v>
+        <v>16.5996848813335</v>
       </c>
       <c r="H13" t="n">
-        <v>3.56534920581216</v>
+        <v>3.56534831995794</v>
       </c>
       <c r="I13" t="n">
-        <v>43.7691184277618</v>
+        <v>43.7691199353152</v>
       </c>
       <c r="J13" t="n">
-        <v>94.6648545879056</v>
+        <v>94.6648545879052</v>
       </c>
       <c r="K13" t="n">
-        <v>0.000000000000810018718766514</v>
+        <v>0.000000000000383693077310454</v>
       </c>
     </row>
     <row r="14">
@@ -4266,34 +4266,34 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>9.53219834761259</v>
+        <v>9.53219834760066</v>
       </c>
       <c r="C14" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
       <c r="D14" t="n">
-        <v>24.2380898887619</v>
+        <v>24.2380904883727</v>
       </c>
       <c r="E14" t="n">
-        <v>109.86798227966</v>
+        <v>109.867985578236</v>
       </c>
       <c r="F14" t="n">
         <v>129.25204448429</v>
       </c>
       <c r="G14" t="n">
-        <v>19.3840622046297</v>
+        <v>19.3840589060543</v>
       </c>
       <c r="H14" t="n">
-        <v>1.55973922049174</v>
+        <v>1.55973836440918</v>
       </c>
       <c r="I14" t="n">
-        <v>25.7978291092536</v>
+        <v>25.7978288527819</v>
       </c>
       <c r="J14" t="n">
         <v>129.252044484291</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000000000000966338120633736</v>
+        <v>0.000000000000795807864051312</v>
       </c>
     </row>
     <row r="15">
@@ -4301,34 +4301,34 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>12.1448667467563</v>
+        <v>12.1448667467561</v>
       </c>
       <c r="C15" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
       <c r="D15" t="n">
-        <v>32.3298704810355</v>
+        <v>32.3298716445326</v>
       </c>
       <c r="E15" t="n">
-        <v>109.86798227966</v>
+        <v>109.867985578236</v>
       </c>
       <c r="F15" t="n">
         <v>129.25204448429</v>
       </c>
       <c r="G15" t="n">
-        <v>19.3840622046297</v>
+        <v>19.3840589060543</v>
       </c>
       <c r="H15" t="n">
-        <v>2.07200575862994</v>
+        <v>2.07200492703151</v>
       </c>
       <c r="I15" t="n">
-        <v>34.4018762396655</v>
+        <v>34.4018765715641</v>
       </c>
       <c r="J15" t="n">
         <v>129.252044484291</v>
       </c>
       <c r="K15" t="n">
-        <v>0.000000000000966338120633736</v>
+        <v>0.000000000000795807864051312</v>
       </c>
     </row>
     <row r="16">
@@ -4336,34 +4336,34 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>3.44863939510121</v>
+        <v>3.44863939509929</v>
       </c>
       <c r="C16" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
       <c r="D16" t="n">
-        <v>5.39650085280999</v>
+        <v>5.39650013953603</v>
       </c>
       <c r="E16" t="n">
-        <v>109.86798227966</v>
+        <v>109.867985578236</v>
       </c>
       <c r="F16" t="n">
         <v>129.25204448429</v>
       </c>
       <c r="G16" t="n">
-        <v>19.3840622046297</v>
+        <v>19.3840589060543</v>
       </c>
       <c r="H16" t="n">
-        <v>5.10214882022676</v>
+        <v>5.10214800782493</v>
       </c>
       <c r="I16" t="n">
-        <v>10.4986496730368</v>
+        <v>10.498648147361</v>
       </c>
       <c r="J16" t="n">
         <v>129.252044484291</v>
       </c>
       <c r="K16" t="n">
-        <v>0.000000000000966338120633736</v>
+        <v>0.000000000000795807864051312</v>
       </c>
     </row>
     <row r="17">
@@ -4371,34 +4371,34 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>17.1732760387875</v>
+        <v>17.1732760388017</v>
       </c>
       <c r="C17" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
       <c r="D17" t="n">
-        <v>47.9035210570528</v>
+        <v>47.9035233057943</v>
       </c>
       <c r="E17" t="n">
-        <v>109.86798227966</v>
+        <v>109.867985578236</v>
       </c>
       <c r="F17" t="n">
         <v>129.25204448429</v>
       </c>
       <c r="G17" t="n">
-        <v>19.3840622046297</v>
+        <v>19.3840589060543</v>
       </c>
       <c r="H17" t="n">
-        <v>10.6501684052822</v>
+        <v>10.6501676067895</v>
       </c>
       <c r="I17" t="n">
-        <v>58.553689462335</v>
+        <v>58.5536909125837</v>
       </c>
       <c r="J17" t="n">
         <v>129.252044484291</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000000000000966338120633736</v>
+        <v>0.000000000000795807864051312</v>
       </c>
     </row>
     <row r="18">
@@ -4406,34 +4406,34 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>9.94389849691342</v>
+        <v>9.94389849690385</v>
       </c>
       <c r="C18" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
       <c r="D18" t="n">
-        <v>33.6945256215777</v>
+        <v>33.6945261969315</v>
       </c>
       <c r="E18" t="n">
-        <v>142.483856543378</v>
+        <v>142.483859381863</v>
       </c>
       <c r="F18" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="G18" t="n">
-        <v>114.982575765636</v>
+        <v>114.982572927151</v>
       </c>
       <c r="H18" t="n">
-        <v>18.7160645137963</v>
+        <v>18.7160637239251</v>
       </c>
       <c r="I18" t="n">
-        <v>52.410590135374</v>
+        <v>52.4105899208566</v>
       </c>
       <c r="J18" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00000000000085265128291212</v>
+        <v>0.000000000000625277607468888</v>
       </c>
     </row>
     <row r="19">
@@ -4441,34 +4441,34 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>11.9749179714078</v>
+        <v>11.974917971407</v>
       </c>
       <c r="C19" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
       <c r="D19" t="n">
-        <v>39.9848623407838</v>
+        <v>39.9848633544868</v>
       </c>
       <c r="E19" t="n">
-        <v>142.483856543378</v>
+        <v>142.483859381863</v>
       </c>
       <c r="F19" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="G19" t="n">
-        <v>114.982575765636</v>
+        <v>114.982572927151</v>
       </c>
       <c r="H19" t="n">
-        <v>25.9542547282471</v>
+        <v>25.9542539739245</v>
       </c>
       <c r="I19" t="n">
-        <v>65.9391170690309</v>
+        <v>65.9391173284113</v>
       </c>
       <c r="J19" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00000000000085265128291212</v>
+        <v>0.000000000000625277607468888</v>
       </c>
     </row>
     <row r="20">
@@ -4476,34 +4476,34 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>3.39658042340207</v>
+        <v>3.39658042339941</v>
       </c>
       <c r="C20" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4166130720764</v>
+        <v>13.4166122344503</v>
       </c>
       <c r="E20" t="n">
-        <v>142.483856543378</v>
+        <v>142.483859381863</v>
       </c>
       <c r="F20" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="G20" t="n">
-        <v>114.982575765636</v>
+        <v>114.982572927151</v>
       </c>
       <c r="H20" t="n">
-        <v>32.3647390486347</v>
+        <v>32.3647383567877</v>
       </c>
       <c r="I20" t="n">
-        <v>45.7813521207111</v>
+        <v>45.781350591238</v>
       </c>
       <c r="J20" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00000000000085265128291212</v>
+        <v>0.000000000000625277607468888</v>
       </c>
     </row>
     <row r="21">
@@ -4511,34 +4511,34 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>16.9482255201931</v>
+        <v>16.9482255202062</v>
       </c>
       <c r="C21" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
       <c r="D21" t="n">
-        <v>55.3878555089404</v>
+        <v>55.3878575959945</v>
       </c>
       <c r="E21" t="n">
-        <v>142.483856543378</v>
+        <v>142.483859381863</v>
       </c>
       <c r="F21" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="G21" t="n">
-        <v>114.982575765636</v>
+        <v>114.982572927151</v>
       </c>
       <c r="H21" t="n">
-        <v>37.947517474959</v>
+        <v>37.9475168725148</v>
       </c>
       <c r="I21" t="n">
-        <v>93.3353729838994</v>
+        <v>93.3353744685093</v>
       </c>
       <c r="J21" t="n">
         <v>257.466432309015</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00000000000085265128291212</v>
+        <v>0.000000000000625277607468888</v>
       </c>
     </row>
     <row r="22">
@@ -4546,34 +4546,34 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>10.3705444540626</v>
+        <v>10.3705444540554</v>
       </c>
       <c r="C22" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
       <c r="D22" t="n">
-        <v>64.9529197490644</v>
+        <v>64.9529199757094</v>
       </c>
       <c r="E22" t="n">
-        <v>262.362953746613</v>
+        <v>262.36295483106</v>
       </c>
       <c r="F22" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="G22" t="n">
-        <v>139.014870546369</v>
+        <v>139.014869461923</v>
       </c>
       <c r="H22" t="n">
-        <v>42.7025900072201</v>
+        <v>42.7025895211057</v>
       </c>
       <c r="I22" t="n">
-        <v>107.655509756284</v>
+        <v>107.655509496815</v>
       </c>
       <c r="J22" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="K22" t="n">
-        <v>0.00000000000056843418860808</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="23">
@@ -4581,34 +4581,34 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>11.824196256855</v>
+        <v>11.8241962568536</v>
       </c>
       <c r="C23" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
       <c r="D23" t="n">
-        <v>69.4550722034726</v>
+        <v>69.4550727438537</v>
       </c>
       <c r="E23" t="n">
-        <v>262.362953746613</v>
+        <v>262.36295483106</v>
       </c>
       <c r="F23" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="G23" t="n">
-        <v>139.014870546369</v>
+        <v>139.014869461923</v>
       </c>
       <c r="H23" t="n">
-        <v>41.4250700718735</v>
+        <v>41.4250697182921</v>
       </c>
       <c r="I23" t="n">
-        <v>110.880142275346</v>
+        <v>110.880142462146</v>
       </c>
       <c r="J23" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00000000000056843418860808</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="24">
@@ -4616,34 +4616,34 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>3.36455201044131</v>
+        <v>3.36455201043794</v>
       </c>
       <c r="C24" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
       <c r="D24" t="n">
-        <v>43.2544318339924</v>
+        <v>43.2544305486596</v>
       </c>
       <c r="E24" t="n">
-        <v>262.362953746613</v>
+        <v>262.36295483106</v>
       </c>
       <c r="F24" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="G24" t="n">
-        <v>139.014870546369</v>
+        <v>139.014869461923</v>
       </c>
       <c r="H24" t="n">
-        <v>34.1149576689192</v>
+        <v>34.114957464074</v>
       </c>
       <c r="I24" t="n">
-        <v>77.3693895029116</v>
+        <v>77.3693880127336</v>
       </c>
       <c r="J24" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00000000000056843418860808</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="25">
@@ -4651,34 +4651,34 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>16.7466388832914</v>
+        <v>16.7466388833034</v>
       </c>
       <c r="C25" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
       <c r="D25" t="n">
-        <v>84.7005299600837</v>
+        <v>84.7005315628371</v>
       </c>
       <c r="E25" t="n">
-        <v>262.362953746613</v>
+        <v>262.36295483106</v>
       </c>
       <c r="F25" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="G25" t="n">
-        <v>139.014870546369</v>
+        <v>139.014869461923</v>
       </c>
       <c r="H25" t="n">
-        <v>20.7722527983573</v>
+        <v>20.7722527584513</v>
       </c>
       <c r="I25" t="n">
-        <v>105.472782758441</v>
+        <v>105.472784321288</v>
       </c>
       <c r="J25" t="n">
         <v>401.377824292983</v>
       </c>
       <c r="K25" t="n">
-        <v>0.00000000000056843418860808</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="26">
@@ -4686,34 +4686,34 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>10.7408214718216</v>
+        <v>10.7408214718168</v>
       </c>
       <c r="C26" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
       <c r="D26" t="n">
-        <v>99.6426090573907</v>
+        <v>99.642608865944</v>
       </c>
       <c r="E26" t="n">
-        <v>396.087863436782</v>
+        <v>396.087862498063</v>
       </c>
       <c r="F26" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="G26" t="n">
-        <v>-45.8654983644314</v>
+        <v>-45.8654974257124</v>
       </c>
       <c r="H26" t="n">
-        <v>1.39695546018769</v>
+        <v>1.39695560142422</v>
       </c>
       <c r="I26" t="n">
-        <v>101.039564517578</v>
+        <v>101.039564467368</v>
       </c>
       <c r="J26" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="K26" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000028421709430404</v>
       </c>
     </row>
     <row r="27">
@@ -4721,34 +4721,34 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>11.646641871478</v>
+        <v>11.6466418714765</v>
       </c>
       <c r="C27" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
       <c r="D27" t="n">
-        <v>102.448054988619</v>
+        <v>102.44805499267</v>
       </c>
       <c r="E27" t="n">
-        <v>396.087863436782</v>
+        <v>396.087862498063</v>
       </c>
       <c r="F27" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="G27" t="n">
-        <v>-45.8654983644314</v>
+        <v>-45.8654974257124</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.4984954955983</v>
+        <v>-11.4984952445275</v>
       </c>
       <c r="I27" t="n">
-        <v>90.9495594930202</v>
+        <v>90.9495597481429</v>
       </c>
       <c r="J27" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="K27" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000028421709430404</v>
       </c>
     </row>
     <row r="28">
@@ -4756,34 +4756,34 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>3.63961093490583</v>
+        <v>3.63961093490175</v>
       </c>
       <c r="C28" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
       <c r="D28" t="n">
-        <v>77.6492180770822</v>
+        <v>77.6492163530987</v>
       </c>
       <c r="E28" t="n">
-        <v>396.087863436782</v>
+        <v>396.087862498063</v>
       </c>
       <c r="F28" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="G28" t="n">
-        <v>-45.8654983644314</v>
+        <v>-45.8654974257124</v>
       </c>
       <c r="H28" t="n">
-        <v>-17.9141000690008</v>
+        <v>-17.9140997794039</v>
       </c>
       <c r="I28" t="n">
-        <v>59.7351180080814</v>
+        <v>59.7351165736948</v>
       </c>
       <c r="J28" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000028421709430404</v>
       </c>
     </row>
     <row r="29">
@@ -4791,34 +4791,34 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>16.1346402601908</v>
+        <v>16.1346402602008</v>
       </c>
       <c r="C29" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
       <c r="D29" t="n">
-        <v>116.347981313691</v>
+        <v>116.34798228635</v>
       </c>
       <c r="E29" t="n">
-        <v>396.087863436782</v>
+        <v>396.087862498063</v>
       </c>
       <c r="F29" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="G29" t="n">
-        <v>-45.8654983644314</v>
+        <v>-45.8654974257124</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.8498582600197</v>
+        <v>-17.8498580032049</v>
       </c>
       <c r="I29" t="n">
-        <v>98.4981230536709</v>
+        <v>98.4981242831451</v>
       </c>
       <c r="J29" t="n">
         <v>350.222365072351</v>
       </c>
       <c r="K29" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.00000000000028421709430404</v>
       </c>
     </row>
     <row r="30">
@@ -4826,34 +4826,34 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>11.1816037184879</v>
+        <v>11.1816037184858</v>
       </c>
       <c r="C30" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
       <c r="D30" t="n">
-        <v>89.1777825742411</v>
+        <v>89.177782660079</v>
       </c>
       <c r="E30" t="n">
-        <v>348.622751606101</v>
+        <v>348.622751385867</v>
       </c>
       <c r="F30" t="n">
         <v>318.31655034489</v>
       </c>
       <c r="G30" t="n">
-        <v>-30.3062012612101</v>
+        <v>-30.3062010409764</v>
       </c>
       <c r="H30" t="n">
-        <v>-11.305770068655</v>
+        <v>-11.3057699159305</v>
       </c>
       <c r="I30" t="n">
-        <v>77.872012505586</v>
+        <v>77.8720127441485</v>
       </c>
       <c r="J30" t="n">
         <v>318.316550344891</v>
       </c>
       <c r="K30" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000511590769747272</v>
       </c>
     </row>
     <row r="31">
@@ -4861,34 +4861,34 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>11.5275263743065</v>
+        <v>11.527526374305</v>
       </c>
       <c r="C31" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
       <c r="D31" t="n">
-        <v>90.2491509245828</v>
+        <v>90.2491510850777</v>
       </c>
       <c r="E31" t="n">
-        <v>348.622751606101</v>
+        <v>348.622751385867</v>
       </c>
       <c r="F31" t="n">
         <v>318.31655034489</v>
       </c>
       <c r="G31" t="n">
-        <v>-30.3062012612101</v>
+        <v>-30.3062010409764</v>
       </c>
       <c r="H31" t="n">
-        <v>-7.19644689076812</v>
+        <v>-7.19644681874616</v>
       </c>
       <c r="I31" t="n">
-        <v>83.0527040338147</v>
+        <v>83.0527042663316</v>
       </c>
       <c r="J31" t="n">
         <v>318.316550344891</v>
       </c>
       <c r="K31" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000511590769747272</v>
       </c>
     </row>
     <row r="32">
@@ -4896,34 +4896,34 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>3.93494656467575</v>
+        <v>3.93494656467131</v>
       </c>
       <c r="C32" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
       <c r="D32" t="n">
-        <v>66.7339241284864</v>
+        <v>66.7339226503887</v>
       </c>
       <c r="E32" t="n">
-        <v>348.622751606101</v>
+        <v>348.622751385867</v>
       </c>
       <c r="F32" t="n">
         <v>318.31655034489</v>
       </c>
       <c r="G32" t="n">
-        <v>-30.3062012612101</v>
+        <v>-30.3062010409764</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.52188872635897</v>
+        <v>-5.52188871165178</v>
       </c>
       <c r="I32" t="n">
-        <v>61.2120354021274</v>
+        <v>61.2120339387369</v>
       </c>
       <c r="J32" t="n">
         <v>318.316550344891</v>
       </c>
       <c r="K32" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000511590769747272</v>
       </c>
     </row>
     <row r="33">
@@ -4931,34 +4931,34 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>15.4707682208608</v>
+        <v>15.4707682208692</v>
       </c>
       <c r="C33" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
       <c r="D33" t="n">
-        <v>102.46189397879</v>
+        <v>102.461894990321</v>
       </c>
       <c r="E33" t="n">
-        <v>348.622751606101</v>
+        <v>348.622751385867</v>
       </c>
       <c r="F33" t="n">
         <v>318.31655034489</v>
       </c>
       <c r="G33" t="n">
-        <v>-30.3062012612101</v>
+        <v>-30.3062010409764</v>
       </c>
       <c r="H33" t="n">
-        <v>-6.28209557542758</v>
+        <v>-6.28209559464739</v>
       </c>
       <c r="I33" t="n">
-        <v>96.1797984033627</v>
+        <v>96.179799395674</v>
       </c>
       <c r="J33" t="n">
         <v>318.316550344891</v>
       </c>
       <c r="K33" t="n">
-        <v>0.000000000000397903932025656</v>
+        <v>0.000000000000511590769747272</v>
       </c>
     </row>
     <row r="34">
@@ -4966,34 +4966,34 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>11.0979545641313</v>
+        <v>11.0979545641297</v>
       </c>
       <c r="C34" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
       <c r="D34" t="n">
-        <v>81.5091848085474</v>
+        <v>81.5091849882317</v>
       </c>
       <c r="E34" t="n">
-        <v>319.683577578662</v>
+        <v>319.683577854721</v>
       </c>
       <c r="F34" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="G34" t="n">
-        <v>-49.9999071336239</v>
+        <v>-49.9999074096829</v>
       </c>
       <c r="H34" t="n">
-        <v>-9.47706743797394</v>
+        <v>-9.477067467733</v>
       </c>
       <c r="I34" t="n">
-        <v>72.0321173705735</v>
+        <v>72.0321175204987</v>
       </c>
       <c r="J34" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="K34" t="n">
-        <v>0.000000000000170530256582424</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="35">
@@ -5001,34 +5001,34 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>11.1768869325764</v>
+        <v>11.1768869325754</v>
       </c>
       <c r="C35" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
       <c r="D35" t="n">
-        <v>81.7536488236882</v>
+        <v>81.7536490204092</v>
       </c>
       <c r="E35" t="n">
-        <v>319.683577578662</v>
+        <v>319.683577854721</v>
       </c>
       <c r="F35" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="G35" t="n">
-        <v>-49.9999071336239</v>
+        <v>-49.9999074096829</v>
       </c>
       <c r="H35" t="n">
-        <v>-11.9642199211653</v>
+        <v>-11.9642199708423</v>
       </c>
       <c r="I35" t="n">
-        <v>69.7894289025229</v>
+        <v>69.7894290495669</v>
       </c>
       <c r="J35" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="K35" t="n">
-        <v>0.000000000000170530256582424</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="36">
@@ -5036,34 +5036,34 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>6.09246182599038</v>
+        <v>6.09246182598753</v>
       </c>
       <c r="C36" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
       <c r="D36" t="n">
-        <v>66.0065098397185</v>
+        <v>66.0065089391448</v>
       </c>
       <c r="E36" t="n">
-        <v>319.683577578662</v>
+        <v>319.683577854721</v>
       </c>
       <c r="F36" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="G36" t="n">
-        <v>-49.9999071336239</v>
+        <v>-49.9999074096829</v>
       </c>
       <c r="H36" t="n">
-        <v>-13.7435530250016</v>
+        <v>-13.7435531039753</v>
       </c>
       <c r="I36" t="n">
-        <v>52.2629568147169</v>
+        <v>52.2629558351695</v>
       </c>
       <c r="J36" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="K36" t="n">
-        <v>0.000000000000170530256582424</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="37">
@@ -5071,34 +5071,34 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>13.9732105882918</v>
+        <v>13.9732105882977</v>
       </c>
       <c r="C37" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
       <c r="D37" t="n">
-        <v>90.4142341067075</v>
+        <v>90.4142349069349</v>
       </c>
       <c r="E37" t="n">
-        <v>319.683577578662</v>
+        <v>319.683577854721</v>
       </c>
       <c r="F37" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="G37" t="n">
-        <v>-49.9999071336239</v>
+        <v>-49.9999074096829</v>
       </c>
       <c r="H37" t="n">
-        <v>-14.8150667494829</v>
+        <v>-14.815066867132</v>
       </c>
       <c r="I37" t="n">
-        <v>75.5991673572246</v>
+        <v>75.5991680398029</v>
       </c>
       <c r="J37" t="n">
         <v>269.683670445038</v>
       </c>
       <c r="K37" t="n">
-        <v>0.000000000000170530256582424</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="38">
@@ -5106,34 +5106,34 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>10.8645335610762</v>
+        <v>10.864533561075</v>
       </c>
       <c r="C38" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
       <c r="D38" t="n">
-        <v>69.2775037046601</v>
+        <v>69.2775039927475</v>
       </c>
       <c r="E38" t="n">
-        <v>274.025698101413</v>
+        <v>274.025699038857</v>
       </c>
       <c r="F38" t="n">
         <v>236.574897953765</v>
       </c>
       <c r="G38" t="n">
-        <v>-37.4508001476473</v>
+        <v>-37.4508010850919</v>
       </c>
       <c r="H38" t="n">
-        <v>-15.1787610946092</v>
+        <v>-15.1787612603123</v>
       </c>
       <c r="I38" t="n">
-        <v>54.0987426100509</v>
+        <v>54.0987427324352</v>
       </c>
       <c r="J38" t="n">
         <v>236.574897953766</v>
       </c>
       <c r="K38" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="39">
@@ -5141,34 +5141,34 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>10.766403877037</v>
+        <v>10.7664038770365</v>
       </c>
       <c r="C39" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
       <c r="D39" t="n">
-        <v>68.9735830566764</v>
+        <v>68.973583323588</v>
       </c>
       <c r="E39" t="n">
-        <v>274.025698101413</v>
+        <v>274.025699038857</v>
       </c>
       <c r="F39" t="n">
         <v>236.574897953765</v>
       </c>
       <c r="G39" t="n">
-        <v>-37.4508001476473</v>
+        <v>-37.4508010850919</v>
       </c>
       <c r="H39" t="n">
-        <v>-12.9978144095808</v>
+        <v>-12.9978146219687</v>
       </c>
       <c r="I39" t="n">
-        <v>55.9757686470956</v>
+        <v>55.9757687016194</v>
       </c>
       <c r="J39" t="n">
         <v>236.574897953766</v>
       </c>
       <c r="K39" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="40">
@@ -5176,34 +5176,34 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>8.26874568961349</v>
+        <v>8.26874568961225</v>
       </c>
       <c r="C40" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
       <c r="D40" t="n">
-        <v>61.2380043457498</v>
+        <v>61.2380040736302</v>
       </c>
       <c r="E40" t="n">
-        <v>274.025698101413</v>
+        <v>274.025699038857</v>
       </c>
       <c r="F40" t="n">
         <v>236.574897953765</v>
       </c>
       <c r="G40" t="n">
-        <v>-37.4508001476473</v>
+        <v>-37.4508010850919</v>
       </c>
       <c r="H40" t="n">
-        <v>-8.27222669439751</v>
+        <v>-8.27222695210104</v>
       </c>
       <c r="I40" t="n">
-        <v>52.9657776513523</v>
+        <v>52.9657771215292</v>
       </c>
       <c r="J40" t="n">
         <v>236.574897953766</v>
       </c>
       <c r="K40" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="41">
@@ -5211,34 +5211,34 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>12.562589114617</v>
+        <v>12.5625891146203</v>
       </c>
       <c r="C41" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
       <c r="D41" t="n">
-        <v>74.5366069943265</v>
+        <v>74.5366076488916</v>
       </c>
       <c r="E41" t="n">
-        <v>274.025698101413</v>
+        <v>274.025699038857</v>
       </c>
       <c r="F41" t="n">
         <v>236.574897953765</v>
       </c>
       <c r="G41" t="n">
-        <v>-37.4508001476473</v>
+        <v>-37.4508010850919</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.00199794905949</v>
+        <v>-1.00199825070943</v>
       </c>
       <c r="I41" t="n">
-        <v>73.534609045267</v>
+        <v>73.5346093981822</v>
       </c>
       <c r="J41" t="n">
         <v>236.574897953766</v>
       </c>
       <c r="K41" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000397903932025656</v>
       </c>
     </row>
     <row r="42">
@@ -5246,34 +5246,34 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>10.7788841220824</v>
+        <v>10.7788841220817</v>
       </c>
       <c r="C42" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
       <c r="D42" t="n">
-        <v>61.2002295009192</v>
+        <v>61.2002298798819</v>
       </c>
       <c r="E42" t="n">
-        <v>242.426969509212</v>
+        <v>242.426970859653</v>
       </c>
       <c r="F42" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="G42" t="n">
-        <v>61.8897539991403</v>
+        <v>61.8897526486993</v>
       </c>
       <c r="H42" t="n">
-        <v>8.81287182643331</v>
+        <v>8.81287148220617</v>
       </c>
       <c r="I42" t="n">
-        <v>70.0131013273525</v>
+        <v>70.0131013620881</v>
       </c>
       <c r="J42" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="K42" t="n">
-        <v>0.000000000000056843418860808</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="43">
@@ -5281,34 +5281,34 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>10.5850677840361</v>
+        <v>10.585067784036</v>
       </c>
       <c r="C43" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
       <c r="D43" t="n">
-        <v>60.5999545930194</v>
+        <v>60.5999549301557</v>
       </c>
       <c r="E43" t="n">
-        <v>242.426969509212</v>
+        <v>242.426970859653</v>
       </c>
       <c r="F43" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="G43" t="n">
-        <v>61.8897539991403</v>
+        <v>61.8897526486993</v>
       </c>
       <c r="H43" t="n">
-        <v>15.4026464059711</v>
+        <v>15.4026460473599</v>
       </c>
       <c r="I43" t="n">
-        <v>76.0026009989905</v>
+        <v>76.0026009775156</v>
       </c>
       <c r="J43" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="K43" t="n">
-        <v>0.000000000000056843418860808</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="44">
@@ -5316,34 +5316,34 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>9.12229912280024</v>
+        <v>9.12229912279982</v>
       </c>
       <c r="C44" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
       <c r="D44" t="n">
-        <v>56.0695660186969</v>
+        <v>56.0695660401466</v>
       </c>
       <c r="E44" t="n">
-        <v>242.426969509212</v>
+        <v>242.426970859653</v>
       </c>
       <c r="F44" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="G44" t="n">
-        <v>61.8897539991403</v>
+        <v>61.8897526486993</v>
       </c>
       <c r="H44" t="n">
-        <v>18.767325789554</v>
+        <v>18.7673254447517</v>
       </c>
       <c r="I44" t="n">
-        <v>74.8368918082509</v>
+        <v>74.8368914848983</v>
       </c>
       <c r="J44" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="K44" t="n">
-        <v>0.000000000000056843418860808</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="45">
@@ -5351,34 +5351,34 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>11.8627866471957</v>
+        <v>11.8627866471977</v>
       </c>
       <c r="C45" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
       <c r="D45" t="n">
-        <v>64.5572193965763</v>
+        <v>64.5572200094685</v>
       </c>
       <c r="E45" t="n">
-        <v>242.426969509212</v>
+        <v>242.426970859653</v>
       </c>
       <c r="F45" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="G45" t="n">
-        <v>61.8897539991403</v>
+        <v>61.8897526486993</v>
       </c>
       <c r="H45" t="n">
-        <v>18.9069099771819</v>
+        <v>18.9069096743816</v>
       </c>
       <c r="I45" t="n">
-        <v>83.4641293737582</v>
+        <v>83.4641296838501</v>
       </c>
       <c r="J45" t="n">
         <v>304.316723508352</v>
       </c>
       <c r="K45" t="n">
-        <v>0.000000000000056843418860808</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="46">
@@ -5386,34 +5386,34 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>10.7822885416376</v>
+        <v>10.7822885416373</v>
       </c>
       <c r="C46" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
       <c r="D46" t="n">
-        <v>77.0962560916924</v>
+        <v>77.0962562422494</v>
       </c>
       <c r="E46" t="n">
-        <v>306.239157255104</v>
+        <v>306.239157707811</v>
       </c>
       <c r="F46" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="G46" t="n">
-        <v>54.372826644351</v>
+        <v>54.3728261916438</v>
       </c>
       <c r="H46" t="n">
-        <v>15.8213989688548</v>
+        <v>15.8213987362497</v>
       </c>
       <c r="I46" t="n">
-        <v>92.9176550605472</v>
+        <v>92.9176549784991</v>
       </c>
       <c r="J46" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="K46" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5421,34 +5421,34 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>10.4438314871757</v>
+        <v>10.443831487176</v>
       </c>
       <c r="C47" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
       <c r="D47" t="n">
-        <v>76.0480096990348</v>
+        <v>76.0480097765498</v>
       </c>
       <c r="E47" t="n">
-        <v>306.239157255104</v>
+        <v>306.239157707811</v>
       </c>
       <c r="F47" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="G47" t="n">
-        <v>54.372826644351</v>
+        <v>54.3728261916438</v>
       </c>
       <c r="H47" t="n">
-        <v>13.6959176424172</v>
+        <v>13.6959174856614</v>
       </c>
       <c r="I47" t="n">
-        <v>89.743927341452</v>
+        <v>89.7439272622113</v>
       </c>
       <c r="J47" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="K47" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5456,34 +5456,34 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>10.0022276754265</v>
+        <v>10.0022276754269</v>
       </c>
       <c r="C48" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
       <c r="D48" t="n">
-        <v>74.6803041170491</v>
+        <v>74.6803040992604</v>
       </c>
       <c r="E48" t="n">
-        <v>306.239157255104</v>
+        <v>306.239157707811</v>
       </c>
       <c r="F48" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="G48" t="n">
-        <v>54.372826644351</v>
+        <v>54.3728261916438</v>
       </c>
       <c r="H48" t="n">
-        <v>12.5304659978689</v>
+        <v>12.5304659226168</v>
       </c>
       <c r="I48" t="n">
-        <v>87.210770114918</v>
+        <v>87.2107700218772</v>
       </c>
       <c r="J48" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="K48" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5491,34 +5491,34 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>11.2079504057878</v>
+        <v>11.2079504057885</v>
       </c>
       <c r="C49" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
       <c r="D49" t="n">
-        <v>78.4145873473275</v>
+        <v>78.4145875897513</v>
       </c>
       <c r="E49" t="n">
-        <v>306.239157255104</v>
+        <v>306.239157707811</v>
       </c>
       <c r="F49" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="G49" t="n">
-        <v>54.372826644351</v>
+        <v>54.3728261916438</v>
       </c>
       <c r="H49" t="n">
-        <v>12.3250440352101</v>
+        <v>12.3250440471158</v>
       </c>
       <c r="I49" t="n">
-        <v>90.7396313825376</v>
+        <v>90.7396316368671</v>
       </c>
       <c r="J49" t="n">
         <v>360.611983899455</v>
       </c>
       <c r="K49" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5529,31 +5529,31 @@
         <v>10.8200506299549</v>
       </c>
       <c r="C50" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
       <c r="D50" t="n">
-        <v>90.2834287546482</v>
+        <v>90.2834287157394</v>
       </c>
       <c r="E50" t="n">
-        <v>359.664432158594</v>
+        <v>359.664431900577</v>
       </c>
       <c r="F50" t="n">
         <v>430.289828585279</v>
       </c>
       <c r="G50" t="n">
-        <v>70.6253964266855</v>
+        <v>70.6253966847027</v>
       </c>
       <c r="H50" t="n">
-        <v>13.0796517544407</v>
+        <v>13.0796518591585</v>
       </c>
       <c r="I50" t="n">
-        <v>103.363080509089</v>
+        <v>103.363080574898</v>
       </c>
       <c r="J50" t="n">
-        <v>430.28982858528</v>
+        <v>430.289828585279</v>
       </c>
       <c r="K50" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="51">
@@ -5564,31 +5564,31 @@
         <v>10.5382561440265</v>
       </c>
       <c r="C51" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
       <c r="D51" t="n">
-        <v>89.4106738528045</v>
+        <v>89.4106737530807</v>
       </c>
       <c r="E51" t="n">
-        <v>359.664432158594</v>
+        <v>359.664431900577</v>
       </c>
       <c r="F51" t="n">
         <v>430.289828585279</v>
       </c>
       <c r="G51" t="n">
-        <v>70.6253964266855</v>
+        <v>70.6253966847027</v>
       </c>
       <c r="H51" t="n">
-        <v>15.2121737830252</v>
+        <v>15.2121739087824</v>
       </c>
       <c r="I51" t="n">
-        <v>104.62284763583</v>
+        <v>104.622847661863</v>
       </c>
       <c r="J51" t="n">
-        <v>430.28982858528</v>
+        <v>430.289828585279</v>
       </c>
       <c r="K51" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="52">
@@ -5599,31 +5599,31 @@
         <v>10.5759503785478</v>
       </c>
       <c r="C52" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
       <c r="D52" t="n">
-        <v>89.5274178971079</v>
+        <v>89.527417805519</v>
       </c>
       <c r="E52" t="n">
-        <v>359.664432158594</v>
+        <v>359.664431900577</v>
       </c>
       <c r="F52" t="n">
         <v>430.289828585279</v>
       </c>
       <c r="G52" t="n">
-        <v>70.6253964266855</v>
+        <v>70.6253966847027</v>
       </c>
       <c r="H52" t="n">
-        <v>18.7226101209637</v>
+        <v>18.7226101959877</v>
       </c>
       <c r="I52" t="n">
-        <v>108.250028018072</v>
+        <v>108.250028001507</v>
       </c>
       <c r="J52" t="n">
-        <v>430.28982858528</v>
+        <v>430.289828585279</v>
       </c>
       <c r="K52" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="53">
@@ -5634,31 +5634,31 @@
         <v>10.8715443558012</v>
       </c>
       <c r="C53" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
       <c r="D53" t="n">
-        <v>90.4429116540333</v>
+        <v>90.4429116262376</v>
       </c>
       <c r="E53" t="n">
-        <v>359.664432158594</v>
+        <v>359.664431900577</v>
       </c>
       <c r="F53" t="n">
         <v>430.289828585279</v>
       </c>
       <c r="G53" t="n">
-        <v>70.6253964266855</v>
+        <v>70.6253966847027</v>
       </c>
       <c r="H53" t="n">
-        <v>23.6109607682561</v>
+        <v>23.6109607207742</v>
       </c>
       <c r="I53" t="n">
-        <v>114.053872422289</v>
+        <v>114.053872347012</v>
       </c>
       <c r="J53" t="n">
-        <v>430.28982858528</v>
+        <v>430.289828585279</v>
       </c>
       <c r="K53" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000056843418860808</v>
       </c>
     </row>
     <row r="54">
@@ -5669,25 +5669,25 @@
         <v>12.9570570133416</v>
       </c>
       <c r="C54" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
       <c r="D54" t="n">
-        <v>112.890365991425</v>
+        <v>112.890366158746</v>
       </c>
       <c r="E54" t="n">
-        <v>454.764378435737</v>
+        <v>454.764379328204</v>
       </c>
       <c r="F54" t="n">
         <v>566.541738110914</v>
       </c>
       <c r="G54" t="n">
-        <v>111.777359675177</v>
+        <v>111.77735878271</v>
       </c>
       <c r="H54" t="n">
-        <v>29.8772257249026</v>
+        <v>29.877225483142</v>
       </c>
       <c r="I54" t="n">
-        <v>142.767591716327</v>
+        <v>142.767591641887</v>
       </c>
       <c r="J54" t="n">
         <v>566.541738110914</v>
@@ -5704,25 +5704,25 @@
         <v>12.7543914906828</v>
       </c>
       <c r="C55" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
       <c r="D55" t="n">
-        <v>112.262683984971</v>
+        <v>112.262684108553</v>
       </c>
       <c r="E55" t="n">
-        <v>454.764378435737</v>
+        <v>454.764379328204</v>
       </c>
       <c r="F55" t="n">
         <v>566.541738110914</v>
       </c>
       <c r="G55" t="n">
-        <v>111.777359675177</v>
+        <v>111.77735878271</v>
       </c>
       <c r="H55" t="n">
-        <v>31.6105773851178</v>
+        <v>31.6105770731033</v>
       </c>
       <c r="I55" t="n">
-        <v>143.873261370088</v>
+        <v>143.873261181657</v>
       </c>
       <c r="J55" t="n">
         <v>566.541738110914</v>
@@ -5739,25 +5739,25 @@
         <v>13.0397525391501</v>
       </c>
       <c r="C56" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
       <c r="D56" t="n">
-        <v>113.146485004088</v>
+        <v>113.146485189256</v>
       </c>
       <c r="E56" t="n">
-        <v>454.764378435737</v>
+        <v>454.764379328204</v>
       </c>
       <c r="F56" t="n">
         <v>566.541738110914</v>
       </c>
       <c r="G56" t="n">
-        <v>111.777359675177</v>
+        <v>111.77735878271</v>
       </c>
       <c r="H56" t="n">
-        <v>28.8110157489019</v>
+        <v>28.8110154906581</v>
       </c>
       <c r="I56" t="n">
-        <v>141.95750075299</v>
+        <v>141.957500679914</v>
       </c>
       <c r="J56" t="n">
         <v>566.541738110914</v>
@@ -5774,25 +5774,25 @@
         <v>14.1111817707667</v>
       </c>
       <c r="C57" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
       <c r="D57" t="n">
-        <v>116.464843455253</v>
+        <v>116.46484387165</v>
       </c>
       <c r="E57" t="n">
-        <v>454.764378435737</v>
+        <v>454.764379328204</v>
       </c>
       <c r="F57" t="n">
         <v>566.541738110914</v>
       </c>
       <c r="G57" t="n">
-        <v>111.777359675177</v>
+        <v>111.77735878271</v>
       </c>
       <c r="H57" t="n">
-        <v>21.4785408162547</v>
+        <v>21.4785407358064</v>
       </c>
       <c r="I57" t="n">
-        <v>137.943384271508</v>
+        <v>137.943384607456</v>
       </c>
       <c r="J57" t="n">
         <v>566.541738110914</v>
@@ -5809,31 +5809,31 @@
         <v>14.0378160523454</v>
       </c>
       <c r="C58" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
       <c r="D58" t="n">
-        <v>140.757918506831</v>
+        <v>140.757918038574</v>
       </c>
       <c r="E58" t="n">
-        <v>569.170479168995</v>
+        <v>569.170477723727</v>
       </c>
       <c r="F58" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="G58" t="n">
-        <v>10.4233460397594</v>
+        <v>10.4233474850274</v>
       </c>
       <c r="H58" t="n">
-        <v>9.61315258717642</v>
+        <v>9.61315280854823</v>
       </c>
       <c r="I58" t="n">
-        <v>150.371071094008</v>
+        <v>150.371070847122</v>
       </c>
       <c r="J58" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="59">
@@ -5844,31 +5844,31 @@
         <v>12.2062827701092</v>
       </c>
       <c r="C59" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
       <c r="D59" t="n">
-        <v>135.085416986103</v>
+        <v>135.085416122575</v>
       </c>
       <c r="E59" t="n">
-        <v>569.170479168995</v>
+        <v>569.170477723727</v>
       </c>
       <c r="F59" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="G59" t="n">
-        <v>10.4233460397594</v>
+        <v>10.4233474850274</v>
       </c>
       <c r="H59" t="n">
-        <v>2.06407086465046</v>
+        <v>2.06407126272842</v>
       </c>
       <c r="I59" t="n">
-        <v>137.149487850753</v>
+        <v>137.149487385303</v>
       </c>
       <c r="J59" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="60">
@@ -5879,31 +5879,31 @@
         <v>14.7690861061654</v>
       </c>
       <c r="C60" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
       <c r="D60" t="n">
-        <v>143.022758863591</v>
+        <v>143.022758553151</v>
       </c>
       <c r="E60" t="n">
-        <v>569.170479168995</v>
+        <v>569.170477723727</v>
       </c>
       <c r="F60" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="G60" t="n">
-        <v>10.4233460397594</v>
+        <v>10.4233474850274</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.16870435132313</v>
+        <v>-1.16870390165303</v>
       </c>
       <c r="I60" t="n">
-        <v>141.854054512268</v>
+        <v>141.854054651498</v>
       </c>
       <c r="J60" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="61">
@@ -5914,31 +5914,31 @@
         <v>17.1201723465891</v>
       </c>
       <c r="C61" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
       <c r="D61" t="n">
-        <v>150.30438481247</v>
+        <v>150.304385009428</v>
       </c>
       <c r="E61" t="n">
-        <v>569.170479168995</v>
+        <v>569.170477723727</v>
       </c>
       <c r="F61" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="G61" t="n">
-        <v>10.4233460397594</v>
+        <v>10.4233474850274</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.085173060744369</v>
+        <v>-0.0851726845961081</v>
       </c>
       <c r="I61" t="n">
-        <v>150.219211751726</v>
+        <v>150.219212324832</v>
       </c>
       <c r="J61" t="n">
         <v>579.593825208755</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
     </row>
     <row r="62">
@@ -5949,31 +5949,31 @@
         <v>16.5595286531131</v>
       </c>
       <c r="C62" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
       <c r="D62" t="n">
-        <v>147.804472255645</v>
+        <v>147.804472077513</v>
       </c>
       <c r="E62" t="n">
-        <v>591.976247737402</v>
+        <v>591.97624707772</v>
       </c>
       <c r="F62" t="n">
         <v>637.096554399705</v>
       </c>
       <c r="G62" t="n">
-        <v>45.1203066623033</v>
+        <v>45.1203073219859</v>
       </c>
       <c r="H62" t="n">
-        <v>5.31466473638676</v>
+        <v>5.31466491389918</v>
       </c>
       <c r="I62" t="n">
-        <v>153.119136992031</v>
+        <v>153.119136991412</v>
       </c>
       <c r="J62" t="n">
         <v>637.096554399706</v>
       </c>
       <c r="K62" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="63">
@@ -5984,31 +5984,31 @@
         <v>16.1236209274397</v>
       </c>
       <c r="C63" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
       <c r="D63" t="n">
-        <v>146.454408207799</v>
+        <v>146.454407935593</v>
       </c>
       <c r="E63" t="n">
-        <v>591.976247737402</v>
+        <v>591.97624707772</v>
       </c>
       <c r="F63" t="n">
         <v>637.096554399705</v>
       </c>
       <c r="G63" t="n">
-        <v>45.1203066623033</v>
+        <v>45.1203073219859</v>
       </c>
       <c r="H63" t="n">
-        <v>9.86076462691483</v>
+        <v>9.86076471993623</v>
       </c>
       <c r="I63" t="n">
-        <v>156.315172834714</v>
+        <v>156.315172655529</v>
       </c>
       <c r="J63" t="n">
         <v>637.096554399706</v>
       </c>
       <c r="K63" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="64">
@@ -6019,31 +6019,31 @@
         <v>16.3192772141769</v>
       </c>
       <c r="C64" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
       <c r="D64" t="n">
-        <v>147.060381680857</v>
+        <v>147.060381450876</v>
       </c>
       <c r="E64" t="n">
-        <v>591.976247737402</v>
+        <v>591.97624707772</v>
       </c>
       <c r="F64" t="n">
         <v>637.096554399705</v>
       </c>
       <c r="G64" t="n">
-        <v>45.1203066623033</v>
+        <v>45.1203073219859</v>
       </c>
       <c r="H64" t="n">
-        <v>13.5531266108399</v>
+        <v>13.553126733515</v>
       </c>
       <c r="I64" t="n">
-        <v>160.613508291697</v>
+        <v>160.613508184391</v>
       </c>
       <c r="J64" t="n">
         <v>637.096554399706</v>
       </c>
       <c r="K64" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="65">
@@ -6054,31 +6054,31 @@
         <v>17.48054614363</v>
       </c>
       <c r="C65" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
       <c r="D65" t="n">
-        <v>150.656985593102</v>
+        <v>150.656985613738</v>
       </c>
       <c r="E65" t="n">
-        <v>591.976247737402</v>
+        <v>591.97624707772</v>
       </c>
       <c r="F65" t="n">
         <v>637.096554399705</v>
       </c>
       <c r="G65" t="n">
-        <v>45.1203066623033</v>
+        <v>45.1203073219859</v>
       </c>
       <c r="H65" t="n">
-        <v>16.3917506881618</v>
+        <v>16.3917509546356</v>
       </c>
       <c r="I65" t="n">
-        <v>167.048736281263</v>
+        <v>167.048736568374</v>
       </c>
       <c r="J65" t="n">
         <v>637.096554399706</v>
       </c>
       <c r="K65" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="66">
@@ -6089,31 +6089,31 @@
         <v>17.3052064617991</v>
       </c>
       <c r="C66" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
       <c r="D66" t="n">
-        <v>157.495980756367</v>
+        <v>157.495980209647</v>
       </c>
       <c r="E66" t="n">
-        <v>636.505129353614</v>
+        <v>636.505127621141</v>
       </c>
       <c r="F66" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="G66" t="n">
-        <v>62.4833240071421</v>
+        <v>62.4833257396152</v>
       </c>
       <c r="H66" t="n">
-        <v>18.3766368588808</v>
+        <v>18.376637383298</v>
       </c>
       <c r="I66" t="n">
-        <v>175.872617615248</v>
+        <v>175.872617592945</v>
       </c>
       <c r="J66" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="K66" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="67">
@@ -6124,31 +6124,31 @@
         <v>17.4491223381665</v>
       </c>
       <c r="C67" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
       <c r="D67" t="n">
-        <v>157.941707315349</v>
+        <v>157.941706799687</v>
       </c>
       <c r="E67" t="n">
-        <v>636.505129353614</v>
+        <v>636.505127621141</v>
       </c>
       <c r="F67" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="G67" t="n">
-        <v>62.4833240071421</v>
+        <v>62.4833257396152</v>
       </c>
       <c r="H67" t="n">
-        <v>18.0682689843302</v>
+        <v>18.0682695754053</v>
       </c>
       <c r="I67" t="n">
-        <v>176.009976299679</v>
+        <v>176.009976375092</v>
       </c>
       <c r="J67" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="K67" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="68">
@@ -6159,31 +6159,31 @@
         <v>17.259954781733</v>
       </c>
       <c r="C68" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
       <c r="D68" t="n">
-        <v>157.355830300746</v>
+        <v>157.35582974426</v>
       </c>
       <c r="E68" t="n">
-        <v>636.505129353614</v>
+        <v>636.505127621141</v>
       </c>
       <c r="F68" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="G68" t="n">
-        <v>62.4833240071421</v>
+        <v>62.4833257396152</v>
       </c>
       <c r="H68" t="n">
-        <v>15.4666470645103</v>
+        <v>15.4666475309576</v>
       </c>
       <c r="I68" t="n">
-        <v>172.822477365257</v>
+        <v>172.822477275217</v>
       </c>
       <c r="J68" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="K68" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="69">
@@ -6194,31 +6194,31 @@
         <v>19.3121047561699</v>
       </c>
       <c r="C69" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
       <c r="D69" t="n">
-        <v>163.711610981152</v>
+        <v>163.711610867547</v>
       </c>
       <c r="E69" t="n">
-        <v>636.505129353614</v>
+        <v>636.505127621141</v>
       </c>
       <c r="F69" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="G69" t="n">
-        <v>62.4833240071421</v>
+        <v>62.4833257396152</v>
       </c>
       <c r="H69" t="n">
-        <v>10.5717710994209</v>
+        <v>10.5717712499548</v>
       </c>
       <c r="I69" t="n">
-        <v>174.283382080572</v>
+        <v>174.283382117502</v>
       </c>
       <c r="J69" t="n">
         <v>698.988453360756</v>
       </c>
       <c r="K69" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="70">
@@ -6229,31 +6229,31 @@
         <v>23.1154258857424</v>
       </c>
       <c r="C70" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
       <c r="D70" t="n">
-        <v>186.430370575297</v>
+        <v>186.430370876925</v>
       </c>
       <c r="E70" t="n">
-        <v>756.877519819912</v>
+        <v>756.877521803797</v>
       </c>
       <c r="F70" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="G70" t="n">
-        <v>-13.3180819971633</v>
+        <v>-13.3180839810478</v>
       </c>
       <c r="H70" t="n">
-        <v>3.38364108906204</v>
+        <v>3.38364073239704</v>
       </c>
       <c r="I70" t="n">
-        <v>189.814011664359</v>
+        <v>189.814011609322</v>
       </c>
       <c r="J70" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="K70" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="71">
@@ -6264,31 +6264,31 @@
         <v>23.8949714243776</v>
       </c>
       <c r="C71" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
       <c r="D71" t="n">
-        <v>188.844726512081</v>
+        <v>188.844726981946</v>
       </c>
       <c r="E71" t="n">
-        <v>756.877519819912</v>
+        <v>756.877521803797</v>
       </c>
       <c r="F71" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="G71" t="n">
-        <v>-13.3180819971633</v>
+        <v>-13.3180839810478</v>
       </c>
       <c r="H71" t="n">
-        <v>-2.17687555042263</v>
+        <v>-2.17687616568963</v>
       </c>
       <c r="I71" t="n">
-        <v>186.667850961659</v>
+        <v>186.667850816256</v>
       </c>
       <c r="J71" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="K71" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="72">
@@ -6299,31 +6299,31 @@
         <v>23.0079858138554</v>
       </c>
       <c r="C72" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
       <c r="D72" t="n">
-        <v>186.097614421162</v>
+        <v>186.097614699603</v>
       </c>
       <c r="E72" t="n">
-        <v>756.877519819912</v>
+        <v>756.877521803797</v>
       </c>
       <c r="F72" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="G72" t="n">
-        <v>-13.3180819971633</v>
+        <v>-13.3180839810478</v>
       </c>
       <c r="H72" t="n">
-        <v>-6.10977881903313</v>
+        <v>-6.1097794443052</v>
       </c>
       <c r="I72" t="n">
-        <v>179.987835602129</v>
+        <v>179.987835255298</v>
       </c>
       <c r="J72" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="K72" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="73">
@@ -6334,31 +6334,31 @@
         <v>26.0453739290296</v>
       </c>
       <c r="C73" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
       <c r="D73" t="n">
-        <v>195.504808311372</v>
+        <v>195.504809245323</v>
       </c>
       <c r="E73" t="n">
-        <v>756.877519819912</v>
+        <v>756.877521803797</v>
       </c>
       <c r="F73" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="G73" t="n">
-        <v>-13.3180819971633</v>
+        <v>-13.3180839810478</v>
       </c>
       <c r="H73" t="n">
-        <v>-8.41506871676944</v>
+        <v>-8.41506910344967</v>
       </c>
       <c r="I73" t="n">
-        <v>187.089739594603</v>
+        <v>187.089740141874</v>
       </c>
       <c r="J73" t="n">
         <v>743.559437822749</v>
       </c>
       <c r="K73" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="74">
@@ -6369,31 +6369,31 @@
         <v>24.404052044643</v>
       </c>
       <c r="C74" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
       <c r="D74" t="n">
-        <v>182.945805617153</v>
+        <v>182.945805061929</v>
       </c>
       <c r="E74" t="n">
-        <v>739.166141940129</v>
+        <v>739.166140233687</v>
       </c>
       <c r="F74" t="n">
         <v>742.49</v>
       </c>
       <c r="G74" t="n">
-        <v>3.32385805987087</v>
+        <v>3.32385976631326</v>
       </c>
       <c r="H74" t="n">
-        <v>-9.09274524363157</v>
+        <v>-9.09274514312303</v>
       </c>
       <c r="I74" t="n">
-        <v>173.853060373522</v>
+        <v>173.853059918806</v>
       </c>
       <c r="J74" t="n">
         <v>742.49</v>
       </c>
       <c r="K74" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="75">
@@ -6404,31 +6404,31 @@
         <v>24.6011462830655</v>
       </c>
       <c r="C75" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
       <c r="D75" t="n">
-        <v>183.556232617319</v>
+        <v>183.55623210463</v>
       </c>
       <c r="E75" t="n">
-        <v>739.166141940129</v>
+        <v>739.166140233687</v>
       </c>
       <c r="F75" t="n">
         <v>742.49</v>
       </c>
       <c r="G75" t="n">
-        <v>3.32385805987087</v>
+        <v>3.32385976631326</v>
       </c>
       <c r="H75" t="n">
-        <v>-5.39433195093671</v>
+        <v>-5.3943315251118</v>
       </c>
       <c r="I75" t="n">
-        <v>178.161900666382</v>
+        <v>178.161900579518</v>
       </c>
       <c r="J75" t="n">
         <v>742.49</v>
       </c>
       <c r="K75" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="76">
@@ -6439,31 +6439,31 @@
         <v>24.7243859880522</v>
       </c>
       <c r="C76" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
       <c r="D76" t="n">
-        <v>183.937922330922</v>
+        <v>183.93792184483</v>
       </c>
       <c r="E76" t="n">
-        <v>739.166141940129</v>
+        <v>739.166140233687</v>
       </c>
       <c r="F76" t="n">
         <v>742.49</v>
       </c>
       <c r="G76" t="n">
-        <v>3.32385805987087</v>
+        <v>3.32385976631326</v>
       </c>
       <c r="H76" t="n">
-        <v>2.68017116131516</v>
+        <v>2.68017175058401</v>
       </c>
       <c r="I76" t="n">
-        <v>186.618093492237</v>
+        <v>186.618093595414</v>
       </c>
       <c r="J76" t="n">
         <v>742.49</v>
       </c>
       <c r="K76" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="77">
@@ -6474,31 +6474,31 @@
         <v>26.2704156842394</v>
       </c>
       <c r="C77" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
       <c r="D77" t="n">
-        <v>188.726181374736</v>
+        <v>188.726181222298</v>
       </c>
       <c r="E77" t="n">
-        <v>739.166141940129</v>
+        <v>739.166140233687</v>
       </c>
       <c r="F77" t="n">
         <v>742.49</v>
       </c>
       <c r="G77" t="n">
-        <v>3.32385805987087</v>
+        <v>3.32385976631326</v>
       </c>
       <c r="H77" t="n">
-        <v>15.130764093124</v>
+        <v>15.1307646839644</v>
       </c>
       <c r="I77" t="n">
-        <v>203.85694546786</v>
+        <v>203.856945906263</v>
       </c>
       <c r="J77" t="n">
         <v>742.49</v>
       </c>
       <c r="K77" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="78">
@@ -6509,31 +6509,31 @@
         <v>25.0797591916903</v>
       </c>
       <c r="C78" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
       <c r="D78" t="n">
-        <v>181.944982791842</v>
+        <v>181.944982229997</v>
       </c>
       <c r="E78" t="n">
-        <v>728.944688807337</v>
+        <v>728.944686641121</v>
       </c>
       <c r="F78" t="n">
         <v>842.728</v>
       </c>
       <c r="G78" t="n">
-        <v>113.783311192663</v>
+        <v>113.783313358879</v>
       </c>
       <c r="H78" t="n">
-        <v>31.9574468444899</v>
+        <v>31.9574472750294</v>
       </c>
       <c r="I78" t="n">
-        <v>213.902429636331</v>
+        <v>213.902429505026</v>
       </c>
       <c r="J78" t="n">
         <v>842.728</v>
       </c>
       <c r="K78" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="79">
@@ -6544,31 +6544,31 @@
         <v>24.5716220485478</v>
       </c>
       <c r="C79" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
       <c r="D79" t="n">
-        <v>180.371214657148</v>
+        <v>180.37121398564</v>
       </c>
       <c r="E79" t="n">
-        <v>728.944688807337</v>
+        <v>728.944686641121</v>
       </c>
       <c r="F79" t="n">
         <v>842.728</v>
       </c>
       <c r="G79" t="n">
-        <v>113.783311192663</v>
+        <v>113.783313358879</v>
       </c>
       <c r="H79" t="n">
-        <v>37.2834723265066</v>
+        <v>37.2834727373315</v>
       </c>
       <c r="I79" t="n">
-        <v>217.654686983654</v>
+        <v>217.654686722971</v>
       </c>
       <c r="J79" t="n">
         <v>842.728</v>
       </c>
       <c r="K79" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="80">
@@ -6579,31 +6579,31 @@
         <v>24.9068420844815</v>
       </c>
       <c r="C80" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
       <c r="D80" t="n">
-        <v>181.409435574046</v>
+        <v>181.409434974883</v>
       </c>
       <c r="E80" t="n">
-        <v>728.944688807337</v>
+        <v>728.944686641121</v>
       </c>
       <c r="F80" t="n">
         <v>842.728</v>
       </c>
       <c r="G80" t="n">
-        <v>113.783311192663</v>
+        <v>113.783313358879</v>
       </c>
       <c r="H80" t="n">
-        <v>31.108840539174</v>
+        <v>31.1088410708709</v>
       </c>
       <c r="I80" t="n">
-        <v>212.51827611322</v>
+        <v>212.518276045754</v>
       </c>
       <c r="J80" t="n">
         <v>842.728</v>
       </c>
       <c r="K80" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="81">
@@ -6614,31 +6614,31 @@
         <v>26.1368895656974</v>
       </c>
       <c r="C81" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
       <c r="D81" t="n">
-        <v>185.219055784303</v>
+        <v>185.219055450601</v>
       </c>
       <c r="E81" t="n">
-        <v>728.944688807337</v>
+        <v>728.944686641121</v>
       </c>
       <c r="F81" t="n">
         <v>842.728</v>
       </c>
       <c r="G81" t="n">
-        <v>113.783311192663</v>
+        <v>113.783313358879</v>
       </c>
       <c r="H81" t="n">
-        <v>13.4335514824922</v>
+        <v>13.4335522756475</v>
       </c>
       <c r="I81" t="n">
-        <v>198.652607266795</v>
+        <v>198.652607726249</v>
       </c>
       <c r="J81" t="n">
         <v>842.728</v>
       </c>
       <c r="K81" t="n">
-        <v>0.000000000000113686837721616</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="82">
@@ -6649,31 +6649,31 @@
         <v>22.1163428289219</v>
       </c>
       <c r="C82" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
       <c r="D82" t="n">
-        <v>195.649426940417</v>
+        <v>195.649425365746</v>
       </c>
       <c r="E82" t="n">
-        <v>798.778466560567</v>
+        <v>798.778461389387</v>
       </c>
       <c r="F82" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="G82" t="n">
-        <v>-113.055275270674</v>
+        <v>-113.055270099494</v>
       </c>
       <c r="H82" t="n">
-        <v>-15.7423948435388</v>
+        <v>-15.7423936483387</v>
       </c>
       <c r="I82" t="n">
-        <v>179.907032096878</v>
+        <v>179.907031717407</v>
       </c>
       <c r="J82" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="K82" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="83">
@@ -6684,31 +6684,31 @@
         <v>24.225607013601</v>
       </c>
       <c r="C83" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
       <c r="D83" t="n">
-        <v>202.182097905917</v>
+        <v>202.182096786454</v>
       </c>
       <c r="E83" t="n">
-        <v>798.778466560567</v>
+        <v>798.778461389387</v>
       </c>
       <c r="F83" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="G83" t="n">
-        <v>-113.055275270674</v>
+        <v>-113.055270099494</v>
       </c>
       <c r="H83" t="n">
-        <v>-32.4213429636031</v>
+        <v>-32.4213415685471</v>
       </c>
       <c r="I83" t="n">
-        <v>169.760754942314</v>
+        <v>169.760755217907</v>
       </c>
       <c r="J83" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="K83" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="84">
@@ -6719,31 +6719,31 @@
         <v>23.3046400646644</v>
       </c>
       <c r="C84" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
       <c r="D84" t="n">
-        <v>199.329741102438</v>
+        <v>199.329739784218</v>
       </c>
       <c r="E84" t="n">
-        <v>798.778466560567</v>
+        <v>798.778461389387</v>
       </c>
       <c r="F84" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="G84" t="n">
-        <v>-113.055275270674</v>
+        <v>-113.055270099494</v>
       </c>
       <c r="H84" t="n">
-        <v>-36.6032928777007</v>
+        <v>-36.6032914849777</v>
       </c>
       <c r="I84" t="n">
-        <v>162.726448224737</v>
+        <v>162.72644829924</v>
       </c>
       <c r="J84" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="K84" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="85">
@@ -6754,31 +6754,31 @@
         <v>24.0432133744899</v>
       </c>
       <c r="C85" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
       <c r="D85" t="n">
-        <v>201.617200611795</v>
+        <v>201.617199452969</v>
       </c>
       <c r="E85" t="n">
-        <v>798.778466560567</v>
+        <v>798.778461389387</v>
       </c>
       <c r="F85" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="G85" t="n">
-        <v>-113.055275270674</v>
+        <v>-113.055270099494</v>
       </c>
       <c r="H85" t="n">
-        <v>-28.2882445858316</v>
+        <v>-28.2882433976304</v>
       </c>
       <c r="I85" t="n">
-        <v>173.328956025963</v>
+        <v>173.328956055339</v>
       </c>
       <c r="J85" t="n">
         <v>685.723191289893</v>
       </c>
       <c r="K85" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>0.000000000000341060513164848</v>
       </c>
     </row>
     <row r="86">
@@ -6789,31 +6789,31 @@
         <v>22.9199205166214</v>
       </c>
       <c r="C86" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
       <c r="D86" t="n">
-        <v>166.571757382443</v>
+        <v>166.571756800558</v>
       </c>
       <c r="E86" t="n">
-        <v>665.2582056142</v>
+        <v>665.258203214969</v>
       </c>
       <c r="F86" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="G86" t="n">
-        <v>49.6556482647231</v>
+        <v>49.6556506639536</v>
       </c>
       <c r="H86" t="n">
-        <v>-7.47619808799581</v>
+        <v>-7.47619730650529</v>
       </c>
       <c r="I86" t="n">
-        <v>159.095559294447</v>
+        <v>159.095559494053</v>
       </c>
       <c r="J86" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="K86" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="87">
@@ -6824,31 +6824,31 @@
         <v>22.1903787476254</v>
       </c>
       <c r="C87" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
       <c r="D87" t="n">
-        <v>164.312269753033</v>
+        <v>164.312269013703</v>
       </c>
       <c r="E87" t="n">
-        <v>665.2582056142</v>
+        <v>665.258203214969</v>
       </c>
       <c r="F87" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="G87" t="n">
-        <v>49.6556482647231</v>
+        <v>49.6556506639536</v>
       </c>
       <c r="H87" t="n">
-        <v>8.80466457280917</v>
+        <v>8.80466511894228</v>
       </c>
       <c r="I87" t="n">
-        <v>173.116934325842</v>
+        <v>173.116934132645</v>
       </c>
       <c r="J87" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="K87" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="88">
@@ -6859,31 +6859,31 @@
         <v>22.5186739517877</v>
       </c>
       <c r="C88" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
       <c r="D88" t="n">
-        <v>165.329043547384</v>
+        <v>165.329042878904</v>
       </c>
       <c r="E88" t="n">
-        <v>665.2582056142</v>
+        <v>665.258203214969</v>
       </c>
       <c r="F88" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="G88" t="n">
-        <v>49.6556482647231</v>
+        <v>49.6556506639536</v>
       </c>
       <c r="H88" t="n">
-        <v>20.5543433965834</v>
+        <v>20.5543438787123</v>
       </c>
       <c r="I88" t="n">
-        <v>185.883386943967</v>
+        <v>185.883386757617</v>
       </c>
       <c r="J88" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="K88" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="89">
@@ -6894,31 +6894,31 @@
         <v>23.7185229116645</v>
       </c>
       <c r="C89" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
       <c r="D89" t="n">
-        <v>169.045134931339</v>
+        <v>169.045134521804</v>
       </c>
       <c r="E89" t="n">
-        <v>665.2582056142</v>
+        <v>665.258203214969</v>
       </c>
       <c r="F89" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="G89" t="n">
-        <v>49.6556482647231</v>
+        <v>49.6556506639536</v>
       </c>
       <c r="H89" t="n">
-        <v>27.7728383833268</v>
+        <v>27.7728389728048</v>
       </c>
       <c r="I89" t="n">
-        <v>196.817973314666</v>
+        <v>196.817973494608</v>
       </c>
       <c r="J89" t="n">
         <v>714.913853878923</v>
       </c>
       <c r="K89" t="n">
-        <v>0.000000000000341060513164848</v>
+        <v>0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="90">
@@ -6929,25 +6929,25 @@
         <v>21.5190468048165</v>
       </c>
       <c r="C90" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
       <c r="D90" t="n">
-        <v>170.735437338026</v>
+        <v>170.735436446048</v>
       </c>
       <c r="E90" t="n">
-        <v>684.972587586088</v>
+        <v>684.972584159691</v>
       </c>
       <c r="F90" t="n">
         <v>767.424752018039</v>
       </c>
       <c r="G90" t="n">
-        <v>82.4521644319509</v>
+        <v>82.452167858348</v>
       </c>
       <c r="H90" t="n">
-        <v>30.4601495330394</v>
+        <v>30.4601504012197</v>
       </c>
       <c r="I90" t="n">
-        <v>201.195586871065</v>
+        <v>201.195586847268</v>
       </c>
       <c r="J90" t="n">
         <v>767.424752018039</v>
@@ -6964,25 +6964,25 @@
         <v>21.1510850813716</v>
       </c>
       <c r="C91" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
       <c r="D91" t="n">
-        <v>169.59581107185</v>
+        <v>169.595810100462</v>
       </c>
       <c r="E91" t="n">
-        <v>684.972587586088</v>
+        <v>684.972584159691</v>
       </c>
       <c r="F91" t="n">
         <v>767.424752018039</v>
       </c>
       <c r="G91" t="n">
-        <v>82.4521644319509</v>
+        <v>82.452167858348</v>
       </c>
       <c r="H91" t="n">
-        <v>27.5962306229039</v>
+        <v>27.5962315979327</v>
       </c>
       <c r="I91" t="n">
-        <v>197.192041694754</v>
+        <v>197.192041698394</v>
       </c>
       <c r="J91" t="n">
         <v>767.424752018039</v>
@@ -6999,25 +6999,25 @@
         <v>21.5583450125892</v>
       </c>
       <c r="C92" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
       <c r="D92" t="n">
-        <v>170.857149100249</v>
+        <v>170.857148216753</v>
       </c>
       <c r="E92" t="n">
-        <v>684.972587586088</v>
+        <v>684.972584159691</v>
       </c>
       <c r="F92" t="n">
         <v>767.424752018039</v>
       </c>
       <c r="G92" t="n">
-        <v>82.4521644319509</v>
+        <v>82.452167858348</v>
       </c>
       <c r="H92" t="n">
-        <v>19.1810816529201</v>
+        <v>19.1810825629437</v>
       </c>
       <c r="I92" t="n">
-        <v>190.038230753169</v>
+        <v>190.038230779697</v>
       </c>
       <c r="J92" t="n">
         <v>767.424752018039</v>
@@ -7034,25 +7034,25 @@
         <v>22.5034259342775</v>
       </c>
       <c r="C93" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
       <c r="D93" t="n">
-        <v>173.784190075963</v>
+        <v>173.784189396428</v>
       </c>
       <c r="E93" t="n">
-        <v>684.972587586088</v>
+        <v>684.972584159691</v>
       </c>
       <c r="F93" t="n">
         <v>767.424752018039</v>
       </c>
       <c r="G93" t="n">
-        <v>82.4521644319509</v>
+        <v>82.452167858348</v>
       </c>
       <c r="H93" t="n">
-        <v>5.21470262308825</v>
+        <v>5.21470329625282</v>
       </c>
       <c r="I93" t="n">
-        <v>178.998892699051</v>
+        <v>178.998892692681</v>
       </c>
       <c r="J93" t="n">
         <v>767.424752018039</v>
@@ -7066,28 +7066,28 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>25.5840539196353</v>
+        <v>25.5840539283816</v>
       </c>
       <c r="C94" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
       <c r="D94" t="n">
-        <v>198.910649424295</v>
+        <v>198.910649438671</v>
       </c>
       <c r="E94" t="n">
-        <v>800.083873618929</v>
+        <v>800.083873991616</v>
       </c>
       <c r="F94" t="n">
         <v>674.560615938681</v>
       </c>
       <c r="G94" t="n">
-        <v>-125.523257680248</v>
+        <v>-125.523258052936</v>
       </c>
       <c r="H94" t="n">
-        <v>-14.3029064665918</v>
+        <v>-14.30290620214</v>
       </c>
       <c r="I94" t="n">
-        <v>184.607742957704</v>
+        <v>184.607743236531</v>
       </c>
       <c r="J94" t="n">
         <v>674.560615938682</v>
@@ -7101,28 +7101,28 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>26.463759148534</v>
+        <v>26.4637591575308</v>
       </c>
       <c r="C95" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
       <c r="D95" t="n">
-        <v>201.635213207613</v>
+        <v>201.635213412616</v>
       </c>
       <c r="E95" t="n">
-        <v>800.083873618929</v>
+        <v>800.083873991616</v>
       </c>
       <c r="F95" t="n">
         <v>674.560615938681</v>
       </c>
       <c r="G95" t="n">
-        <v>-125.523257680248</v>
+        <v>-125.523258052936</v>
       </c>
       <c r="H95" t="n">
-        <v>-28.9411132838518</v>
+        <v>-28.9411133259346</v>
       </c>
       <c r="I95" t="n">
-        <v>172.694099923761</v>
+        <v>172.694100086681</v>
       </c>
       <c r="J95" t="n">
         <v>674.560615938682</v>
@@ -7136,28 +7136,28 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>22.280409710173</v>
+        <v>22.2804097195315</v>
       </c>
       <c r="C96" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
       <c r="D96" t="n">
-        <v>188.678825092258</v>
+        <v>188.678824395557</v>
       </c>
       <c r="E96" t="n">
-        <v>800.083873618929</v>
+        <v>800.083873991616</v>
       </c>
       <c r="F96" t="n">
         <v>674.560615938681</v>
       </c>
       <c r="G96" t="n">
-        <v>-125.523257680248</v>
+        <v>-125.523258052936</v>
       </c>
       <c r="H96" t="n">
-        <v>-38.6999178286919</v>
+        <v>-38.699918075131</v>
       </c>
       <c r="I96" t="n">
-        <v>149.978907263566</v>
+        <v>149.978906320426</v>
       </c>
       <c r="J96" t="n">
         <v>674.560615938682</v>
@@ -7171,28 +7171,28 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>29.4419889311474</v>
+        <v>29.4419889408751</v>
       </c>
       <c r="C97" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
       <c r="D97" t="n">
-        <v>210.859185894763</v>
+        <v>210.859186744773</v>
       </c>
       <c r="E97" t="n">
-        <v>800.083873618929</v>
+        <v>800.083873991616</v>
       </c>
       <c r="F97" t="n">
         <v>674.560615938681</v>
       </c>
       <c r="G97" t="n">
-        <v>-125.523257680248</v>
+        <v>-125.523258052936</v>
       </c>
       <c r="H97" t="n">
-        <v>-43.5793201011119</v>
+        <v>-43.5793204497292</v>
       </c>
       <c r="I97" t="n">
-        <v>167.279865793651</v>
+        <v>167.279866295044</v>
       </c>
       <c r="J97" t="n">
         <v>674.560615938682</v>
@@ -7231,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>6.58158660432072</v>
+        <v>6.58158653671646</v>
       </c>
       <c r="C2" t="n">
-        <v>9.43429602011821</v>
+        <v>9.43429602010574</v>
       </c>
       <c r="D2" t="n">
-        <v>-186.115112664519</v>
+        <v>-186.115116197947</v>
       </c>
     </row>
     <row r="3">
@@ -7245,13 +7245,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8638338028851</v>
+        <v>16.8638342557031</v>
       </c>
       <c r="C3" t="n">
         <v>12.1937909319798</v>
       </c>
       <c r="D3" t="n">
-        <v>-186.115112664519</v>
+        <v>-186.115116197947</v>
       </c>
     </row>
     <row r="4">
@@ -7259,13 +7259,13 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>-6.7178477866303</v>
+        <v>-6.71784936923454</v>
       </c>
       <c r="C4" t="n">
-        <v>3.45889465139194</v>
+        <v>3.45889465139056</v>
       </c>
       <c r="D4" t="n">
-        <v>-186.115112664519</v>
+        <v>-186.115116197947</v>
       </c>
     </row>
     <row r="5">
@@ -7273,13 +7273,13 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>41.6197312137347</v>
+        <v>41.619732411125</v>
       </c>
       <c r="C5" t="n">
-        <v>17.3848086073612</v>
+        <v>17.3848086073763</v>
       </c>
       <c r="D5" t="n">
-        <v>-186.115112664519</v>
+        <v>-186.115116197947</v>
       </c>
     </row>
     <row r="6">
@@ -7287,13 +7287,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.18604902225504</v>
+        <v>4.18604899490934</v>
       </c>
       <c r="C6" t="n">
-        <v>9.45592239730524</v>
+        <v>9.45592239729289</v>
       </c>
       <c r="D6" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
     </row>
     <row r="7">
@@ -7301,13 +7301,13 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>18.3346197356864</v>
+        <v>18.3346200893177</v>
       </c>
       <c r="C7" t="n">
         <v>12.1917626444412</v>
       </c>
       <c r="D7" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
     </row>
     <row r="8">
@@ -7315,13 +7315,13 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.27531649850542</v>
+        <v>-4.27531814589013</v>
       </c>
       <c r="C8" t="n">
-        <v>3.46832106816489</v>
+        <v>3.46832106816347</v>
       </c>
       <c r="D8" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
     </row>
     <row r="9">
@@ -7329,13 +7329,13 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>41.8557349419305</v>
+        <v>41.8557362630293</v>
       </c>
       <c r="C9" t="n">
-        <v>17.3491999352476</v>
+        <v>17.3491999352625</v>
       </c>
       <c r="D9" t="n">
-        <v>-271.071823077797</v>
+        <v>-271.071824493194</v>
       </c>
     </row>
     <row r="10">
@@ -7343,13 +7343,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>19.8261312377309</v>
+        <v>19.8261309224413</v>
       </c>
       <c r="C10" t="n">
-        <v>9.4980531804306</v>
+        <v>9.49805318041849</v>
       </c>
       <c r="D10" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
     </row>
     <row r="11">
@@ -7357,13 +7357,13 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>29.0387581516253</v>
+        <v>29.0387584707472</v>
       </c>
       <c r="C11" t="n">
         <v>12.1810595075462</v>
       </c>
       <c r="D11" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
     </row>
     <row r="12">
@@ -7371,13 +7371,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>2.03084677078762</v>
+        <v>2.03084525940147</v>
       </c>
       <c r="C12" t="n">
-        <v>3.48224738555144</v>
+        <v>3.48224738554993</v>
       </c>
       <c r="D12" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
     </row>
     <row r="13">
@@ -7385,13 +7385,13 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>43.7691184277618</v>
+        <v>43.7691199353152</v>
       </c>
       <c r="C13" t="n">
-        <v>17.2931976179497</v>
+        <v>17.2931976179645</v>
       </c>
       <c r="D13" t="n">
-        <v>-269.297647676228</v>
+        <v>-269.297649090204</v>
       </c>
     </row>
     <row r="14">
@@ -7399,13 +7399,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>25.7978291092536</v>
+        <v>25.7978288527819</v>
       </c>
       <c r="C14" t="n">
-        <v>9.53219834761259</v>
+        <v>9.53219834760066</v>
       </c>
       <c r="D14" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
     </row>
     <row r="15">
@@ -7413,13 +7413,13 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>34.4018762396655</v>
+        <v>34.4018765715641</v>
       </c>
       <c r="C15" t="n">
-        <v>12.1448667467563</v>
+        <v>12.1448667467561</v>
       </c>
       <c r="D15" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
     </row>
     <row r="16">
@@ -7427,13 +7427,13 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>10.4986496730368</v>
+        <v>10.498648147361</v>
       </c>
       <c r="C16" t="n">
-        <v>3.44863939510121</v>
+        <v>3.44863939509929</v>
       </c>
       <c r="D16" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
     </row>
     <row r="17">
@@ -7441,13 +7441,13 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>58.553689462335</v>
+        <v>58.5536909125837</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1732760387875</v>
+        <v>17.1732760388017</v>
       </c>
       <c r="D17" t="n">
-        <v>-234.700900925877</v>
+        <v>-234.700902337555</v>
       </c>
     </row>
     <row r="18">
@@ -7455,13 +7455,13 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>52.410590135374</v>
+        <v>52.4105899208566</v>
       </c>
       <c r="C18" t="n">
-        <v>9.94389849691342</v>
+        <v>9.94389849690385</v>
       </c>
       <c r="D18" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
     </row>
     <row r="19">
@@ -7469,13 +7469,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>65.9391170690309</v>
+        <v>65.9391173284113</v>
       </c>
       <c r="C19" t="n">
-        <v>11.9749179714078</v>
+        <v>11.974917971407</v>
       </c>
       <c r="D19" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
     </row>
     <row r="20">
@@ -7483,13 +7483,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>45.7813521207111</v>
+        <v>45.781350591238</v>
       </c>
       <c r="C20" t="n">
-        <v>3.39658042340207</v>
+        <v>3.39658042339941</v>
       </c>
       <c r="D20" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
     </row>
     <row r="21">
@@ -7497,13 +7497,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>93.3353729838994</v>
+        <v>93.3353744685093</v>
       </c>
       <c r="C21" t="n">
-        <v>16.9482255201931</v>
+        <v>16.9482255202062</v>
       </c>
       <c r="D21" t="n">
-        <v>-199.631867918304</v>
+        <v>-199.631869296403</v>
       </c>
     </row>
     <row r="22">
@@ -7511,13 +7511,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>107.655509756284</v>
+        <v>107.655509496815</v>
       </c>
       <c r="C22" t="n">
-        <v>10.3705444540626</v>
+        <v>10.3705444540554</v>
       </c>
       <c r="D22" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
     </row>
     <row r="23">
@@ -7525,13 +7525,13 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>110.880142275346</v>
+        <v>110.880142462146</v>
       </c>
       <c r="C23" t="n">
-        <v>11.824196256855</v>
+        <v>11.8241962568536</v>
       </c>
       <c r="D23" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
     </row>
     <row r="24">
@@ -7539,13 +7539,13 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>77.3693895029116</v>
+        <v>77.3693880127336</v>
       </c>
       <c r="C24" t="n">
-        <v>3.36455201044131</v>
+        <v>3.36455201043794</v>
       </c>
       <c r="D24" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
     </row>
     <row r="25">
@@ -7553,13 +7553,13 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>105.472782758441</v>
+        <v>105.472784321288</v>
       </c>
       <c r="C25" t="n">
-        <v>16.7466388832914</v>
+        <v>16.7466388833034</v>
       </c>
       <c r="D25" t="n">
-        <v>-71.307971317156</v>
+        <v>-71.3079726876238</v>
       </c>
     </row>
     <row r="26">
@@ -7567,13 +7567,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>101.039564517578</v>
+        <v>101.039564467368</v>
       </c>
       <c r="C26" t="n">
-        <v>10.7408214718216</v>
+        <v>10.7408214718168</v>
       </c>
       <c r="D26" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
     </row>
     <row r="27">
@@ -7581,13 +7581,13 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>90.9495594930202</v>
+        <v>90.9495597481429</v>
       </c>
       <c r="C27" t="n">
-        <v>11.646641871478</v>
+        <v>11.6466418714765</v>
       </c>
       <c r="D27" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
     </row>
     <row r="28">
@@ -7595,13 +7595,13 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>59.7351180080814</v>
+        <v>59.7351165736948</v>
       </c>
       <c r="C28" t="n">
-        <v>3.63961093490583</v>
+        <v>3.63961093490175</v>
       </c>
       <c r="D28" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
     </row>
     <row r="29">
@@ -7609,13 +7609,13 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>98.4981230536709</v>
+        <v>98.4981242831451</v>
       </c>
       <c r="C29" t="n">
-        <v>16.1346402601908</v>
+        <v>16.1346402602008</v>
       </c>
       <c r="D29" t="n">
-        <v>72.4723834847681</v>
+        <v>72.4723821051694</v>
       </c>
     </row>
     <row r="30">
@@ -7623,13 +7623,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>77.872012505586</v>
+        <v>77.8720127441485</v>
       </c>
       <c r="C30" t="n">
-        <v>11.1816037184879</v>
+        <v>11.1816037184858</v>
       </c>
       <c r="D30" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
     </row>
     <row r="31">
@@ -7637,13 +7637,13 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>83.0527040338147</v>
+        <v>83.0527042663316</v>
       </c>
       <c r="C31" t="n">
-        <v>11.5275263743065</v>
+        <v>11.527526374305</v>
       </c>
       <c r="D31" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
     </row>
     <row r="32">
@@ -7651,13 +7651,13 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>61.2120354021274</v>
+        <v>61.2120339387369</v>
       </c>
       <c r="C32" t="n">
-        <v>3.93494656467575</v>
+        <v>3.93494656467131</v>
       </c>
       <c r="D32" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
     </row>
     <row r="33">
@@ -7665,13 +7665,13 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>96.1797984033627</v>
+        <v>96.179799395674</v>
       </c>
       <c r="C33" t="n">
-        <v>15.4707682208608</v>
+        <v>15.4707682208692</v>
       </c>
       <c r="D33" t="n">
-        <v>21.7635836481479</v>
+        <v>21.7635822996747</v>
       </c>
     </row>
     <row r="34">
@@ -7679,13 +7679,13 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>72.0321173705735</v>
+        <v>72.0321175204987</v>
       </c>
       <c r="C34" t="n">
-        <v>11.0979545641313</v>
+        <v>11.0979545641297</v>
       </c>
       <c r="D34" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
     </row>
     <row r="35">
@@ -7693,13 +7693,13 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>69.7894289025229</v>
+        <v>69.7894290495669</v>
       </c>
       <c r="C35" t="n">
-        <v>11.1768869325764</v>
+        <v>11.1768869325754</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
     </row>
     <row r="36">
@@ -7707,13 +7707,13 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>52.2629568147169</v>
+        <v>52.2629558351695</v>
       </c>
       <c r="C36" t="n">
-        <v>6.09246182599038</v>
+        <v>6.09246182598753</v>
       </c>
       <c r="D36" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
     </row>
     <row r="37">
@@ -7721,13 +7721,13 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>75.5991673572246</v>
+        <v>75.5991680398029</v>
       </c>
       <c r="C37" t="n">
-        <v>13.9732105882918</v>
+        <v>13.9732105882977</v>
       </c>
       <c r="D37" t="n">
-        <v>-9.99706952501475</v>
+        <v>-9.99707086337543</v>
       </c>
     </row>
     <row r="38">
@@ -7735,13 +7735,13 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>54.0987426100509</v>
+        <v>54.0987427324352</v>
       </c>
       <c r="C38" t="n">
-        <v>10.8645335610762</v>
+        <v>10.864533561075</v>
       </c>
       <c r="D38" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
     </row>
     <row r="39">
@@ -7749,13 +7749,13 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>55.9757686470956</v>
+        <v>55.9757687016194</v>
       </c>
       <c r="C39" t="n">
-        <v>10.766403877037</v>
+        <v>10.7664038770365</v>
       </c>
       <c r="D39" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
     </row>
     <row r="40">
@@ -7763,13 +7763,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>52.9657776513523</v>
+        <v>52.9657771215292</v>
       </c>
       <c r="C40" t="n">
-        <v>8.26874568961349</v>
+        <v>8.26874568961225</v>
       </c>
       <c r="D40" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
     </row>
     <row r="41">
@@ -7777,13 +7777,13 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>73.534609045267</v>
+        <v>73.5346093981822</v>
       </c>
       <c r="C41" t="n">
-        <v>12.562589114617</v>
+        <v>12.5625891146203</v>
       </c>
       <c r="D41" t="n">
-        <v>-59.3288763531168</v>
+        <v>-59.3288777401798</v>
       </c>
     </row>
     <row r="42">
@@ -7791,13 +7791,13 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>70.0131013273525</v>
+        <v>70.0131013620881</v>
       </c>
       <c r="C42" t="n">
-        <v>10.7788841220824</v>
+        <v>10.7788841220817</v>
       </c>
       <c r="D42" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
     </row>
     <row r="43">
@@ -7805,13 +7805,13 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>76.0026009989905</v>
+        <v>76.0026009775156</v>
       </c>
       <c r="C43" t="n">
-        <v>10.5850677840361</v>
+        <v>10.585067784036</v>
       </c>
       <c r="D43" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
     </row>
     <row r="44">
@@ -7819,13 +7819,13 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>74.8368918082509</v>
+        <v>74.8368914848983</v>
       </c>
       <c r="C44" t="n">
-        <v>9.12229912280024</v>
+        <v>9.12229912279982</v>
       </c>
       <c r="D44" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
     </row>
     <row r="45">
@@ -7833,13 +7833,13 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>83.4641293737582</v>
+        <v>83.4641296838501</v>
       </c>
       <c r="C45" t="n">
-        <v>11.8627866471957</v>
+        <v>11.8627866471977</v>
       </c>
       <c r="D45" t="n">
-        <v>-92.8147505473524</v>
+        <v>-92.8147519606926</v>
       </c>
     </row>
     <row r="46">
@@ -7847,13 +7847,13 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>92.9176550605472</v>
+        <v>92.9176549784991</v>
       </c>
       <c r="C46" t="n">
-        <v>10.7822885416376</v>
+        <v>10.7822885416373</v>
       </c>
       <c r="D46" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
     </row>
     <row r="47">
@@ -7861,13 +7861,13 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>89.743927341452</v>
+        <v>89.7439272622113</v>
       </c>
       <c r="C47" t="n">
-        <v>10.4438314871757</v>
+        <v>10.443831487176</v>
       </c>
       <c r="D47" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
     </row>
     <row r="48">
@@ -7875,13 +7875,13 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>87.210770114918</v>
+        <v>87.2107700218772</v>
       </c>
       <c r="C48" t="n">
-        <v>10.0022276754265</v>
+        <v>10.0022276754269</v>
       </c>
       <c r="D48" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
     </row>
     <row r="49">
@@ -7889,13 +7889,13 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>90.7396313825376</v>
+        <v>90.7396316368671</v>
       </c>
       <c r="C49" t="n">
-        <v>11.2079504057878</v>
+        <v>11.2079504057885</v>
       </c>
       <c r="D49" t="n">
-        <v>-24.7222225210366</v>
+        <v>-24.7222239099404</v>
       </c>
     </row>
     <row r="50">
@@ -7903,13 +7903,13 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>103.363080509089</v>
+        <v>103.363080574898</v>
       </c>
       <c r="C50" t="n">
         <v>10.8200506299549</v>
       </c>
       <c r="D50" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
     </row>
     <row r="51">
@@ -7917,13 +7917,13 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>104.62284763583</v>
+        <v>104.622847661863</v>
       </c>
       <c r="C51" t="n">
         <v>10.5382561440265</v>
       </c>
       <c r="D51" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
     </row>
     <row r="52">
@@ -7931,13 +7931,13 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>108.250028018072</v>
+        <v>108.250028001507</v>
       </c>
       <c r="C52" t="n">
         <v>10.5759503785478</v>
       </c>
       <c r="D52" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
     </row>
     <row r="53">
@@ -7945,13 +7945,13 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>114.053872422289</v>
+        <v>114.053872347012</v>
       </c>
       <c r="C53" t="n">
         <v>10.8715443558012</v>
       </c>
       <c r="D53" t="n">
-        <v>31.3027807314851</v>
+        <v>31.3027793237491</v>
       </c>
     </row>
     <row r="54">
@@ -7959,13 +7959,13 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>142.767591716327</v>
+        <v>142.767591641887</v>
       </c>
       <c r="C54" t="n">
         <v>12.9570570133416</v>
       </c>
       <c r="D54" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
     </row>
     <row r="55">
@@ -7973,13 +7973,13 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>143.873261370088</v>
+        <v>143.873261181657</v>
       </c>
       <c r="C55" t="n">
         <v>12.7543914906828</v>
       </c>
       <c r="D55" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
     </row>
     <row r="56">
@@ -7987,13 +7987,13 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>141.95750075299</v>
+        <v>141.957500679914</v>
       </c>
       <c r="C56" t="n">
         <v>13.0397525391501</v>
       </c>
       <c r="D56" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
     </row>
     <row r="57">
@@ -8001,13 +8001,13 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>137.943384271508</v>
+        <v>137.943384607456</v>
       </c>
       <c r="C57" t="n">
         <v>14.1111817707667</v>
       </c>
       <c r="D57" t="n">
-        <v>99.8362243796026</v>
+        <v>99.8362228921252</v>
       </c>
     </row>
     <row r="58">
@@ -8015,13 +8015,13 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>150.371071094008</v>
+        <v>150.371070847122</v>
       </c>
       <c r="C58" t="n">
         <v>14.0378160523454</v>
       </c>
       <c r="D58" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
     </row>
     <row r="59">
@@ -8029,13 +8029,13 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>137.149487850753</v>
+        <v>137.149487385303</v>
       </c>
       <c r="C59" t="n">
         <v>12.2062827701092</v>
       </c>
       <c r="D59" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
     </row>
     <row r="60">
@@ -8043,13 +8043,13 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>141.854054512268</v>
+        <v>141.854054651498</v>
       </c>
       <c r="C60" t="n">
         <v>14.7690861061654</v>
       </c>
       <c r="D60" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
     </row>
     <row r="61">
@@ -8057,13 +8057,13 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>150.219211751726</v>
+        <v>150.219212324832</v>
       </c>
       <c r="C61" t="n">
         <v>17.1201723465891</v>
       </c>
       <c r="D61" t="n">
-        <v>204.941567636041</v>
+        <v>204.941563978215</v>
       </c>
     </row>
     <row r="62">
@@ -8071,13 +8071,13 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>153.119136992031</v>
+        <v>153.119136991412</v>
       </c>
       <c r="C62" t="n">
         <v>16.5595286531131</v>
       </c>
       <c r="D62" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
     </row>
     <row r="63">
@@ -8085,13 +8085,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>156.315172834714</v>
+        <v>156.315172655529</v>
       </c>
       <c r="C63" t="n">
         <v>16.1236209274397</v>
       </c>
       <c r="D63" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
     </row>
     <row r="64">
@@ -8099,13 +8099,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>160.613508291697</v>
+        <v>160.613508184391</v>
       </c>
       <c r="C64" t="n">
         <v>16.3192772141769</v>
       </c>
       <c r="D64" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
     </row>
     <row r="65">
@@ -8113,13 +8113,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>167.048736281263</v>
+        <v>167.048736568374</v>
       </c>
       <c r="C65" t="n">
         <v>17.48054614363</v>
       </c>
       <c r="D65" t="n">
-        <v>201.668747653429</v>
+        <v>201.668742858055</v>
       </c>
     </row>
     <row r="66">
@@ -8127,13 +8127,13 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>175.872617615248</v>
+        <v>175.872617592945</v>
       </c>
       <c r="C66" t="n">
         <v>17.3052064617991</v>
       </c>
       <c r="D66" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
     </row>
     <row r="67">
@@ -8141,13 +8141,13 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>176.009976299679</v>
+        <v>176.009976375092</v>
       </c>
       <c r="C67" t="n">
         <v>17.4491223381665</v>
       </c>
       <c r="D67" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
     </row>
     <row r="68">
@@ -8155,13 +8155,13 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>172.822477365257</v>
+        <v>172.822477275217</v>
       </c>
       <c r="C68" t="n">
         <v>17.259954781733</v>
       </c>
       <c r="D68" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
     </row>
     <row r="69">
@@ -8169,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>174.283382080572</v>
+        <v>174.283382117502</v>
       </c>
       <c r="C69" t="n">
         <v>19.3121047561699</v>
       </c>
       <c r="D69" t="n">
-        <v>233.311609592121</v>
+        <v>233.311602994784</v>
       </c>
     </row>
     <row r="70">
@@ -8183,13 +8183,13 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>189.814011664359</v>
+        <v>189.814011609322</v>
       </c>
       <c r="C70" t="n">
         <v>23.1154258857424</v>
       </c>
       <c r="D70" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
     </row>
     <row r="71">
@@ -8197,13 +8197,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>186.667850961659</v>
+        <v>186.667850816256</v>
       </c>
       <c r="C71" t="n">
         <v>23.8949714243776</v>
       </c>
       <c r="D71" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
     </row>
     <row r="72">
@@ -8211,13 +8211,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>179.987835602129</v>
+        <v>179.987835255298</v>
       </c>
       <c r="C72" t="n">
         <v>23.0079858138554</v>
       </c>
       <c r="D72" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
     </row>
     <row r="73">
@@ -8225,13 +8225,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>187.089739594603</v>
+        <v>187.089740141874</v>
       </c>
       <c r="C73" t="n">
         <v>26.0453739290296</v>
       </c>
       <c r="D73" t="n">
-        <v>280.202808601004</v>
+        <v>280.202800958392</v>
       </c>
     </row>
     <row r="74">
@@ -8239,13 +8239,13 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>173.853060373522</v>
+        <v>173.853059918806</v>
       </c>
       <c r="C74" t="n">
         <v>24.404052044643</v>
       </c>
       <c r="D74" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
     </row>
     <row r="75">
@@ -8253,13 +8253,13 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>178.161900666382</v>
+        <v>178.161900579518</v>
       </c>
       <c r="C75" t="n">
         <v>24.6011462830655</v>
       </c>
       <c r="D75" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
     </row>
     <row r="76">
@@ -8267,13 +8267,13 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>186.618093492237</v>
+        <v>186.618093595414</v>
       </c>
       <c r="C76" t="n">
         <v>24.7243859880522</v>
       </c>
       <c r="D76" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
     </row>
     <row r="77">
@@ -8281,13 +8281,13 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>203.85694546786</v>
+        <v>203.856945906263</v>
       </c>
       <c r="C77" t="n">
         <v>26.2704156842394</v>
       </c>
       <c r="D77" t="n">
-        <v>248.158880838138</v>
+        <v>248.15886785686</v>
       </c>
     </row>
     <row r="78">
@@ -8295,13 +8295,13 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>213.902429636331</v>
+        <v>213.902429505026</v>
       </c>
       <c r="C78" t="n">
         <v>25.0797591916903</v>
       </c>
       <c r="D78" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
     </row>
     <row r="79">
@@ -8309,13 +8309,13 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>217.654686983654</v>
+        <v>217.654686722971</v>
       </c>
       <c r="C79" t="n">
         <v>24.5716220485478</v>
       </c>
       <c r="D79" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
     </row>
     <row r="80">
@@ -8323,13 +8323,13 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>212.51827611322</v>
+        <v>212.518276045754</v>
       </c>
       <c r="C80" t="n">
         <v>24.9068420844815</v>
       </c>
       <c r="D80" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
     </row>
     <row r="81">
@@ -8337,13 +8337,13 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>198.652607266795</v>
+        <v>198.652607726249</v>
       </c>
       <c r="C81" t="n">
         <v>26.1368895656974</v>
       </c>
       <c r="D81" t="n">
-        <v>234.898376481493</v>
+        <v>234.898362650721</v>
       </c>
     </row>
     <row r="82">
@@ -8351,13 +8351,13 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>179.907032096878</v>
+        <v>179.907031717407</v>
       </c>
       <c r="C82" t="n">
         <v>22.1163428289219</v>
       </c>
       <c r="D82" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
     </row>
     <row r="83">
@@ -8365,13 +8365,13 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>169.760754942314</v>
+        <v>169.760755217907</v>
       </c>
       <c r="C83" t="n">
         <v>24.225607013601</v>
       </c>
       <c r="D83" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
     </row>
     <row r="84">
@@ -8379,13 +8379,13 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>162.726448224737</v>
+        <v>162.72644829924</v>
       </c>
       <c r="C84" t="n">
         <v>23.3046400646644</v>
       </c>
       <c r="D84" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
     </row>
     <row r="85">
@@ -8393,13 +8393,13 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>173.328956025963</v>
+        <v>173.328956055339</v>
       </c>
       <c r="C85" t="n">
         <v>24.0432133744899</v>
       </c>
       <c r="D85" t="n">
-        <v>332.983519655897</v>
+        <v>332.98350567511</v>
       </c>
     </row>
     <row r="86">
@@ -8407,13 +8407,13 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>159.095559294447</v>
+        <v>159.095559494053</v>
       </c>
       <c r="C86" t="n">
         <v>22.9199205166214</v>
       </c>
       <c r="D86" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
     </row>
     <row r="87">
@@ -8421,13 +8421,13 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>173.116934325842</v>
+        <v>173.116934132645</v>
       </c>
       <c r="C87" t="n">
         <v>22.1903787476254</v>
       </c>
       <c r="D87" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
     </row>
     <row r="88">
@@ -8435,13 +8435,13 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>185.883386943967</v>
+        <v>185.883386757617</v>
       </c>
       <c r="C88" t="n">
         <v>22.5186739517877</v>
       </c>
       <c r="D88" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
     </row>
     <row r="89">
@@ -8449,13 +8449,13 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>196.817973314666</v>
+        <v>196.817973494608</v>
       </c>
       <c r="C89" t="n">
         <v>23.7185229116645</v>
       </c>
       <c r="D89" t="n">
-        <v>197.675084030659</v>
+        <v>197.675071561713</v>
       </c>
     </row>
     <row r="90">
@@ -8463,13 +8463,13 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>201.195586871065</v>
+        <v>201.195586847268</v>
       </c>
       <c r="C90" t="n">
         <v>21.5190468048165</v>
       </c>
       <c r="D90" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
     </row>
     <row r="91">
@@ -8477,13 +8477,13 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>197.192041694754</v>
+        <v>197.192041698394</v>
       </c>
       <c r="C91" t="n">
         <v>21.1510850813716</v>
       </c>
       <c r="D91" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
     </row>
     <row r="92">
@@ -8491,13 +8491,13 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>190.038230753169</v>
+        <v>190.038230779697</v>
       </c>
       <c r="C92" t="n">
         <v>21.5583450125892</v>
       </c>
       <c r="D92" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
     </row>
     <row r="93">
@@ -8505,13 +8505,13 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>178.998892699051</v>
+        <v>178.998892692681</v>
       </c>
       <c r="C93" t="n">
         <v>22.5034259342775</v>
       </c>
       <c r="D93" t="n">
-        <v>234.120182573336</v>
+        <v>234.120170609892</v>
       </c>
     </row>
     <row r="94">
@@ -8519,13 +8519,13 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>184.607742957704</v>
+        <v>184.607743236531</v>
       </c>
       <c r="C94" t="n">
-        <v>25.5840539196353</v>
+        <v>25.5840539283816</v>
       </c>
       <c r="D94" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
     </row>
     <row r="95">
@@ -8533,13 +8533,13 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>172.694099923761</v>
+        <v>172.694100086681</v>
       </c>
       <c r="C95" t="n">
-        <v>26.463759148534</v>
+        <v>26.4637591575308</v>
       </c>
       <c r="D95" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
     </row>
     <row r="96">
@@ -8547,13 +8547,13 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>149.978907263566</v>
+        <v>149.978906320426</v>
       </c>
       <c r="C96" t="n">
-        <v>22.280409710173</v>
+        <v>22.2804097195315</v>
       </c>
       <c r="D96" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
     </row>
     <row r="97">
@@ -8561,13 +8561,13 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>167.279865793651</v>
+        <v>167.279866295044</v>
       </c>
       <c r="C97" t="n">
-        <v>29.4419889311474</v>
+        <v>29.4419889408751</v>
       </c>
       <c r="D97" t="n">
-        <v>300.926185386153</v>
+        <v>300.926174418818</v>
       </c>
     </row>
     <row r="98">
@@ -8575,13 +8575,13 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>166.486665217697</v>
+        <v>166.48666497716</v>
       </c>
       <c r="C98" t="n">
-        <v>25.9314570586997</v>
+        <v>25.931457069085</v>
       </c>
       <c r="D98" t="n">
-        <v>39.3324883166545</v>
+        <v>39.3324846851576</v>
       </c>
     </row>
     <row r="99">
@@ -8589,13 +8589,13 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>170.388451293531</v>
+        <v>170.388451321141</v>
       </c>
       <c r="C99" t="n">
-        <v>27.2526623869227</v>
+        <v>27.252662397921</v>
       </c>
       <c r="D99" t="n">
-        <v>39.1287076552146</v>
+        <v>39.1287040004663</v>
       </c>
     </row>
     <row r="100">
@@ -8603,13 +8603,13 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>158.650978132251</v>
+        <v>158.650977331891</v>
       </c>
       <c r="C100" t="n">
-        <v>23.5856741424488</v>
+        <v>23.5856741538312</v>
       </c>
       <c r="D100" t="n">
-        <v>38.7211463323348</v>
+        <v>38.7211426310837</v>
       </c>
     </row>
     <row r="101">
@@ -8617,13 +8617,13 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>178.720746369567</v>
+        <v>178.720746952097</v>
       </c>
       <c r="C101" t="n">
-        <v>30.2499849199284</v>
+        <v>30.2499849317301</v>
       </c>
       <c r="D101" t="n">
-        <v>38.109804348015</v>
+        <v>38.1098005770098</v>
       </c>
     </row>
     <row r="102">
@@ -8631,13 +8631,13 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>168.692007788062</v>
+        <v>168.69200765167</v>
       </c>
       <c r="C102" t="n">
-        <v>27.2575104839305</v>
+        <v>27.25751049652</v>
       </c>
       <c r="D102" t="n">
-        <v>37.2946817022554</v>
+        <v>37.2946778382445</v>
       </c>
     </row>
     <row r="103">
@@ -8645,13 +8645,13 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>170.353376184887</v>
+        <v>170.353376147471</v>
       </c>
       <c r="C103" t="n">
-        <v>28.0206668137277</v>
+        <v>28.0206668267677</v>
       </c>
       <c r="D103" t="n">
-        <v>36.5421631939914</v>
+        <v>36.54215924693</v>
       </c>
     </row>
     <row r="104">
@@ -8659,13 +8659,13 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>160.032405987878</v>
+        <v>160.032405218552</v>
       </c>
       <c r="C104" t="n">
-        <v>24.8961114123793</v>
+        <v>24.8961114257762</v>
       </c>
       <c r="D104" t="n">
-        <v>35.8522488232232</v>
+        <v>35.8522448030663</v>
       </c>
     </row>
     <row r="105">
@@ -8673,13 +8673,13 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>178.589139522246</v>
+        <v>178.589140037729</v>
       </c>
       <c r="C105" t="n">
-        <v>31.0767058699152</v>
+        <v>31.0767058837054</v>
       </c>
       <c r="D105" t="n">
-        <v>35.2249385899507</v>
+        <v>35.2249345066532</v>
       </c>
     </row>
     <row r="106">
@@ -8687,13 +8687,13 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>170.276514225127</v>
+        <v>170.276514159564</v>
       </c>
       <c r="C106" t="n">
-        <v>28.5628780226813</v>
+        <v>28.5628780375415</v>
       </c>
       <c r="D106" t="n">
-        <v>34.660232494174</v>
+        <v>34.6602283576909</v>
       </c>
     </row>
     <row r="107">
@@ -8701,13 +8701,13 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>170.382605566025</v>
+        <v>170.382605505123</v>
       </c>
       <c r="C107" t="n">
-        <v>28.7679787760825</v>
+        <v>28.7679787912051</v>
       </c>
       <c r="D107" t="n">
-        <v>34.0932053932477</v>
+        <v>34.0932012050712</v>
       </c>
     </row>
     <row r="108">
@@ -8715,13 +8715,13 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>161.932430118163</v>
+        <v>161.932429467335</v>
       </c>
       <c r="C108" t="n">
-        <v>26.2111374775603</v>
+        <v>26.2111374929631</v>
       </c>
       <c r="D108" t="n">
-        <v>33.5238572871718</v>
+        <v>33.5238530487941</v>
       </c>
     </row>
     <row r="109">
@@ -8729,13 +8729,13 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>179.088223894483</v>
+        <v>179.088224439605</v>
       </c>
       <c r="C109" t="n">
-        <v>31.9226327484023</v>
+        <v>31.9226327640953</v>
       </c>
       <c r="D109" t="n">
-        <v>32.9521881759465</v>
+        <v>32.9521838888596</v>
       </c>
     </row>
     <row r="110">
@@ -8743,13 +8743,13 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>172.125602214255</v>
+        <v>172.125602280048</v>
       </c>
       <c r="C110" t="n">
-        <v>29.8474904032911</v>
+        <v>29.8474904204879</v>
       </c>
       <c r="D110" t="n">
-        <v>32.3781980595716</v>
+        <v>32.3781937252677</v>
       </c>
     </row>
     <row r="111">
@@ -8757,13 +8757,13 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>174.326041179765</v>
+        <v>174.326041402758</v>
       </c>
       <c r="C111" t="n">
-        <v>30.7271956321931</v>
+        <v>30.7271956496404</v>
       </c>
       <c r="D111" t="n">
-        <v>31.8165376960058</v>
+        <v>31.8165333175774</v>
       </c>
     </row>
     <row r="112">
@@ -8771,13 +8771,13 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>160.85703400677</v>
+        <v>160.857033297347</v>
       </c>
       <c r="C112" t="n">
-        <v>26.5438461938319</v>
+        <v>26.5438462116409</v>
       </c>
       <c r="D112" t="n">
-        <v>31.2672070852491</v>
+        <v>31.2672026657887</v>
       </c>
     </row>
     <row r="113">
@@ -8785,13 +8785,13 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>182.536281511811</v>
+        <v>182.536282321103</v>
       </c>
       <c r="C113" t="n">
-        <v>33.7054254148057</v>
+        <v>33.7054254329839</v>
       </c>
       <c r="D113" t="n">
-        <v>30.7302062273016</v>
+        <v>30.7302017699016</v>
       </c>
     </row>
     <row r="114">
@@ -8799,13 +8799,13 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>171.174091107399</v>
+        <v>171.174091135827</v>
       </c>
       <c r="C114" t="n">
-        <v>30.1948935423596</v>
+        <v>30.1948935611954</v>
       </c>
       <c r="D114" t="n">
-        <v>30.2055351221632</v>
+        <v>30.2055306299161</v>
       </c>
     </row>
     <row r="115">
@@ -8813,13 +8813,13 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>174.784332177757</v>
+        <v>174.784332469976</v>
       </c>
       <c r="C115" t="n">
-        <v>31.5160988705814</v>
+        <v>31.5160988900302</v>
       </c>
       <c r="D115" t="n">
-        <v>29.6893302667087</v>
+        <v>29.6893257419247</v>
       </c>
     </row>
     <row r="116">
@@ -8827,13 +8827,13 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>162.953376542831</v>
+        <v>162.953376023652</v>
       </c>
       <c r="C116" t="n">
-        <v>27.8491106261133</v>
+        <v>27.8491106459462</v>
       </c>
       <c r="D116" t="n">
-        <v>29.1815916609381</v>
+        <v>29.1815871059276</v>
       </c>
     </row>
     <row r="117">
@@ -8841,13 +8841,13 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>183.127724838288</v>
+        <v>183.127725739494</v>
       </c>
       <c r="C117" t="n">
-        <v>34.5134214035907</v>
+        <v>34.5134214238429</v>
       </c>
       <c r="D117" t="n">
-        <v>28.6823193048514</v>
+        <v>28.6823147219246</v>
       </c>
     </row>
     <row r="118">
@@ -8855,13 +8855,13 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>173.401628846726</v>
+        <v>173.401629087431</v>
       </c>
       <c r="C118" t="n">
-        <v>31.5209469675882</v>
+        <v>31.5209469886282</v>
       </c>
       <c r="D118" t="n">
-        <v>28.1915131984486</v>
+        <v>28.1915085899159</v>
       </c>
     </row>
     <row r="119">
@@ -8869,13 +8869,13 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>175.31354514518</v>
+        <v>175.313545536774</v>
       </c>
       <c r="C119" t="n">
-        <v>32.2841032973871</v>
+        <v>32.2841033188776</v>
       </c>
       <c r="D119" t="n">
-        <v>27.7074857456212</v>
+        <v>27.7074811136374</v>
       </c>
     </row>
     <row r="120">
@@ -8883,13 +8883,13 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>165.191028161482</v>
+        <v>165.19102786657</v>
       </c>
       <c r="C120" t="n">
-        <v>29.1595478960459</v>
+        <v>29.1595479178933</v>
       </c>
       <c r="D120" t="n">
-        <v>27.2302369463691</v>
+        <v>27.2302322930891</v>
       </c>
     </row>
     <row r="121">
@@ -8897,13 +8897,13 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>183.894120220789</v>
+        <v>183.894121249581</v>
       </c>
       <c r="C121" t="n">
-        <v>35.3401423535762</v>
+        <v>35.3401423758169</v>
       </c>
       <c r="D121" t="n">
-        <v>26.7597668006924</v>
+        <v>26.7597621282711</v>
       </c>
     </row>
     <row r="122">
@@ -8911,13 +8911,13 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>175.675758760289</v>
+        <v>175.675759240422</v>
       </c>
       <c r="C122" t="n">
-        <v>32.8263145063414</v>
+        <v>32.8263145296521</v>
       </c>
       <c r="D122" t="n">
-        <v>26.296075308591</v>
+        <v>26.2960706191834</v>
       </c>
     </row>
     <row r="123">
@@ -8925,13 +8925,13 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>175.891625164988</v>
+        <v>175.891625682238</v>
       </c>
       <c r="C123" t="n">
-        <v>33.0314152597404</v>
+        <v>33.0314152833135</v>
       </c>
       <c r="D123" t="n">
-        <v>25.8466848853268</v>
+        <v>25.846680180746</v>
       </c>
     </row>
     <row r="124">
@@ -8939,13 +8939,13 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>167.566736008126</v>
+        <v>167.566735967977</v>
       </c>
       <c r="C124" t="n">
-        <v>30.474573961221</v>
+        <v>30.4745739850742</v>
       </c>
       <c r="D124" t="n">
-        <v>25.4115955308996</v>
+        <v>25.4115908129589</v>
       </c>
     </row>
     <row r="125">
@@ -8953,13 +8953,13 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>184.863327302613</v>
+        <v>184.863328491012</v>
       </c>
       <c r="C125" t="n">
-        <v>36.1860692320598</v>
+        <v>36.1860692562033</v>
       </c>
       <c r="D125" t="n">
-        <v>24.9908072453095</v>
+        <v>24.9908025158222</v>
       </c>
     </row>
     <row r="126">
@@ -8967,13 +8967,13 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>178.057014367754</v>
+        <v>178.057015109491</v>
       </c>
       <c r="C126" t="n">
-        <v>34.1109268869508</v>
+        <v>34.1109269125981</v>
       </c>
       <c r="D126" t="n">
-        <v>24.5843200285566</v>
+        <v>24.5843152893357</v>
       </c>
     </row>
     <row r="127">
@@ -8981,13 +8981,13 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>180.383009904626</v>
+        <v>180.383010835515</v>
       </c>
       <c r="C127" t="n">
-        <v>34.9906321158527</v>
+        <v>34.9906321417504</v>
       </c>
       <c r="D127" t="n">
-        <v>24.1572080533184</v>
+        <v>24.1572033062014</v>
       </c>
     </row>
     <row r="128">
@@ -8995,13 +8995,13 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>167.008807129002</v>
+        <v>167.008807158709</v>
       </c>
       <c r="C128" t="n">
-        <v>30.8072826774936</v>
+        <v>30.807282703753</v>
       </c>
       <c r="D128" t="n">
-        <v>23.7094713195951</v>
+        <v>23.7094665664191</v>
       </c>
     </row>
     <row r="129">
@@ -9009,13 +9009,13 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>188.752106857407</v>
+        <v>188.752108436347</v>
       </c>
       <c r="C129" t="n">
-        <v>37.9688618984663</v>
+        <v>37.9688619250949</v>
       </c>
       <c r="D129" t="n">
-        <v>23.2411098273867</v>
+        <v>23.241105069989</v>
       </c>
     </row>
     <row r="130">
@@ -9023,13 +9023,13 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>177.423216502348</v>
+        <v>177.423217330224</v>
       </c>
       <c r="C130" t="n">
-        <v>34.4583300260155</v>
+        <v>34.4583300533017</v>
       </c>
       <c r="D130" t="n">
-        <v>22.752123576693</v>
+        <v>22.7521188169109</v>
       </c>
     </row>
     <row r="131">
@@ -9037,13 +9037,13 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>181.172934040588</v>
+        <v>181.172935158887</v>
       </c>
       <c r="C131" t="n">
-        <v>35.7795353542417</v>
+        <v>35.779535382141</v>
       </c>
       <c r="D131" t="n">
-        <v>22.3853838886728</v>
+        <v>22.3853791271024</v>
       </c>
     </row>
     <row r="132">
@@ -9051,13 +9051,13 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>169.587631292023</v>
+        <v>169.587631622385</v>
       </c>
       <c r="C132" t="n">
-        <v>32.112547109771</v>
+        <v>32.1125471380543</v>
       </c>
       <c r="D132" t="n">
-        <v>22.140890763326</v>
+        <v>22.1408860005633</v>
       </c>
     </row>
     <row r="133">
@@ -9065,13 +9065,13 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>190.11380889235</v>
+        <v>190.113810663391</v>
       </c>
       <c r="C133" t="n">
-        <v>38.7768578872492</v>
+        <v>38.7768579159518</v>
       </c>
       <c r="D133" t="n">
-        <v>22.0186442006526</v>
+        <v>22.0186394372938</v>
       </c>
     </row>
   </sheetData>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>6.58158660432072</v>
+        <v>6.58158653671646</v>
       </c>
     </row>
     <row r="3">
@@ -9106,7 +9106,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8638338028851</v>
+        <v>16.8638342557031</v>
       </c>
     </row>
     <row r="4">
@@ -9114,7 +9114,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>-6.7178477866303</v>
+        <v>-6.71784936923454</v>
       </c>
     </row>
     <row r="5">
@@ -9122,7 +9122,7 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>41.6197312137347</v>
+        <v>41.619732411125</v>
       </c>
     </row>
     <row r="6">
@@ -9130,7 +9130,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.18604902225504</v>
+        <v>4.18604899490934</v>
       </c>
     </row>
     <row r="7">
@@ -9138,7 +9138,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>18.3346197356864</v>
+        <v>18.3346200893177</v>
       </c>
     </row>
     <row r="8">
@@ -9146,7 +9146,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.27531649850542</v>
+        <v>-4.27531814589013</v>
       </c>
     </row>
     <row r="9">
@@ -9154,7 +9154,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>41.8557349419305</v>
+        <v>41.8557362630293</v>
       </c>
     </row>
     <row r="10">
@@ -9162,7 +9162,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>19.8261312377309</v>
+        <v>19.8261309224413</v>
       </c>
     </row>
     <row r="11">
@@ -9170,7 +9170,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>29.0387581516253</v>
+        <v>29.0387584707472</v>
       </c>
     </row>
     <row r="12">
@@ -9178,7 +9178,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>2.03084677078762</v>
+        <v>2.03084525940147</v>
       </c>
     </row>
     <row r="13">
@@ -9186,7 +9186,7 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>43.7691184277618</v>
+        <v>43.7691199353152</v>
       </c>
     </row>
     <row r="14">
@@ -9194,7 +9194,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>25.7978291092536</v>
+        <v>25.7978288527819</v>
       </c>
     </row>
     <row r="15">
@@ -9202,7 +9202,7 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>34.4018762396655</v>
+        <v>34.4018765715641</v>
       </c>
     </row>
     <row r="16">
@@ -9210,7 +9210,7 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>10.4986496730368</v>
+        <v>10.498648147361</v>
       </c>
     </row>
     <row r="17">
@@ -9218,7 +9218,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>58.553689462335</v>
+        <v>58.5536909125837</v>
       </c>
     </row>
     <row r="18">
@@ -9226,7 +9226,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>52.410590135374</v>
+        <v>52.4105899208566</v>
       </c>
     </row>
     <row r="19">
@@ -9234,7 +9234,7 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>65.9391170690309</v>
+        <v>65.9391173284113</v>
       </c>
     </row>
     <row r="20">
@@ -9242,7 +9242,7 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>45.7813521207111</v>
+        <v>45.781350591238</v>
       </c>
     </row>
     <row r="21">
@@ -9250,7 +9250,7 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>93.3353729838994</v>
+        <v>93.3353744685093</v>
       </c>
     </row>
     <row r="22">
@@ -9258,7 +9258,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>107.655509756284</v>
+        <v>107.655509496815</v>
       </c>
     </row>
     <row r="23">
@@ -9266,7 +9266,7 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>110.880142275346</v>
+        <v>110.880142462146</v>
       </c>
     </row>
     <row r="24">
@@ -9274,7 +9274,7 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>77.3693895029116</v>
+        <v>77.3693880127336</v>
       </c>
     </row>
     <row r="25">
@@ -9282,7 +9282,7 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>105.472782758441</v>
+        <v>105.472784321288</v>
       </c>
     </row>
     <row r="26">
@@ -9290,7 +9290,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>101.039564517578</v>
+        <v>101.039564467368</v>
       </c>
     </row>
     <row r="27">
@@ -9298,7 +9298,7 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>90.9495594930202</v>
+        <v>90.9495597481429</v>
       </c>
     </row>
     <row r="28">
@@ -9306,7 +9306,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>59.7351180080814</v>
+        <v>59.7351165736948</v>
       </c>
     </row>
     <row r="29">
@@ -9314,7 +9314,7 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>98.4981230536709</v>
+        <v>98.4981242831451</v>
       </c>
     </row>
     <row r="30">
@@ -9322,7 +9322,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>77.872012505586</v>
+        <v>77.8720127441485</v>
       </c>
     </row>
     <row r="31">
@@ -9330,7 +9330,7 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>83.0527040338147</v>
+        <v>83.0527042663316</v>
       </c>
     </row>
     <row r="32">
@@ -9338,7 +9338,7 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>61.2120354021274</v>
+        <v>61.2120339387369</v>
       </c>
     </row>
     <row r="33">
@@ -9346,7 +9346,7 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>96.1797984033627</v>
+        <v>96.179799395674</v>
       </c>
     </row>
     <row r="34">
@@ -9354,7 +9354,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>72.0321173705735</v>
+        <v>72.0321175204987</v>
       </c>
     </row>
     <row r="35">
@@ -9362,7 +9362,7 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>69.7894289025229</v>
+        <v>69.7894290495669</v>
       </c>
     </row>
     <row r="36">
@@ -9370,7 +9370,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>52.2629568147169</v>
+        <v>52.2629558351695</v>
       </c>
     </row>
     <row r="37">
@@ -9378,7 +9378,7 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>75.5991673572246</v>
+        <v>75.5991680398029</v>
       </c>
     </row>
     <row r="38">
@@ -9386,7 +9386,7 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>54.0987426100509</v>
+        <v>54.0987427324352</v>
       </c>
     </row>
     <row r="39">
@@ -9394,7 +9394,7 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>55.9757686470956</v>
+        <v>55.9757687016194</v>
       </c>
     </row>
     <row r="40">
@@ -9402,7 +9402,7 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>52.9657776513523</v>
+        <v>52.9657771215292</v>
       </c>
     </row>
     <row r="41">
@@ -9410,7 +9410,7 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>73.534609045267</v>
+        <v>73.5346093981822</v>
       </c>
     </row>
     <row r="42">
@@ -9418,7 +9418,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>70.0131013273525</v>
+        <v>70.0131013620881</v>
       </c>
     </row>
     <row r="43">
@@ -9426,7 +9426,7 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>76.0026009989905</v>
+        <v>76.0026009775156</v>
       </c>
     </row>
     <row r="44">
@@ -9434,7 +9434,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>74.8368918082509</v>
+        <v>74.8368914848983</v>
       </c>
     </row>
     <row r="45">
@@ -9442,7 +9442,7 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>83.4641293737582</v>
+        <v>83.4641296838501</v>
       </c>
     </row>
     <row r="46">
@@ -9450,7 +9450,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>92.9176550605472</v>
+        <v>92.9176549784991</v>
       </c>
     </row>
     <row r="47">
@@ -9458,7 +9458,7 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>89.743927341452</v>
+        <v>89.7439272622113</v>
       </c>
     </row>
     <row r="48">
@@ -9466,7 +9466,7 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>87.210770114918</v>
+        <v>87.2107700218772</v>
       </c>
     </row>
     <row r="49">
@@ -9474,7 +9474,7 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>90.7396313825376</v>
+        <v>90.7396316368671</v>
       </c>
     </row>
     <row r="50">
@@ -9482,7 +9482,7 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>103.363080509089</v>
+        <v>103.363080574898</v>
       </c>
     </row>
     <row r="51">
@@ -9490,7 +9490,7 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>104.62284763583</v>
+        <v>104.622847661863</v>
       </c>
     </row>
     <row r="52">
@@ -9498,7 +9498,7 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>108.250028018072</v>
+        <v>108.250028001507</v>
       </c>
     </row>
     <row r="53">
@@ -9506,7 +9506,7 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>114.053872422289</v>
+        <v>114.053872347012</v>
       </c>
     </row>
     <row r="54">
@@ -9514,7 +9514,7 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>142.767591716327</v>
+        <v>142.767591641887</v>
       </c>
     </row>
     <row r="55">
@@ -9522,7 +9522,7 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>143.873261370088</v>
+        <v>143.873261181657</v>
       </c>
     </row>
     <row r="56">
@@ -9530,7 +9530,7 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>141.95750075299</v>
+        <v>141.957500679914</v>
       </c>
     </row>
     <row r="57">
@@ -9538,7 +9538,7 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>137.943384271508</v>
+        <v>137.943384607456</v>
       </c>
     </row>
     <row r="58">
@@ -9546,7 +9546,7 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>150.371071094008</v>
+        <v>150.371070847122</v>
       </c>
     </row>
     <row r="59">
@@ -9554,7 +9554,7 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>137.149487850753</v>
+        <v>137.149487385303</v>
       </c>
     </row>
     <row r="60">
@@ -9562,7 +9562,7 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>141.854054512268</v>
+        <v>141.854054651498</v>
       </c>
     </row>
     <row r="61">
@@ -9570,7 +9570,7 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>150.219211751726</v>
+        <v>150.219212324832</v>
       </c>
     </row>
     <row r="62">
@@ -9578,7 +9578,7 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>153.119136992031</v>
+        <v>153.119136991412</v>
       </c>
     </row>
     <row r="63">
@@ -9586,7 +9586,7 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>156.315172834714</v>
+        <v>156.315172655529</v>
       </c>
     </row>
     <row r="64">
@@ -9594,7 +9594,7 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>160.613508291697</v>
+        <v>160.613508184391</v>
       </c>
     </row>
     <row r="65">
@@ -9602,7 +9602,7 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>167.048736281263</v>
+        <v>167.048736568374</v>
       </c>
     </row>
     <row r="66">
@@ -9610,7 +9610,7 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>175.872617615248</v>
+        <v>175.872617592945</v>
       </c>
     </row>
     <row r="67">
@@ -9618,7 +9618,7 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>176.009976299679</v>
+        <v>176.009976375092</v>
       </c>
     </row>
     <row r="68">
@@ -9626,7 +9626,7 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>172.822477365257</v>
+        <v>172.822477275217</v>
       </c>
     </row>
     <row r="69">
@@ -9634,7 +9634,7 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>174.283382080572</v>
+        <v>174.283382117502</v>
       </c>
     </row>
     <row r="70">
@@ -9642,7 +9642,7 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>189.814011664359</v>
+        <v>189.814011609322</v>
       </c>
     </row>
     <row r="71">
@@ -9650,7 +9650,7 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>186.667850961659</v>
+        <v>186.667850816256</v>
       </c>
     </row>
     <row r="72">
@@ -9658,7 +9658,7 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>179.987835602129</v>
+        <v>179.987835255298</v>
       </c>
     </row>
     <row r="73">
@@ -9666,7 +9666,7 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>187.089739594603</v>
+        <v>187.089740141874</v>
       </c>
     </row>
     <row r="74">
@@ -9674,7 +9674,7 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>173.853060373522</v>
+        <v>173.853059918806</v>
       </c>
     </row>
     <row r="75">
@@ -9682,7 +9682,7 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>178.161900666382</v>
+        <v>178.161900579518</v>
       </c>
     </row>
     <row r="76">
@@ -9690,7 +9690,7 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>186.618093492237</v>
+        <v>186.618093595414</v>
       </c>
     </row>
     <row r="77">
@@ -9698,7 +9698,7 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>203.85694546786</v>
+        <v>203.856945906263</v>
       </c>
     </row>
     <row r="78">
@@ -9706,7 +9706,7 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>213.902429636331</v>
+        <v>213.902429505026</v>
       </c>
     </row>
     <row r="79">
@@ -9714,7 +9714,7 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>217.654686983654</v>
+        <v>217.654686722971</v>
       </c>
     </row>
     <row r="80">
@@ -9722,7 +9722,7 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>212.51827611322</v>
+        <v>212.518276045754</v>
       </c>
     </row>
     <row r="81">
@@ -9730,7 +9730,7 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>198.652607266795</v>
+        <v>198.652607726249</v>
       </c>
     </row>
     <row r="82">
@@ -9738,7 +9738,7 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>179.907032096878</v>
+        <v>179.907031717407</v>
       </c>
     </row>
     <row r="83">
@@ -9746,7 +9746,7 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>169.760754942314</v>
+        <v>169.760755217907</v>
       </c>
     </row>
     <row r="84">
@@ -9754,7 +9754,7 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>162.726448224737</v>
+        <v>162.72644829924</v>
       </c>
     </row>
     <row r="85">
@@ -9762,7 +9762,7 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>173.328956025963</v>
+        <v>173.328956055339</v>
       </c>
     </row>
     <row r="86">
@@ -9770,7 +9770,7 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>159.095559294447</v>
+        <v>159.095559494053</v>
       </c>
     </row>
     <row r="87">
@@ -9778,7 +9778,7 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>173.116934325842</v>
+        <v>173.116934132645</v>
       </c>
     </row>
     <row r="88">
@@ -9786,7 +9786,7 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>185.883386943967</v>
+        <v>185.883386757617</v>
       </c>
     </row>
     <row r="89">
@@ -9794,7 +9794,7 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>196.817973314666</v>
+        <v>196.817973494608</v>
       </c>
     </row>
     <row r="90">
@@ -9802,7 +9802,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>201.195586871065</v>
+        <v>201.195586847268</v>
       </c>
     </row>
     <row r="91">
@@ -9810,7 +9810,7 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>197.192041694754</v>
+        <v>197.192041698394</v>
       </c>
     </row>
     <row r="92">
@@ -9818,7 +9818,7 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>190.038230753169</v>
+        <v>190.038230779697</v>
       </c>
     </row>
     <row r="93">
@@ -9826,7 +9826,7 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>178.998892699051</v>
+        <v>178.998892692681</v>
       </c>
     </row>
     <row r="94">
@@ -9834,7 +9834,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>184.607742957704</v>
+        <v>184.607743236531</v>
       </c>
     </row>
     <row r="95">
@@ -9842,7 +9842,7 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>172.694099923761</v>
+        <v>172.694100086681</v>
       </c>
     </row>
     <row r="96">
@@ -9850,7 +9850,7 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>149.978907263566</v>
+        <v>149.978906320426</v>
       </c>
     </row>
     <row r="97">
@@ -9858,7 +9858,7 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>167.279865793651</v>
+        <v>167.279866295044</v>
       </c>
     </row>
     <row r="98">
@@ -9866,7 +9866,7 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>166.486665217697</v>
+        <v>166.48666497716</v>
       </c>
     </row>
     <row r="99">
@@ -9874,7 +9874,7 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>170.388451293531</v>
+        <v>170.388451321141</v>
       </c>
     </row>
     <row r="100">
@@ -9882,7 +9882,7 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>158.650978132251</v>
+        <v>158.650977331891</v>
       </c>
     </row>
     <row r="101">
@@ -9890,7 +9890,7 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>178.720746369567</v>
+        <v>178.720746952097</v>
       </c>
     </row>
     <row r="102">
@@ -9898,7 +9898,7 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>168.692007788062</v>
+        <v>168.69200765167</v>
       </c>
     </row>
     <row r="103">
@@ -9906,7 +9906,7 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>170.353376184887</v>
+        <v>170.353376147471</v>
       </c>
     </row>
     <row r="104">
@@ -9914,7 +9914,7 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>160.032405987878</v>
+        <v>160.032405218552</v>
       </c>
     </row>
     <row r="105">
@@ -9922,7 +9922,7 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>178.589139522246</v>
+        <v>178.589140037729</v>
       </c>
     </row>
     <row r="106">
@@ -9930,7 +9930,7 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>170.276514225127</v>
+        <v>170.276514159564</v>
       </c>
     </row>
     <row r="107">
@@ -9938,7 +9938,7 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>170.382605566025</v>
+        <v>170.382605505123</v>
       </c>
     </row>
     <row r="108">
@@ -9946,7 +9946,7 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>161.932430118163</v>
+        <v>161.932429467335</v>
       </c>
     </row>
     <row r="109">
@@ -9954,7 +9954,7 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>179.088223894483</v>
+        <v>179.088224439605</v>
       </c>
     </row>
     <row r="110">
@@ -9962,7 +9962,7 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>172.125602214255</v>
+        <v>172.125602280048</v>
       </c>
     </row>
     <row r="111">
@@ -9970,7 +9970,7 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>174.326041179765</v>
+        <v>174.326041402758</v>
       </c>
     </row>
     <row r="112">
@@ -9978,7 +9978,7 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>160.85703400677</v>
+        <v>160.857033297347</v>
       </c>
     </row>
     <row r="113">
@@ -9986,7 +9986,7 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>182.536281511811</v>
+        <v>182.536282321103</v>
       </c>
     </row>
     <row r="114">
@@ -9994,7 +9994,7 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>171.174091107399</v>
+        <v>171.174091135827</v>
       </c>
     </row>
     <row r="115">
@@ -10002,7 +10002,7 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>174.784332177757</v>
+        <v>174.784332469976</v>
       </c>
     </row>
     <row r="116">
@@ -10010,7 +10010,7 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>162.953376542831</v>
+        <v>162.953376023652</v>
       </c>
     </row>
     <row r="117">
@@ -10018,7 +10018,7 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>183.127724838288</v>
+        <v>183.127725739494</v>
       </c>
     </row>
     <row r="118">
@@ -10026,7 +10026,7 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>173.401628846726</v>
+        <v>173.401629087431</v>
       </c>
     </row>
     <row r="119">
@@ -10034,7 +10034,7 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>175.31354514518</v>
+        <v>175.313545536774</v>
       </c>
     </row>
     <row r="120">
@@ -10042,7 +10042,7 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>165.191028161482</v>
+        <v>165.19102786657</v>
       </c>
     </row>
     <row r="121">
@@ -10050,7 +10050,7 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>183.894120220789</v>
+        <v>183.894121249581</v>
       </c>
     </row>
     <row r="122">
@@ -10058,7 +10058,7 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>175.675758760289</v>
+        <v>175.675759240422</v>
       </c>
     </row>
     <row r="123">
@@ -10066,7 +10066,7 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>175.891625164988</v>
+        <v>175.891625682238</v>
       </c>
     </row>
     <row r="124">
@@ -10074,7 +10074,7 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>167.566736008126</v>
+        <v>167.566735967977</v>
       </c>
     </row>
     <row r="125">
@@ -10082,7 +10082,7 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>184.863327302613</v>
+        <v>184.863328491012</v>
       </c>
     </row>
     <row r="126">
@@ -10090,7 +10090,7 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>178.057014367754</v>
+        <v>178.057015109491</v>
       </c>
     </row>
     <row r="127">
@@ -10098,7 +10098,7 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>180.383009904626</v>
+        <v>180.383010835515</v>
       </c>
     </row>
     <row r="128">
@@ -10106,7 +10106,7 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>167.008807129002</v>
+        <v>167.008807158709</v>
       </c>
     </row>
     <row r="129">
@@ -10114,7 +10114,7 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>188.752106857407</v>
+        <v>188.752108436347</v>
       </c>
     </row>
     <row r="130">
@@ -10122,7 +10122,7 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>177.423216502348</v>
+        <v>177.423217330224</v>
       </c>
     </row>
     <row r="131">
@@ -10130,7 +10130,7 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>181.172934040588</v>
+        <v>181.172935158887</v>
       </c>
     </row>
     <row r="132">
@@ -10138,7 +10138,7 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>169.587631292023</v>
+        <v>169.587631622385</v>
       </c>
     </row>
     <row r="133">
@@ -10146,7 +10146,7 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>190.11380889235</v>
+        <v>190.113810663391</v>
       </c>
     </row>
   </sheetData>
